--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_office_equipment_services.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_office_equipment_services.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="cose_gest_n0000" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0415</v>
+        <v>0.13</v>
+      </c>
+      <c r="E2">
+        <v>0.0742</v>
       </c>
       <c r="G2">
-        <v>0.1425316455696202</v>
+        <v>0.1082914572864322</v>
       </c>
       <c r="H2">
-        <v>0.1425316455696202</v>
+        <v>0.1082914572864322</v>
       </c>
       <c r="I2">
-        <v>-0.006075949367088608</v>
+        <v>0.1183417085427136</v>
       </c>
       <c r="J2">
-        <v>-0.006075949367088608</v>
+        <v>0.1163129935391242</v>
       </c>
       <c r="K2">
-        <v>-0.137</v>
+        <v>0.172</v>
       </c>
       <c r="L2">
-        <v>-0.03468354430379747</v>
+        <v>0.04321608040201005</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +629,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.035</v>
+        <v>0.067</v>
       </c>
       <c r="V2">
-        <v>0.03538928210313448</v>
+        <v>0.1324110671936759</v>
       </c>
       <c r="W2">
-        <v>-0.09647887323943663</v>
+        <v>0.1194444444444444</v>
       </c>
       <c r="X2">
-        <v>0.254352669402848</v>
+        <v>0.4205887707456893</v>
       </c>
       <c r="Y2">
-        <v>-0.3508315426422847</v>
+        <v>-0.3011443263012449</v>
       </c>
       <c r="Z2">
-        <v>1.861451460885957</v>
+        <v>1.660408844388819</v>
       </c>
       <c r="AA2">
-        <v>-0.01131008482563619</v>
+        <v>0.1931271231897014</v>
       </c>
       <c r="AB2">
-        <v>0.1650237613978035</v>
+        <v>0.2913512063631132</v>
       </c>
       <c r="AC2">
-        <v>-0.1763338462234397</v>
+        <v>-0.09822408317341175</v>
       </c>
       <c r="AD2">
-        <v>0.992</v>
+        <v>0.474</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.992</v>
+        <v>0.474</v>
       </c>
       <c r="AG2">
-        <v>0.957</v>
+        <v>0.407</v>
       </c>
       <c r="AH2">
-        <v>0.5007571933366987</v>
+        <v>0.4836734693877551</v>
       </c>
       <c r="AI2">
-        <v>0.4078947368421053</v>
+        <v>0.3298538622129437</v>
       </c>
       <c r="AJ2">
-        <v>0.4917780061664954</v>
+        <v>0.4457831325301204</v>
       </c>
       <c r="AK2">
-        <v>0.3992490613266583</v>
+        <v>0.2970802919708029</v>
       </c>
       <c r="AL2">
-        <v>0.007</v>
+        <v>0.13</v>
       </c>
       <c r="AM2">
-        <v>-0.043</v>
+        <v>0.129</v>
       </c>
       <c r="AN2">
-        <v>2.259681093394077</v>
+        <v>0.6899563318777292</v>
       </c>
       <c r="AO2">
-        <v>-3.428571428571428</v>
+        <v>3.623076923076923</v>
       </c>
       <c r="AP2">
-        <v>2.17995444191344</v>
+        <v>0.5924308588064046</v>
       </c>
       <c r="AQ2">
-        <v>0.5581395348837209</v>
+        <v>3.651162790697674</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0415</v>
+        <v>0.13</v>
+      </c>
+      <c r="E3">
+        <v>0.0742</v>
       </c>
       <c r="G3">
-        <v>0.1425316455696202</v>
+        <v>0.1082914572864322</v>
       </c>
       <c r="H3">
-        <v>0.1425316455696202</v>
+        <v>0.1082914572864322</v>
       </c>
       <c r="I3">
-        <v>-0.006075949367088608</v>
+        <v>0.1183417085427136</v>
       </c>
       <c r="J3">
-        <v>-0.006075949367088608</v>
+        <v>0.1163129935391242</v>
       </c>
       <c r="K3">
-        <v>-0.137</v>
+        <v>0.172</v>
       </c>
       <c r="L3">
-        <v>-0.03468354430379747</v>
+        <v>0.04321608040201005</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +751,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +760,8791 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.035</v>
+        <v>0.067</v>
       </c>
       <c r="V3">
-        <v>0.03538928210313448</v>
+        <v>0.1324110671936759</v>
       </c>
       <c r="W3">
-        <v>-0.09647887323943663</v>
+        <v>0.1194444444444444</v>
       </c>
       <c r="X3">
-        <v>0.254352669402848</v>
+        <v>0.4205887707456893</v>
       </c>
       <c r="Y3">
-        <v>-0.3508315426422847</v>
+        <v>-0.3011443263012449</v>
       </c>
       <c r="Z3">
-        <v>1.861451460885957</v>
+        <v>1.660408844388819</v>
       </c>
       <c r="AA3">
-        <v>-0.01131008482563619</v>
+        <v>0.1931271231897014</v>
       </c>
       <c r="AB3">
-        <v>0.1650237613978035</v>
+        <v>0.2913512063631132</v>
       </c>
       <c r="AC3">
-        <v>-0.1763338462234397</v>
+        <v>-0.09822408317341175</v>
       </c>
       <c r="AD3">
-        <v>0.992</v>
+        <v>0.474</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.992</v>
+        <v>0.474</v>
       </c>
       <c r="AG3">
-        <v>0.957</v>
+        <v>0.407</v>
       </c>
       <c r="AH3">
-        <v>0.5007571933366987</v>
+        <v>0.4836734693877551</v>
       </c>
       <c r="AI3">
-        <v>0.4078947368421053</v>
+        <v>0.3298538622129437</v>
       </c>
       <c r="AJ3">
-        <v>0.4917780061664954</v>
+        <v>0.4457831325301204</v>
       </c>
       <c r="AK3">
-        <v>0.3992490613266583</v>
+        <v>0.2970802919708029</v>
       </c>
       <c r="AL3">
-        <v>0.007</v>
+        <v>0.13</v>
       </c>
       <c r="AM3">
-        <v>-0.043</v>
+        <v>0.129</v>
       </c>
       <c r="AN3">
-        <v>2.259681093394077</v>
+        <v>0.6899563318777292</v>
       </c>
       <c r="AO3">
-        <v>-3.428571428571428</v>
+        <v>3.623076923076923</v>
       </c>
       <c r="AP3">
-        <v>2.17995444191344</v>
+        <v>0.5924308588064046</v>
       </c>
       <c r="AQ3">
-        <v>0.5581395348837209</v>
+        <v>3.651162790697674</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Gestetner of Ceylon PLC (COSE:GEST.N0000)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>COSE:GEST.N0000</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Office Equipment &amp; Services</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.483673469387755</v>
+      </c>
+      <c r="F2">
+        <v>0.99</v>
+      </c>
+      <c r="G2">
+        <v>0.506</v>
+      </c>
+      <c r="H2">
+        <v>0.475832090994348</v>
+      </c>
+      <c r="I2">
+        <v>0.913</v>
+      </c>
+      <c r="J2">
+        <v>1.37903209099435</v>
+      </c>
+      <c r="K2">
+        <v>0.474</v>
+      </c>
+      <c r="L2">
+        <v>0.9702</v>
+      </c>
+      <c r="M2">
+        <v>0.291351206363113</v>
+      </c>
+      <c r="N2">
+        <v>0.206003687945553</v>
+      </c>
+      <c r="O2">
+        <v>0.153388743119266</v>
+      </c>
+      <c r="P2">
+        <v>0.035948</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.420588770745689</v>
+      </c>
+      <c r="T2">
+        <v>17.0415167945553</v>
+      </c>
+      <c r="U2">
+        <v>1.43389137385794</v>
+      </c>
+      <c r="V2">
+        <v>63.8574280124701</v>
+      </c>
+      <c r="W2">
+        <v>10.26357112131802</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>0.506</v>
+      </c>
+      <c r="AB2">
+        <v>0.2662605952628563</v>
+      </c>
+      <c r="AC2">
+        <v>0.2018272935779817</v>
+      </c>
+      <c r="AD2">
+        <v>0.24</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="AH2">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="AI2">
+        <v>0.4320000000000001</v>
+      </c>
+      <c r="AJ2">
+        <v>0.474</v>
+      </c>
+      <c r="AK2">
+        <v>0.474</v>
+      </c>
+      <c r="AL2">
+        <v>0.13</v>
+      </c>
+      <c r="AM2">
+        <v>0.474</v>
+      </c>
+      <c r="AN2">
+        <v>0.067</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.261815697725017</v>
+      </c>
+      <c r="C2">
+        <v>1.100914893712241</v>
+      </c>
+      <c r="D2">
+        <v>1.033914893712242</v>
+      </c>
+      <c r="E2">
+        <v>-0.474</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.067</v>
+      </c>
+      <c r="H2">
+        <v>0.506</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K2">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L2">
+        <v>0.471</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0.471</v>
+      </c>
+      <c r="O2">
+        <v>0.11304</v>
+      </c>
+      <c r="P2">
+        <v>0.35796</v>
+      </c>
+      <c r="Q2">
+        <v>0.57396</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.261815697725017</v>
+      </c>
+      <c r="T2">
+        <v>0.8375843128603114</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.24</v>
+      </c>
+      <c r="W2">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.261239780050477</v>
+      </c>
+      <c r="C3">
+        <v>1.093791797371847</v>
+      </c>
+      <c r="D3">
+        <v>1.036591797371847</v>
+      </c>
+      <c r="E3">
+        <v>-0.4642</v>
+      </c>
+      <c r="F3">
+        <v>0.0098</v>
+      </c>
+      <c r="G3">
+        <v>0.067</v>
+      </c>
+      <c r="H3">
+        <v>0.506</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K3">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L3">
+        <v>0.471</v>
+      </c>
+      <c r="M3">
+        <v>0.00044786</v>
+      </c>
+      <c r="N3">
+        <v>0.47055214</v>
+      </c>
+      <c r="O3">
+        <v>0.1129325136</v>
+      </c>
+      <c r="P3">
+        <v>0.3576196264</v>
+      </c>
+      <c r="Q3">
+        <v>0.5736196264000001</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.2635277374247242</v>
+      </c>
+      <c r="T3">
+        <v>0.8440142530398452</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.24</v>
+      </c>
+      <c r="W3">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>1051.667931943018</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.2606638623759369</v>
+      </c>
+      <c r="C4">
+        <v>1.086682598528</v>
+      </c>
+      <c r="D4">
+        <v>1.039282598528</v>
+      </c>
+      <c r="E4">
+        <v>-0.4544</v>
+      </c>
+      <c r="F4">
+        <v>0.0196</v>
+      </c>
+      <c r="G4">
+        <v>0.067</v>
+      </c>
+      <c r="H4">
+        <v>0.506</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K4">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L4">
+        <v>0.471</v>
+      </c>
+      <c r="M4">
+        <v>0.00089572</v>
+      </c>
+      <c r="N4">
+        <v>0.47010428</v>
+      </c>
+      <c r="O4">
+        <v>0.1128250272</v>
+      </c>
+      <c r="P4">
+        <v>0.3572792528</v>
+      </c>
+      <c r="Q4">
+        <v>0.5732792528000001</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.2652747167101397</v>
+      </c>
+      <c r="T4">
+        <v>0.8505754164883489</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.24</v>
+      </c>
+      <c r="W4">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>525.833965971509</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.2600879447013969</v>
+      </c>
+      <c r="C5">
+        <v>1.07958740568838</v>
+      </c>
+      <c r="D5">
+        <v>1.04198740568838</v>
+      </c>
+      <c r="E5">
+        <v>-0.4446</v>
+      </c>
+      <c r="F5">
+        <v>0.0294</v>
+      </c>
+      <c r="G5">
+        <v>0.067</v>
+      </c>
+      <c r="H5">
+        <v>0.506</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K5">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L5">
+        <v>0.471</v>
+      </c>
+      <c r="M5">
+        <v>0.00134358</v>
+      </c>
+      <c r="N5">
+        <v>0.46965642</v>
+      </c>
+      <c r="O5">
+        <v>0.1127175408</v>
+      </c>
+      <c r="P5">
+        <v>0.3569388792</v>
+      </c>
+      <c r="Q5">
+        <v>0.5729388792000001</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.2670577161870071</v>
+      </c>
+      <c r="T5">
+        <v>0.8572718616574405</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.24</v>
+      </c>
+      <c r="W5">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>350.5559773143393</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.2595120270268568</v>
+      </c>
+      <c r="C6">
+        <v>1.072506328493213</v>
+      </c>
+      <c r="D6">
+        <v>1.044706328493213</v>
+      </c>
+      <c r="E6">
+        <v>-0.4348</v>
+      </c>
+      <c r="F6">
+        <v>0.0392</v>
+      </c>
+      <c r="G6">
+        <v>0.067</v>
+      </c>
+      <c r="H6">
+        <v>0.506</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K6">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L6">
+        <v>0.471</v>
+      </c>
+      <c r="M6">
+        <v>0.00179144</v>
+      </c>
+      <c r="N6">
+        <v>0.46920856</v>
+      </c>
+      <c r="O6">
+        <v>0.1126100544</v>
+      </c>
+      <c r="P6">
+        <v>0.3565985056</v>
+      </c>
+      <c r="Q6">
+        <v>0.5725985056</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.2688778614863092</v>
+      </c>
+      <c r="T6">
+        <v>0.864107816100888</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.24</v>
+      </c>
+      <c r="W6">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>262.9169829857545</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.2589361093523168</v>
+      </c>
+      <c r="C7">
+        <v>1.065439477730079</v>
+      </c>
+      <c r="D7">
+        <v>1.047439477730079</v>
+      </c>
+      <c r="E7">
+        <v>-0.425</v>
+      </c>
+      <c r="F7">
+        <v>0.049</v>
+      </c>
+      <c r="G7">
+        <v>0.067</v>
+      </c>
+      <c r="H7">
+        <v>0.506</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K7">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L7">
+        <v>0.471</v>
+      </c>
+      <c r="M7">
+        <v>0.0022393</v>
+      </c>
+      <c r="N7">
+        <v>0.4687607</v>
+      </c>
+      <c r="O7">
+        <v>0.112502568</v>
+      </c>
+      <c r="P7">
+        <v>0.356258132</v>
+      </c>
+      <c r="Q7">
+        <v>0.5722581320000001</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.2707363256340177</v>
+      </c>
+      <c r="T7">
+        <v>0.8710876853747239</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.24</v>
+      </c>
+      <c r="W7">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>210.3335863886035</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.2583601916777768</v>
+      </c>
+      <c r="C8">
+        <v>1.058386965348969</v>
+      </c>
+      <c r="D8">
+        <v>1.050186965348969</v>
+      </c>
+      <c r="E8">
+        <v>-0.4152</v>
+      </c>
+      <c r="F8">
+        <v>0.0588</v>
+      </c>
+      <c r="G8">
+        <v>0.067</v>
+      </c>
+      <c r="H8">
+        <v>0.506</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K8">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L8">
+        <v>0.471</v>
+      </c>
+      <c r="M8">
+        <v>0.00268716</v>
+      </c>
+      <c r="N8">
+        <v>0.46831284</v>
+      </c>
+      <c r="O8">
+        <v>0.1123950816</v>
+      </c>
+      <c r="P8">
+        <v>0.3559177584</v>
+      </c>
+      <c r="Q8">
+        <v>0.5719177584</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.272634331572103</v>
+      </c>
+      <c r="T8">
+        <v>0.87821606250545</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.24</v>
+      </c>
+      <c r="W8">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>175.2779886571696</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.2577842740032367</v>
+      </c>
+      <c r="C9">
+        <v>1.051348904477562</v>
+      </c>
+      <c r="D9">
+        <v>1.052948904477562</v>
+      </c>
+      <c r="E9">
+        <v>-0.4054</v>
+      </c>
+      <c r="F9">
+        <v>0.06860000000000001</v>
+      </c>
+      <c r="G9">
+        <v>0.067</v>
+      </c>
+      <c r="H9">
+        <v>0.506</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K9">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L9">
+        <v>0.471</v>
+      </c>
+      <c r="M9">
+        <v>0.003135020000000001</v>
+      </c>
+      <c r="N9">
+        <v>0.46786498</v>
+      </c>
+      <c r="O9">
+        <v>0.1122875952</v>
+      </c>
+      <c r="P9">
+        <v>0.3555773848</v>
+      </c>
+      <c r="Q9">
+        <v>0.5715773848000001</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.27457315484219</v>
+      </c>
+      <c r="T9">
+        <v>0.8854977380690948</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.24</v>
+      </c>
+      <c r="W9">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>150.2382759918597</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.2572083563286967</v>
+      </c>
+      <c r="C10">
+        <v>1.044325409436757</v>
+      </c>
+      <c r="D10">
+        <v>1.055725409436757</v>
+      </c>
+      <c r="E10">
+        <v>-0.3956</v>
+      </c>
+      <c r="F10">
+        <v>0.0784</v>
+      </c>
+      <c r="G10">
+        <v>0.067</v>
+      </c>
+      <c r="H10">
+        <v>0.506</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K10">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L10">
+        <v>0.471</v>
+      </c>
+      <c r="M10">
+        <v>0.00358288</v>
+      </c>
+      <c r="N10">
+        <v>0.46741712</v>
+      </c>
+      <c r="O10">
+        <v>0.1121801088</v>
+      </c>
+      <c r="P10">
+        <v>0.3552370112</v>
+      </c>
+      <c r="Q10">
+        <v>0.5712370112</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.2765541264442355</v>
+      </c>
+      <c r="T10">
+        <v>0.8929377109276014</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.24</v>
+      </c>
+      <c r="W10">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>131.4584914928772</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.2566324386541566</v>
+      </c>
+      <c r="C11">
+        <v>1.037316595756444</v>
+      </c>
+      <c r="D11">
+        <v>1.058516595756444</v>
+      </c>
+      <c r="E11">
+        <v>-0.3858</v>
+      </c>
+      <c r="F11">
+        <v>0.0882</v>
+      </c>
+      <c r="G11">
+        <v>0.067</v>
+      </c>
+      <c r="H11">
+        <v>0.506</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K11">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L11">
+        <v>0.471</v>
+      </c>
+      <c r="M11">
+        <v>0.004030740000000001</v>
+      </c>
+      <c r="N11">
+        <v>0.46696926</v>
+      </c>
+      <c r="O11">
+        <v>0.1120726224</v>
+      </c>
+      <c r="P11">
+        <v>0.3548966376</v>
+      </c>
+      <c r="Q11">
+        <v>0.5708966376000001</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.2785786358836886</v>
+      </c>
+      <c r="T11">
+        <v>0.9005411996731084</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.24</v>
+      </c>
+      <c r="W11">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>116.8519924381131</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.2560565209796167</v>
+      </c>
+      <c r="C12">
+        <v>1.030322580191531</v>
+      </c>
+      <c r="D12">
+        <v>1.061322580191532</v>
+      </c>
+      <c r="E12">
+        <v>-0.376</v>
+      </c>
+      <c r="F12">
+        <v>0.098</v>
+      </c>
+      <c r="G12">
+        <v>0.067</v>
+      </c>
+      <c r="H12">
+        <v>0.506</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K12">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L12">
+        <v>0.471</v>
+      </c>
+      <c r="M12">
+        <v>0.004478600000000001</v>
+      </c>
+      <c r="N12">
+        <v>0.4665214</v>
+      </c>
+      <c r="O12">
+        <v>0.111965136</v>
+      </c>
+      <c r="P12">
+        <v>0.354556264</v>
+      </c>
+      <c r="Q12">
+        <v>0.570556264</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.2806481344217963</v>
+      </c>
+      <c r="T12">
+        <v>0.9083136548351822</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.24</v>
+      </c>
+      <c r="W12">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>105.1667931943018</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.2554806033050766</v>
+      </c>
+      <c r="C13">
+        <v>1.023343480738223</v>
+      </c>
+      <c r="D13">
+        <v>1.064143480738223</v>
+      </c>
+      <c r="E13">
+        <v>-0.3662</v>
+      </c>
+      <c r="F13">
+        <v>0.1078</v>
+      </c>
+      <c r="G13">
+        <v>0.067</v>
+      </c>
+      <c r="H13">
+        <v>0.506</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K13">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L13">
+        <v>0.471</v>
+      </c>
+      <c r="M13">
+        <v>0.004926460000000001</v>
+      </c>
+      <c r="N13">
+        <v>0.46607354</v>
+      </c>
+      <c r="O13">
+        <v>0.1118576496</v>
+      </c>
+      <c r="P13">
+        <v>0.3542158904</v>
+      </c>
+      <c r="Q13">
+        <v>0.5702158904000001</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.2827641385450299</v>
+      </c>
+      <c r="T13">
+        <v>0.9162607719110104</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.24</v>
+      </c>
+      <c r="W13">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>95.60617563118342</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.2549046856305365</v>
+      </c>
+      <c r="C14">
+        <v>1.016379416650559</v>
+      </c>
+      <c r="D14">
+        <v>1.066979416650559</v>
+      </c>
+      <c r="E14">
+        <v>-0.3564</v>
+      </c>
+      <c r="F14">
+        <v>0.1176</v>
+      </c>
+      <c r="G14">
+        <v>0.067</v>
+      </c>
+      <c r="H14">
+        <v>0.506</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K14">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L14">
+        <v>0.471</v>
+      </c>
+      <c r="M14">
+        <v>0.00537432</v>
+      </c>
+      <c r="N14">
+        <v>0.46562568</v>
+      </c>
+      <c r="O14">
+        <v>0.1117501632</v>
+      </c>
+      <c r="P14">
+        <v>0.3538755168</v>
+      </c>
+      <c r="Q14">
+        <v>0.5698755168</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.2849282336710642</v>
+      </c>
+      <c r="T14">
+        <v>0.9243885052840164</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.24</v>
+      </c>
+      <c r="W14">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>87.63899432858481</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.2543287679559965</v>
+      </c>
+      <c r="C15">
+        <v>1.009430508457222</v>
+      </c>
+      <c r="D15">
+        <v>1.069830508457222</v>
+      </c>
+      <c r="E15">
+        <v>-0.3466</v>
+      </c>
+      <c r="F15">
+        <v>0.1274</v>
+      </c>
+      <c r="G15">
+        <v>0.067</v>
+      </c>
+      <c r="H15">
+        <v>0.506</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K15">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L15">
+        <v>0.471</v>
+      </c>
+      <c r="M15">
+        <v>0.005822180000000001</v>
+      </c>
+      <c r="N15">
+        <v>0.46517782</v>
+      </c>
+      <c r="O15">
+        <v>0.1116426768</v>
+      </c>
+      <c r="P15">
+        <v>0.3535351432</v>
+      </c>
+      <c r="Q15">
+        <v>0.5695351432</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.2871420781103408</v>
+      </c>
+      <c r="T15">
+        <v>0.932703083102379</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.24</v>
+      </c>
+      <c r="W15">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>80.89753322638596</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.2537528502814564</v>
+      </c>
+      <c r="C16">
+        <v>1.002496877978612</v>
+      </c>
+      <c r="D16">
+        <v>1.072696877978612</v>
+      </c>
+      <c r="E16">
+        <v>-0.3368</v>
+      </c>
+      <c r="F16">
+        <v>0.1372</v>
+      </c>
+      <c r="G16">
+        <v>0.067</v>
+      </c>
+      <c r="H16">
+        <v>0.506</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K16">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L16">
+        <v>0.471</v>
+      </c>
+      <c r="M16">
+        <v>0.006270040000000001</v>
+      </c>
+      <c r="N16">
+        <v>0.46472996</v>
+      </c>
+      <c r="O16">
+        <v>0.1115351904</v>
+      </c>
+      <c r="P16">
+        <v>0.3531947696</v>
+      </c>
+      <c r="Q16">
+        <v>0.5691947696000001</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.2894074073040191</v>
+      </c>
+      <c r="T16">
+        <v>0.9412110231955871</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.24</v>
+      </c>
+      <c r="W16">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>75.11913799592983</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.2531769326069164</v>
+      </c>
+      <c r="C17">
+        <v>0.9955786483441977</v>
+      </c>
+      <c r="D17">
+        <v>1.075578648344198</v>
+      </c>
+      <c r="E17">
+        <v>-0.327</v>
+      </c>
+      <c r="F17">
+        <v>0.147</v>
+      </c>
+      <c r="G17">
+        <v>0.067</v>
+      </c>
+      <c r="H17">
+        <v>0.506</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K17">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L17">
+        <v>0.471</v>
+      </c>
+      <c r="M17">
+        <v>0.006717900000000001</v>
+      </c>
+      <c r="N17">
+        <v>0.4642821</v>
+      </c>
+      <c r="O17">
+        <v>0.111427704</v>
+      </c>
+      <c r="P17">
+        <v>0.352854396</v>
+      </c>
+      <c r="Q17">
+        <v>0.5688543960000001</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.2917260383610781</v>
+      </c>
+      <c r="T17">
+        <v>0.9499191501145179</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0.24</v>
+      </c>
+      <c r="W17">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>70.11119546286785</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.2526010149323764</v>
+      </c>
+      <c r="C18">
+        <v>0.9886759440101478</v>
+      </c>
+      <c r="D18">
+        <v>1.078475944010148</v>
+      </c>
+      <c r="E18">
+        <v>-0.3172</v>
+      </c>
+      <c r="F18">
+        <v>0.1568</v>
+      </c>
+      <c r="G18">
+        <v>0.067</v>
+      </c>
+      <c r="H18">
+        <v>0.506</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K18">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L18">
+        <v>0.471</v>
+      </c>
+      <c r="M18">
+        <v>0.00716576</v>
+      </c>
+      <c r="N18">
+        <v>0.46383424</v>
+      </c>
+      <c r="O18">
+        <v>0.1113202176</v>
+      </c>
+      <c r="P18">
+        <v>0.3525140224</v>
+      </c>
+      <c r="Q18">
+        <v>0.5685140224</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.2940998749194957</v>
+      </c>
+      <c r="T18">
+        <v>0.9588346133886614</v>
+      </c>
+      <c r="U18">
+        <v>0.0457</v>
+      </c>
+      <c r="V18">
+        <v>0.24</v>
+      </c>
+      <c r="W18">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>65.72924574643861</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.2520250972578363</v>
+      </c>
+      <c r="C19">
+        <v>0.9817888907772473</v>
+      </c>
+      <c r="D19">
+        <v>1.081388890777247</v>
+      </c>
+      <c r="E19">
+        <v>-0.3074</v>
+      </c>
+      <c r="F19">
+        <v>0.1666</v>
+      </c>
+      <c r="G19">
+        <v>0.067</v>
+      </c>
+      <c r="H19">
+        <v>0.506</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K19">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L19">
+        <v>0.471</v>
+      </c>
+      <c r="M19">
+        <v>0.007613620000000001</v>
+      </c>
+      <c r="N19">
+        <v>0.46338638</v>
+      </c>
+      <c r="O19">
+        <v>0.1112127312</v>
+      </c>
+      <c r="P19">
+        <v>0.3521736488</v>
+      </c>
+      <c r="Q19">
+        <v>0.5681736488000001</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.296530912358839</v>
+      </c>
+      <c r="T19">
+        <v>0.9679649071031455</v>
+      </c>
+      <c r="U19">
+        <v>0.0457</v>
+      </c>
+      <c r="V19">
+        <v>0.24</v>
+      </c>
+      <c r="W19">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>61.86281952605987</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.2514491795832963</v>
+      </c>
+      <c r="C20">
+        <v>0.9749176158091065</v>
+      </c>
+      <c r="D20">
+        <v>1.084317615809107</v>
+      </c>
+      <c r="E20">
+        <v>-0.2976</v>
+      </c>
+      <c r="F20">
+        <v>0.1764</v>
+      </c>
+      <c r="G20">
+        <v>0.067</v>
+      </c>
+      <c r="H20">
+        <v>0.506</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K20">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L20">
+        <v>0.471</v>
+      </c>
+      <c r="M20">
+        <v>0.008061480000000001</v>
+      </c>
+      <c r="N20">
+        <v>0.46293852</v>
+      </c>
+      <c r="O20">
+        <v>0.1111052448</v>
+      </c>
+      <c r="P20">
+        <v>0.3518332752</v>
+      </c>
+      <c r="Q20">
+        <v>0.5678332752</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.2990212433942637</v>
+      </c>
+      <c r="T20">
+        <v>0.9773178909082267</v>
+      </c>
+      <c r="U20">
+        <v>0.0457</v>
+      </c>
+      <c r="V20">
+        <v>0.24</v>
+      </c>
+      <c r="W20">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>58.42599621905654</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.2508732619087562</v>
+      </c>
+      <c r="C21">
+        <v>0.9680622476506645</v>
+      </c>
+      <c r="D21">
+        <v>1.087262247650665</v>
+      </c>
+      <c r="E21">
+        <v>-0.2877999999999999</v>
+      </c>
+      <c r="F21">
+        <v>0.1862</v>
+      </c>
+      <c r="G21">
+        <v>0.067</v>
+      </c>
+      <c r="H21">
+        <v>0.506</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K21">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L21">
+        <v>0.471</v>
+      </c>
+      <c r="M21">
+        <v>0.008509340000000001</v>
+      </c>
+      <c r="N21">
+        <v>0.46249066</v>
+      </c>
+      <c r="O21">
+        <v>0.1109977584</v>
+      </c>
+      <c r="P21">
+        <v>0.3514929016</v>
+      </c>
+      <c r="Q21">
+        <v>0.5674929016000001</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.3015730640848842</v>
+      </c>
+      <c r="T21">
+        <v>0.9869018125850385</v>
+      </c>
+      <c r="U21">
+        <v>0.0457</v>
+      </c>
+      <c r="V21">
+        <v>0.24</v>
+      </c>
+      <c r="W21">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>55.35094378647462</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.2502973442342162</v>
+      </c>
+      <c r="C22">
+        <v>0.9612229162469976</v>
+      </c>
+      <c r="D22">
+        <v>1.090222916246998</v>
+      </c>
+      <c r="E22">
+        <v>-0.278</v>
+      </c>
+      <c r="F22">
+        <v>0.196</v>
+      </c>
+      <c r="G22">
+        <v>0.067</v>
+      </c>
+      <c r="H22">
+        <v>0.506</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K22">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L22">
+        <v>0.471</v>
+      </c>
+      <c r="M22">
+        <v>0.008957200000000002</v>
+      </c>
+      <c r="N22">
+        <v>0.4620428</v>
+      </c>
+      <c r="O22">
+        <v>0.110890272</v>
+      </c>
+      <c r="P22">
+        <v>0.351152528</v>
+      </c>
+      <c r="Q22">
+        <v>0.567152528</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.3041886802927702</v>
+      </c>
+      <c r="T22">
+        <v>0.9967253323037706</v>
+      </c>
+      <c r="U22">
+        <v>0.0457</v>
+      </c>
+      <c r="V22">
+        <v>0.24</v>
+      </c>
+      <c r="W22">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>52.58339659715088</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.2497214265596762</v>
+      </c>
+      <c r="C23">
+        <v>0.9543997529624346</v>
+      </c>
+      <c r="D23">
+        <v>1.093199752962435</v>
+      </c>
+      <c r="E23">
+        <v>-0.2682</v>
+      </c>
+      <c r="F23">
+        <v>0.2058</v>
+      </c>
+      <c r="G23">
+        <v>0.067</v>
+      </c>
+      <c r="H23">
+        <v>0.506</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K23">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L23">
+        <v>0.471</v>
+      </c>
+      <c r="M23">
+        <v>0.00940506</v>
+      </c>
+      <c r="N23">
+        <v>0.46159494</v>
+      </c>
+      <c r="O23">
+        <v>0.1107827856</v>
+      </c>
+      <c r="P23">
+        <v>0.3508121544</v>
+      </c>
+      <c r="Q23">
+        <v>0.5668121544</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.3068705146325015</v>
+      </c>
+      <c r="T23">
+        <v>1.006797548724243</v>
+      </c>
+      <c r="U23">
+        <v>0.0457</v>
+      </c>
+      <c r="V23">
+        <v>0.24</v>
+      </c>
+      <c r="W23">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>50.0794253306199</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.2491455088851362</v>
+      </c>
+      <c r="C24">
+        <v>0.9475928905999853</v>
+      </c>
+      <c r="D24">
+        <v>1.096192890599985</v>
+      </c>
+      <c r="E24">
+        <v>-0.2584</v>
+      </c>
+      <c r="F24">
+        <v>0.2156</v>
+      </c>
+      <c r="G24">
+        <v>0.067</v>
+      </c>
+      <c r="H24">
+        <v>0.506</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K24">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L24">
+        <v>0.471</v>
+      </c>
+      <c r="M24">
+        <v>0.009852920000000001</v>
+      </c>
+      <c r="N24">
+        <v>0.46114708</v>
+      </c>
+      <c r="O24">
+        <v>0.1106752992</v>
+      </c>
+      <c r="P24">
+        <v>0.3504717808</v>
+      </c>
+      <c r="Q24">
+        <v>0.5664717808</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.3096211139553028</v>
+      </c>
+      <c r="T24">
+        <v>1.017128027104214</v>
+      </c>
+      <c r="U24">
+        <v>0.0457</v>
+      </c>
+      <c r="V24">
+        <v>0.24</v>
+      </c>
+      <c r="W24">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>47.80308781559172</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.2485695912105961</v>
+      </c>
+      <c r="C25">
+        <v>0.9408024634210903</v>
+      </c>
+      <c r="D25">
+        <v>1.09920246342109</v>
+      </c>
+      <c r="E25">
+        <v>-0.2486</v>
+      </c>
+      <c r="F25">
+        <v>0.2254</v>
+      </c>
+      <c r="G25">
+        <v>0.067</v>
+      </c>
+      <c r="H25">
+        <v>0.506</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K25">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L25">
+        <v>0.471</v>
+      </c>
+      <c r="M25">
+        <v>0.01030078</v>
+      </c>
+      <c r="N25">
+        <v>0.46069922</v>
+      </c>
+      <c r="O25">
+        <v>0.1105678128</v>
+      </c>
+      <c r="P25">
+        <v>0.3501314072</v>
+      </c>
+      <c r="Q25">
+        <v>0.5661314072000001</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.3124431574163586</v>
+      </c>
+      <c r="T25">
+        <v>1.027726829597951</v>
+      </c>
+      <c r="U25">
+        <v>0.0457</v>
+      </c>
+      <c r="V25">
+        <v>0.24</v>
+      </c>
+      <c r="W25">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>45.72469269317467</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.2479936735360561</v>
+      </c>
+      <c r="C26">
+        <v>0.9340286071656957</v>
+      </c>
+      <c r="D26">
+        <v>1.102228607165696</v>
+      </c>
+      <c r="E26">
+        <v>-0.2388</v>
+      </c>
+      <c r="F26">
+        <v>0.2352</v>
+      </c>
+      <c r="G26">
+        <v>0.067</v>
+      </c>
+      <c r="H26">
+        <v>0.506</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K26">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L26">
+        <v>0.471</v>
+      </c>
+      <c r="M26">
+        <v>0.01074864</v>
+      </c>
+      <c r="N26">
+        <v>0.46025136</v>
+      </c>
+      <c r="O26">
+        <v>0.1104603264</v>
+      </c>
+      <c r="P26">
+        <v>0.3497910336</v>
+      </c>
+      <c r="Q26">
+        <v>0.5657910336</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.3153394651790211</v>
+      </c>
+      <c r="T26">
+        <v>1.038604547946786</v>
+      </c>
+      <c r="U26">
+        <v>0.0457</v>
+      </c>
+      <c r="V26">
+        <v>0.24</v>
+      </c>
+      <c r="W26">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>43.81949716429241</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.247417755861516</v>
+      </c>
+      <c r="C27">
+        <v>0.9272714590726624</v>
+      </c>
+      <c r="D27">
+        <v>1.105271459072662</v>
+      </c>
+      <c r="E27">
+        <v>-0.229</v>
+      </c>
+      <c r="F27">
+        <v>0.245</v>
+      </c>
+      <c r="G27">
+        <v>0.067</v>
+      </c>
+      <c r="H27">
+        <v>0.506</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K27">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L27">
+        <v>0.471</v>
+      </c>
+      <c r="M27">
+        <v>0.0111965</v>
+      </c>
+      <c r="N27">
+        <v>0.4598035</v>
+      </c>
+      <c r="O27">
+        <v>0.11035284</v>
+      </c>
+      <c r="P27">
+        <v>0.34945066</v>
+      </c>
+      <c r="Q27">
+        <v>0.56545066</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.3183130078153547</v>
+      </c>
+      <c r="T27">
+        <v>1.049772338784924</v>
+      </c>
+      <c r="U27">
+        <v>0.0457</v>
+      </c>
+      <c r="V27">
+        <v>0.24</v>
+      </c>
+      <c r="W27">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>42.06671727772071</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.246841838186976</v>
+      </c>
+      <c r="C28">
+        <v>0.9205311579005134</v>
+      </c>
+      <c r="D28">
+        <v>1.108331157900514</v>
+      </c>
+      <c r="E28">
+        <v>-0.2192</v>
+      </c>
+      <c r="F28">
+        <v>0.2548</v>
+      </c>
+      <c r="G28">
+        <v>0.067</v>
+      </c>
+      <c r="H28">
+        <v>0.506</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K28">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L28">
+        <v>0.471</v>
+      </c>
+      <c r="M28">
+        <v>0.01164436</v>
+      </c>
+      <c r="N28">
+        <v>0.45935564</v>
+      </c>
+      <c r="O28">
+        <v>0.1102453536</v>
+      </c>
+      <c r="P28">
+        <v>0.3491102864</v>
+      </c>
+      <c r="Q28">
+        <v>0.5651102864000001</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.3213669164688864</v>
+      </c>
+      <c r="T28">
+        <v>1.061241961807876</v>
+      </c>
+      <c r="U28">
+        <v>0.0457</v>
+      </c>
+      <c r="V28">
+        <v>0.24</v>
+      </c>
+      <c r="W28">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>40.44876661319298</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.2462659205124359</v>
+      </c>
+      <c r="C29">
+        <v>0.9138078439485247</v>
+      </c>
+      <c r="D29">
+        <v>1.111407843948525</v>
+      </c>
+      <c r="E29">
+        <v>-0.2094</v>
+      </c>
+      <c r="F29">
+        <v>0.2646</v>
+      </c>
+      <c r="G29">
+        <v>0.067</v>
+      </c>
+      <c r="H29">
+        <v>0.506</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K29">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L29">
+        <v>0.471</v>
+      </c>
+      <c r="M29">
+        <v>0.01209222</v>
+      </c>
+      <c r="N29">
+        <v>0.45890778</v>
+      </c>
+      <c r="O29">
+        <v>0.1101378672</v>
+      </c>
+      <c r="P29">
+        <v>0.3487699128</v>
+      </c>
+      <c r="Q29">
+        <v>0.5647699128000001</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.3245044938526519</v>
+      </c>
+      <c r="T29">
+        <v>1.073025821078032</v>
+      </c>
+      <c r="U29">
+        <v>0.0457</v>
+      </c>
+      <c r="V29">
+        <v>0.24</v>
+      </c>
+      <c r="W29">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>38.9506641460377</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.2456900028378958</v>
+      </c>
+      <c r="C30">
+        <v>0.9071016590781706</v>
+      </c>
+      <c r="D30">
+        <v>1.114501659078171</v>
+      </c>
+      <c r="E30">
+        <v>-0.1995999999999999</v>
+      </c>
+      <c r="F30">
+        <v>0.2744</v>
+      </c>
+      <c r="G30">
+        <v>0.067</v>
+      </c>
+      <c r="H30">
+        <v>0.506</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K30">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L30">
+        <v>0.471</v>
+      </c>
+      <c r="M30">
+        <v>0.01254008</v>
+      </c>
+      <c r="N30">
+        <v>0.45845992</v>
+      </c>
+      <c r="O30">
+        <v>0.1100303808</v>
+      </c>
+      <c r="P30">
+        <v>0.3484295392</v>
+      </c>
+      <c r="Q30">
+        <v>0.5644295392000001</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.3277292261637442</v>
+      </c>
+      <c r="T30">
+        <v>1.085137009772359</v>
+      </c>
+      <c r="U30">
+        <v>0.0457</v>
+      </c>
+      <c r="V30">
+        <v>0.24</v>
+      </c>
+      <c r="W30">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>37.55956899796492</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.2451140851633558</v>
+      </c>
+      <c r="C31">
+        <v>0.9004127467349297</v>
+      </c>
+      <c r="D31">
+        <v>1.11761274673493</v>
+      </c>
+      <c r="E31">
+        <v>-0.1898</v>
+      </c>
+      <c r="F31">
+        <v>0.2842</v>
+      </c>
+      <c r="G31">
+        <v>0.067</v>
+      </c>
+      <c r="H31">
+        <v>0.506</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K31">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L31">
+        <v>0.471</v>
+      </c>
+      <c r="M31">
+        <v>0.01298794</v>
+      </c>
+      <c r="N31">
+        <v>0.45801206</v>
+      </c>
+      <c r="O31">
+        <v>0.1099228944</v>
+      </c>
+      <c r="P31">
+        <v>0.3480891656</v>
+      </c>
+      <c r="Q31">
+        <v>0.5640891656000001</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.3310447960047266</v>
+      </c>
+      <c r="T31">
+        <v>1.097589358711597</v>
+      </c>
+      <c r="U31">
+        <v>0.0457</v>
+      </c>
+      <c r="V31">
+        <v>0.24</v>
+      </c>
+      <c r="W31">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>36.26441144631097</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.2445381674888158</v>
+      </c>
+      <c r="C32">
+        <v>0.893741251970454</v>
+      </c>
+      <c r="D32">
+        <v>1.120741251970454</v>
+      </c>
+      <c r="E32">
+        <v>-0.18</v>
+      </c>
+      <c r="F32">
+        <v>0.294</v>
+      </c>
+      <c r="G32">
+        <v>0.067</v>
+      </c>
+      <c r="H32">
+        <v>0.506</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K32">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L32">
+        <v>0.471</v>
+      </c>
+      <c r="M32">
+        <v>0.0134358</v>
+      </c>
+      <c r="N32">
+        <v>0.4575642</v>
+      </c>
+      <c r="O32">
+        <v>0.109815408</v>
+      </c>
+      <c r="P32">
+        <v>0.347748792</v>
+      </c>
+      <c r="Q32">
+        <v>0.5637487920000001</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.334455096412594</v>
+      </c>
+      <c r="T32">
+        <v>1.110397489049098</v>
+      </c>
+      <c r="U32">
+        <v>0.0457</v>
+      </c>
+      <c r="V32">
+        <v>0.24</v>
+      </c>
+      <c r="W32">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>35.05559773143393</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.2439622498142757</v>
+      </c>
+      <c r="C33">
+        <v>0.8870873214651112</v>
+      </c>
+      <c r="D33">
+        <v>1.123887321465111</v>
+      </c>
+      <c r="E33">
+        <v>-0.1702</v>
+      </c>
+      <c r="F33">
+        <v>0.3038</v>
+      </c>
+      <c r="G33">
+        <v>0.067</v>
+      </c>
+      <c r="H33">
+        <v>0.506</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K33">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L33">
+        <v>0.471</v>
+      </c>
+      <c r="M33">
+        <v>0.01388366</v>
+      </c>
+      <c r="N33">
+        <v>0.45711634</v>
+      </c>
+      <c r="O33">
+        <v>0.1097079216</v>
+      </c>
+      <c r="P33">
+        <v>0.3474084184</v>
+      </c>
+      <c r="Q33">
+        <v>0.5634084184000001</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.337964246107646</v>
+      </c>
+      <c r="T33">
+        <v>1.12357686954131</v>
+      </c>
+      <c r="U33">
+        <v>0.0457</v>
+      </c>
+      <c r="V33">
+        <v>0.24</v>
+      </c>
+      <c r="W33">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>33.92477199816186</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.2433863321397357</v>
+      </c>
+      <c r="C34">
+        <v>0.8804511035509112</v>
+      </c>
+      <c r="D34">
+        <v>1.127051103550911</v>
+      </c>
+      <c r="E34">
+        <v>-0.1604</v>
+      </c>
+      <c r="F34">
+        <v>0.3136</v>
+      </c>
+      <c r="G34">
+        <v>0.067</v>
+      </c>
+      <c r="H34">
+        <v>0.506</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K34">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L34">
+        <v>0.471</v>
+      </c>
+      <c r="M34">
+        <v>0.01433152</v>
+      </c>
+      <c r="N34">
+        <v>0.45666848</v>
+      </c>
+      <c r="O34">
+        <v>0.1096004352</v>
+      </c>
+      <c r="P34">
+        <v>0.3470680448</v>
+      </c>
+      <c r="Q34">
+        <v>0.5630680448000001</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.3415766060878466</v>
+      </c>
+      <c r="T34">
+        <v>1.137143878871529</v>
+      </c>
+      <c r="U34">
+        <v>0.0457</v>
+      </c>
+      <c r="V34">
+        <v>0.24</v>
+      </c>
+      <c r="W34">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>32.8646228732193</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.2428104144651957</v>
+      </c>
+      <c r="C35">
+        <v>0.8738327482348177</v>
+      </c>
+      <c r="D35">
+        <v>1.130232748234818</v>
+      </c>
+      <c r="E35">
+        <v>-0.1506</v>
+      </c>
+      <c r="F35">
+        <v>0.3234</v>
+      </c>
+      <c r="G35">
+        <v>0.067</v>
+      </c>
+      <c r="H35">
+        <v>0.506</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K35">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L35">
+        <v>0.471</v>
+      </c>
+      <c r="M35">
+        <v>0.01477938</v>
+      </c>
+      <c r="N35">
+        <v>0.45622062</v>
+      </c>
+      <c r="O35">
+        <v>0.1094929488</v>
+      </c>
+      <c r="P35">
+        <v>0.3467276712</v>
+      </c>
+      <c r="Q35">
+        <v>0.5627276712</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.3452967977092473</v>
+      </c>
+      <c r="T35">
+        <v>1.151115873554888</v>
+      </c>
+      <c r="U35">
+        <v>0.0457</v>
+      </c>
+      <c r="V35">
+        <v>0.24</v>
+      </c>
+      <c r="W35">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>31.86872521039448</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.2422344967906556</v>
+      </c>
+      <c r="C36">
+        <v>0.8672324072224586</v>
+      </c>
+      <c r="D36">
+        <v>1.133432407222459</v>
+      </c>
+      <c r="E36">
+        <v>-0.1408</v>
+      </c>
+      <c r="F36">
+        <v>0.3332</v>
+      </c>
+      <c r="G36">
+        <v>0.067</v>
+      </c>
+      <c r="H36">
+        <v>0.506</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K36">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L36">
+        <v>0.471</v>
+      </c>
+      <c r="M36">
+        <v>0.01522724</v>
+      </c>
+      <c r="N36">
+        <v>0.45577276</v>
+      </c>
+      <c r="O36">
+        <v>0.1093854624</v>
+      </c>
+      <c r="P36">
+        <v>0.3463872976</v>
+      </c>
+      <c r="Q36">
+        <v>0.5623872976000001</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.3491297224100843</v>
+      </c>
+      <c r="T36">
+        <v>1.16551126201653</v>
+      </c>
+      <c r="U36">
+        <v>0.0457</v>
+      </c>
+      <c r="V36">
+        <v>0.24</v>
+      </c>
+      <c r="W36">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>30.93140976302994</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.2416585791161156</v>
+      </c>
+      <c r="C37">
+        <v>0.8606502339422359</v>
+      </c>
+      <c r="D37">
+        <v>1.136650233942236</v>
+      </c>
+      <c r="E37">
+        <v>-0.1309999999999999</v>
+      </c>
+      <c r="F37">
+        <v>0.343</v>
+      </c>
+      <c r="G37">
+        <v>0.067</v>
+      </c>
+      <c r="H37">
+        <v>0.506</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K37">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L37">
+        <v>0.471</v>
+      </c>
+      <c r="M37">
+        <v>0.0156751</v>
+      </c>
+      <c r="N37">
+        <v>0.4553249</v>
+      </c>
+      <c r="O37">
+        <v>0.109277976</v>
+      </c>
+      <c r="P37">
+        <v>0.346046924</v>
+      </c>
+      <c r="Q37">
+        <v>0.5620469240000001</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.3530805832555625</v>
+      </c>
+      <c r="T37">
+        <v>1.180349585507762</v>
+      </c>
+      <c r="U37">
+        <v>0.0457</v>
+      </c>
+      <c r="V37">
+        <v>0.24</v>
+      </c>
+      <c r="W37">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>30.04765519837193</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.2410826614415756</v>
+      </c>
+      <c r="C38">
+        <v>0.854086383569852</v>
+      </c>
+      <c r="D38">
+        <v>1.139886383569852</v>
+      </c>
+      <c r="E38">
+        <v>-0.1212</v>
+      </c>
+      <c r="F38">
+        <v>0.3528</v>
+      </c>
+      <c r="G38">
+        <v>0.067</v>
+      </c>
+      <c r="H38">
+        <v>0.506</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K38">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L38">
+        <v>0.471</v>
+      </c>
+      <c r="M38">
+        <v>0.01612296</v>
+      </c>
+      <c r="N38">
+        <v>0.45487704</v>
+      </c>
+      <c r="O38">
+        <v>0.1091704896</v>
+      </c>
+      <c r="P38">
+        <v>0.3457065504</v>
+      </c>
+      <c r="Q38">
+        <v>0.5617065504000001</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.3571549085024618</v>
+      </c>
+      <c r="T38">
+        <v>1.195651606608095</v>
+      </c>
+      <c r="U38">
+        <v>0.0457</v>
+      </c>
+      <c r="V38">
+        <v>0.24</v>
+      </c>
+      <c r="W38">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>29.21299810952827</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.2405067437670355</v>
+      </c>
+      <c r="C39">
+        <v>0.847541013053255</v>
+      </c>
+      <c r="D39">
+        <v>1.143141013053255</v>
+      </c>
+      <c r="E39">
+        <v>-0.1114</v>
+      </c>
+      <c r="F39">
+        <v>0.3626</v>
+      </c>
+      <c r="G39">
+        <v>0.067</v>
+      </c>
+      <c r="H39">
+        <v>0.506</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K39">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L39">
+        <v>0.471</v>
+      </c>
+      <c r="M39">
+        <v>0.01657082</v>
+      </c>
+      <c r="N39">
+        <v>0.45442918</v>
+      </c>
+      <c r="O39">
+        <v>0.1090630032</v>
+      </c>
+      <c r="P39">
+        <v>0.3453661768</v>
+      </c>
+      <c r="Q39">
+        <v>0.5613661768</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.3613585774079929</v>
+      </c>
+      <c r="T39">
+        <v>1.211439406156057</v>
+      </c>
+      <c r="U39">
+        <v>0.0457</v>
+      </c>
+      <c r="V39">
+        <v>0.24</v>
+      </c>
+      <c r="W39">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>28.42345762008156</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2399308260924955</v>
+      </c>
+      <c r="C40">
+        <v>0.8410142811380101</v>
+      </c>
+      <c r="D40">
+        <v>1.14641428113801</v>
+      </c>
+      <c r="E40">
+        <v>-0.1016</v>
+      </c>
+      <c r="F40">
+        <v>0.3724</v>
+      </c>
+      <c r="G40">
+        <v>0.067</v>
+      </c>
+      <c r="H40">
+        <v>0.506</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K40">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L40">
+        <v>0.471</v>
+      </c>
+      <c r="M40">
+        <v>0.01701868</v>
+      </c>
+      <c r="N40">
+        <v>0.45398132</v>
+      </c>
+      <c r="O40">
+        <v>0.1089555168</v>
+      </c>
+      <c r="P40">
+        <v>0.3450258032</v>
+      </c>
+      <c r="Q40">
+        <v>0.5610258032000001</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.365697848536283</v>
+      </c>
+      <c r="T40">
+        <v>1.227736489560405</v>
+      </c>
+      <c r="U40">
+        <v>0.0457</v>
+      </c>
+      <c r="V40">
+        <v>0.24</v>
+      </c>
+      <c r="W40">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>27.67547189323731</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2393549084179554</v>
+      </c>
+      <c r="C41">
+        <v>0.8345063483931111</v>
+      </c>
+      <c r="D41">
+        <v>1.149706348393111</v>
+      </c>
+      <c r="E41">
+        <v>-0.09179999999999999</v>
+      </c>
+      <c r="F41">
+        <v>0.3822</v>
+      </c>
+      <c r="G41">
+        <v>0.067</v>
+      </c>
+      <c r="H41">
+        <v>0.506</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K41">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L41">
+        <v>0.471</v>
+      </c>
+      <c r="M41">
+        <v>0.01746654</v>
+      </c>
+      <c r="N41">
+        <v>0.4535334599999999</v>
+      </c>
+      <c r="O41">
+        <v>0.1088480304</v>
+      </c>
+      <c r="P41">
+        <v>0.3446854296</v>
+      </c>
+      <c r="Q41">
+        <v>0.5606854296000001</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.3701793908491073</v>
+      </c>
+      <c r="T41">
+        <v>1.244567903568174</v>
+      </c>
+      <c r="U41">
+        <v>0.0457</v>
+      </c>
+      <c r="V41">
+        <v>0.24</v>
+      </c>
+      <c r="W41">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>26.96584440879532</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2387789907434154</v>
+      </c>
+      <c r="C42">
+        <v>0.828017377237236</v>
+      </c>
+      <c r="D42">
+        <v>1.153017377237236</v>
+      </c>
+      <c r="E42">
+        <v>-0.08199999999999996</v>
+      </c>
+      <c r="F42">
+        <v>0.392</v>
+      </c>
+      <c r="G42">
+        <v>0.067</v>
+      </c>
+      <c r="H42">
+        <v>0.506</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K42">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L42">
+        <v>0.471</v>
+      </c>
+      <c r="M42">
+        <v>0.0179144</v>
+      </c>
+      <c r="N42">
+        <v>0.4530856</v>
+      </c>
+      <c r="O42">
+        <v>0.108740544</v>
+      </c>
+      <c r="P42">
+        <v>0.344345056</v>
+      </c>
+      <c r="Q42">
+        <v>0.5603450560000001</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.3748103179056924</v>
+      </c>
+      <c r="T42">
+        <v>1.261960364709536</v>
+      </c>
+      <c r="U42">
+        <v>0.0457</v>
+      </c>
+      <c r="V42">
+        <v>0.24</v>
+      </c>
+      <c r="W42">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>26.29169829857544</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2382030730688753</v>
+      </c>
+      <c r="C43">
+        <v>0.8215475319654607</v>
+      </c>
+      <c r="D43">
+        <v>1.156347531965461</v>
+      </c>
+      <c r="E43">
+        <v>-0.07219999999999993</v>
+      </c>
+      <c r="F43">
+        <v>0.4018</v>
+      </c>
+      <c r="G43">
+        <v>0.067</v>
+      </c>
+      <c r="H43">
+        <v>0.506</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K43">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L43">
+        <v>0.471</v>
+      </c>
+      <c r="M43">
+        <v>0.01836226000000001</v>
+      </c>
+      <c r="N43">
+        <v>0.45263774</v>
+      </c>
+      <c r="O43">
+        <v>0.1086330576</v>
+      </c>
+      <c r="P43">
+        <v>0.3440046824</v>
+      </c>
+      <c r="Q43">
+        <v>0.5600046824</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.3795982255404666</v>
+      </c>
+      <c r="T43">
+        <v>1.279942400804842</v>
+      </c>
+      <c r="U43">
+        <v>0.0457</v>
+      </c>
+      <c r="V43">
+        <v>0.24</v>
+      </c>
+      <c r="W43">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>25.65043736446384</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2376271553943353</v>
+      </c>
+      <c r="C44">
+        <v>0.8150969787764295</v>
+      </c>
+      <c r="D44">
+        <v>1.15969697877643</v>
+      </c>
+      <c r="E44">
+        <v>-0.06240000000000001</v>
+      </c>
+      <c r="F44">
+        <v>0.4116</v>
+      </c>
+      <c r="G44">
+        <v>0.067</v>
+      </c>
+      <c r="H44">
+        <v>0.506</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K44">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L44">
+        <v>0.471</v>
+      </c>
+      <c r="M44">
+        <v>0.01881012</v>
+      </c>
+      <c r="N44">
+        <v>0.45218988</v>
+      </c>
+      <c r="O44">
+        <v>0.1085255712</v>
+      </c>
+      <c r="P44">
+        <v>0.3436643088</v>
+      </c>
+      <c r="Q44">
+        <v>0.5596643088000001</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.3845512334385091</v>
+      </c>
+      <c r="T44">
+        <v>1.298544507110331</v>
+      </c>
+      <c r="U44">
+        <v>0.0457</v>
+      </c>
+      <c r="V44">
+        <v>0.24</v>
+      </c>
+      <c r="W44">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>25.03971266530995</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2370512377197953</v>
+      </c>
+      <c r="C45">
+        <v>0.8086658858000115</v>
+      </c>
+      <c r="D45">
+        <v>1.163065885800012</v>
+      </c>
+      <c r="E45">
+        <v>-0.05259999999999998</v>
+      </c>
+      <c r="F45">
+        <v>0.4214</v>
+      </c>
+      <c r="G45">
+        <v>0.067</v>
+      </c>
+      <c r="H45">
+        <v>0.506</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K45">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L45">
+        <v>0.471</v>
+      </c>
+      <c r="M45">
+        <v>0.01925798</v>
+      </c>
+      <c r="N45">
+        <v>0.45174202</v>
+      </c>
+      <c r="O45">
+        <v>0.1084180848</v>
+      </c>
+      <c r="P45">
+        <v>0.3433239352</v>
+      </c>
+      <c r="Q45">
+        <v>0.5593239352000001</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.3896780310873601</v>
+      </c>
+      <c r="T45">
+        <v>1.317799318900223</v>
+      </c>
+      <c r="U45">
+        <v>0.0457</v>
+      </c>
+      <c r="V45">
+        <v>0.24</v>
+      </c>
+      <c r="W45">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>24.45739376611669</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2364753200452553</v>
+      </c>
+      <c r="C46">
+        <v>0.8022544231254267</v>
+      </c>
+      <c r="D46">
+        <v>1.166454423125427</v>
+      </c>
+      <c r="E46">
+        <v>-0.0428</v>
+      </c>
+      <c r="F46">
+        <v>0.4312</v>
+      </c>
+      <c r="G46">
+        <v>0.067</v>
+      </c>
+      <c r="H46">
+        <v>0.506</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K46">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L46">
+        <v>0.471</v>
+      </c>
+      <c r="M46">
+        <v>0.01970584</v>
+      </c>
+      <c r="N46">
+        <v>0.45129416</v>
+      </c>
+      <c r="O46">
+        <v>0.1083105984</v>
+      </c>
+      <c r="P46">
+        <v>0.3429835616</v>
+      </c>
+      <c r="Q46">
+        <v>0.5589835616000001</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.3949879286522415</v>
+      </c>
+      <c r="T46">
+        <v>1.337741802539754</v>
+      </c>
+      <c r="U46">
+        <v>0.0457</v>
+      </c>
+      <c r="V46">
+        <v>0.24</v>
+      </c>
+      <c r="W46">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>23.90154390779586</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2358994023707152</v>
+      </c>
+      <c r="C47">
+        <v>0.795862762829876</v>
+      </c>
+      <c r="D47">
+        <v>1.169862762829876</v>
+      </c>
+      <c r="E47">
+        <v>-0.03299999999999997</v>
+      </c>
+      <c r="F47">
+        <v>0.441</v>
+      </c>
+      <c r="G47">
+        <v>0.067</v>
+      </c>
+      <c r="H47">
+        <v>0.506</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K47">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L47">
+        <v>0.471</v>
+      </c>
+      <c r="M47">
+        <v>0.0201537</v>
+      </c>
+      <c r="N47">
+        <v>0.4508463</v>
+      </c>
+      <c r="O47">
+        <v>0.108203112</v>
+      </c>
+      <c r="P47">
+        <v>0.342643188</v>
+      </c>
+      <c r="Q47">
+        <v>0.558643188</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.4004909134013003</v>
+      </c>
+      <c r="T47">
+        <v>1.358409467402542</v>
+      </c>
+      <c r="U47">
+        <v>0.0457</v>
+      </c>
+      <c r="V47">
+        <v>0.24</v>
+      </c>
+      <c r="W47">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>23.37039848762262</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2353234846961752</v>
+      </c>
+      <c r="C48">
+        <v>0.7894910790076681</v>
+      </c>
+      <c r="D48">
+        <v>1.173291079007668</v>
+      </c>
+      <c r="E48">
+        <v>-0.02319999999999994</v>
+      </c>
+      <c r="F48">
+        <v>0.4508</v>
+      </c>
+      <c r="G48">
+        <v>0.067</v>
+      </c>
+      <c r="H48">
+        <v>0.506</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K48">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L48">
+        <v>0.471</v>
+      </c>
+      <c r="M48">
+        <v>0.02060156</v>
+      </c>
+      <c r="N48">
+        <v>0.45039844</v>
+      </c>
+      <c r="O48">
+        <v>0.1080956256</v>
+      </c>
+      <c r="P48">
+        <v>0.3423028144</v>
+      </c>
+      <c r="Q48">
+        <v>0.5583028144000001</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.4061977124003244</v>
+      </c>
+      <c r="T48">
+        <v>1.379842601334321</v>
+      </c>
+      <c r="U48">
+        <v>0.0457</v>
+      </c>
+      <c r="V48">
+        <v>0.24</v>
+      </c>
+      <c r="W48">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>22.86234634658734</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2347475670216351</v>
+      </c>
+      <c r="C49">
+        <v>0.7831395477998634</v>
+      </c>
+      <c r="D49">
+        <v>1.176739547799863</v>
+      </c>
+      <c r="E49">
+        <v>-0.01339999999999997</v>
+      </c>
+      <c r="F49">
+        <v>0.4606</v>
+      </c>
+      <c r="G49">
+        <v>0.067</v>
+      </c>
+      <c r="H49">
+        <v>0.506</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K49">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L49">
+        <v>0.471</v>
+      </c>
+      <c r="M49">
+        <v>0.02104942</v>
+      </c>
+      <c r="N49">
+        <v>0.44995058</v>
+      </c>
+      <c r="O49">
+        <v>0.1079881392</v>
+      </c>
+      <c r="P49">
+        <v>0.3419624408</v>
+      </c>
+      <c r="Q49">
+        <v>0.5579624408000001</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.4121198623049719</v>
+      </c>
+      <c r="T49">
+        <v>1.402084532772959</v>
+      </c>
+      <c r="U49">
+        <v>0.0457</v>
+      </c>
+      <c r="V49">
+        <v>0.24</v>
+      </c>
+      <c r="W49">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>22.37591344559612</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2341716493470951</v>
+      </c>
+      <c r="C50">
+        <v>0.7768083474244405</v>
+      </c>
+      <c r="D50">
+        <v>1.18020834742444</v>
+      </c>
+      <c r="E50">
+        <v>-0.003599999999999992</v>
+      </c>
+      <c r="F50">
+        <v>0.4704</v>
+      </c>
+      <c r="G50">
+        <v>0.067</v>
+      </c>
+      <c r="H50">
+        <v>0.506</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K50">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L50">
+        <v>0.471</v>
+      </c>
+      <c r="M50">
+        <v>0.02149728</v>
+      </c>
+      <c r="N50">
+        <v>0.44950272</v>
+      </c>
+      <c r="O50">
+        <v>0.1078806528</v>
+      </c>
+      <c r="P50">
+        <v>0.3416220672</v>
+      </c>
+      <c r="Q50">
+        <v>0.5576220672000001</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.418269787205952</v>
+      </c>
+      <c r="T50">
+        <v>1.425181923113084</v>
+      </c>
+      <c r="U50">
+        <v>0.0457</v>
+      </c>
+      <c r="V50">
+        <v>0.24</v>
+      </c>
+      <c r="W50">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>21.9097485821462</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.233595731672555</v>
+      </c>
+      <c r="C51">
+        <v>0.7704976582069991</v>
+      </c>
+      <c r="D51">
+        <v>1.183697658206999</v>
+      </c>
+      <c r="E51">
+        <v>0.006199999999999983</v>
+      </c>
+      <c r="F51">
+        <v>0.4802</v>
+      </c>
+      <c r="G51">
+        <v>0.067</v>
+      </c>
+      <c r="H51">
+        <v>0.506</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K51">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L51">
+        <v>0.471</v>
+      </c>
+      <c r="M51">
+        <v>0.02194514</v>
+      </c>
+      <c r="N51">
+        <v>0.4490548599999999</v>
+      </c>
+      <c r="O51">
+        <v>0.1077731664</v>
+      </c>
+      <c r="P51">
+        <v>0.3412816935999999</v>
+      </c>
+      <c r="Q51">
+        <v>0.5572816936</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.4246608856324607</v>
+      </c>
+      <c r="T51">
+        <v>1.449185093466546</v>
+      </c>
+      <c r="U51">
+        <v>0.0457</v>
+      </c>
+      <c r="V51">
+        <v>0.24</v>
+      </c>
+      <c r="W51">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>21.46261085597995</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.233019813998015</v>
+      </c>
+      <c r="C52">
+        <v>0.764207662612008</v>
+      </c>
+      <c r="D52">
+        <v>1.187207662612008</v>
+      </c>
+      <c r="E52">
+        <v>0.01600000000000001</v>
+      </c>
+      <c r="F52">
+        <v>0.49</v>
+      </c>
+      <c r="G52">
+        <v>0.067</v>
+      </c>
+      <c r="H52">
+        <v>0.506</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K52">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L52">
+        <v>0.471</v>
+      </c>
+      <c r="M52">
+        <v>0.022393</v>
+      </c>
+      <c r="N52">
+        <v>0.448607</v>
+      </c>
+      <c r="O52">
+        <v>0.10766568</v>
+      </c>
+      <c r="P52">
+        <v>0.34094132</v>
+      </c>
+      <c r="Q52">
+        <v>0.5569413200000001</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.43130762799603</v>
+      </c>
+      <c r="T52">
+        <v>1.474148390634148</v>
+      </c>
+      <c r="U52">
+        <v>0.0457</v>
+      </c>
+      <c r="V52">
+        <v>0.24</v>
+      </c>
+      <c r="W52">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>21.03335863886035</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.232443896323475</v>
+      </c>
+      <c r="C53">
+        <v>0.7579385452746119</v>
+      </c>
+      <c r="D53">
+        <v>1.190738545274612</v>
+      </c>
+      <c r="E53">
+        <v>0.02580000000000005</v>
+      </c>
+      <c r="F53">
+        <v>0.4998</v>
+      </c>
+      <c r="G53">
+        <v>0.067</v>
+      </c>
+      <c r="H53">
+        <v>0.506</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K53">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L53">
+        <v>0.471</v>
+      </c>
+      <c r="M53">
+        <v>0.02284086</v>
+      </c>
+      <c r="N53">
+        <v>0.44815914</v>
+      </c>
+      <c r="O53">
+        <v>0.1075581936</v>
+      </c>
+      <c r="P53">
+        <v>0.3406009463999999</v>
+      </c>
+      <c r="Q53">
+        <v>0.5566009464</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.4382256659662754</v>
+      </c>
+      <c r="T53">
+        <v>1.500130597890223</v>
+      </c>
+      <c r="U53">
+        <v>0.0457</v>
+      </c>
+      <c r="V53">
+        <v>0.24</v>
+      </c>
+      <c r="W53">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>20.62093984201995</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2318679786489349</v>
+      </c>
+      <c r="C54">
+        <v>0.7516904930330057</v>
+      </c>
+      <c r="D54">
+        <v>1.194290493033006</v>
+      </c>
+      <c r="E54">
+        <v>0.03560000000000008</v>
+      </c>
+      <c r="F54">
+        <v>0.5096000000000001</v>
+      </c>
+      <c r="G54">
+        <v>0.067</v>
+      </c>
+      <c r="H54">
+        <v>0.506</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K54">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L54">
+        <v>0.471</v>
+      </c>
+      <c r="M54">
+        <v>0.02328872000000001</v>
+      </c>
+      <c r="N54">
+        <v>0.44771128</v>
+      </c>
+      <c r="O54">
+        <v>0.1074507072</v>
+      </c>
+      <c r="P54">
+        <v>0.3402605728</v>
+      </c>
+      <c r="Q54">
+        <v>0.5562605728000001</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.4454319555186144</v>
+      </c>
+      <c r="T54">
+        <v>1.527195397115301</v>
+      </c>
+      <c r="U54">
+        <v>0.0457</v>
+      </c>
+      <c r="V54">
+        <v>0.24</v>
+      </c>
+      <c r="W54">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>20.22438330659649</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2312920609743948</v>
+      </c>
+      <c r="C55">
+        <v>0.745463694961393</v>
+      </c>
+      <c r="D55">
+        <v>1.197863694961393</v>
+      </c>
+      <c r="E55">
+        <v>0.0454</v>
+      </c>
+      <c r="F55">
+        <v>0.5194</v>
+      </c>
+      <c r="G55">
+        <v>0.067</v>
+      </c>
+      <c r="H55">
+        <v>0.506</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K55">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L55">
+        <v>0.471</v>
+      </c>
+      <c r="M55">
+        <v>0.02373658</v>
+      </c>
+      <c r="N55">
+        <v>0.44726342</v>
+      </c>
+      <c r="O55">
+        <v>0.1073432208</v>
+      </c>
+      <c r="P55">
+        <v>0.3399201992</v>
+      </c>
+      <c r="Q55">
+        <v>0.5559201992</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.4529448956902018</v>
+      </c>
+      <c r="T55">
+        <v>1.555411889924425</v>
+      </c>
+      <c r="U55">
+        <v>0.0457</v>
+      </c>
+      <c r="V55">
+        <v>0.24</v>
+      </c>
+      <c r="W55">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>19.84279116873618</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2307161432998548</v>
+      </c>
+      <c r="C56">
+        <v>0.7392583424035323</v>
+      </c>
+      <c r="D56">
+        <v>1.201458342403532</v>
+      </c>
+      <c r="E56">
+        <v>0.05520000000000003</v>
+      </c>
+      <c r="F56">
+        <v>0.5292</v>
+      </c>
+      <c r="G56">
+        <v>0.067</v>
+      </c>
+      <c r="H56">
+        <v>0.506</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K56">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L56">
+        <v>0.471</v>
+      </c>
+      <c r="M56">
+        <v>0.02418444</v>
+      </c>
+      <c r="N56">
+        <v>0.44681556</v>
+      </c>
+      <c r="O56">
+        <v>0.1072357344</v>
+      </c>
+      <c r="P56">
+        <v>0.3395798256</v>
+      </c>
+      <c r="Q56">
+        <v>0.5555798256000001</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.460784485434467</v>
+      </c>
+      <c r="T56">
+        <v>1.584855186768728</v>
+      </c>
+      <c r="U56">
+        <v>0.0457</v>
+      </c>
+      <c r="V56">
+        <v>0.24</v>
+      </c>
+      <c r="W56">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>19.47533207301885</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2301402256253147</v>
+      </c>
+      <c r="C57">
+        <v>0.733074629006898</v>
+      </c>
+      <c r="D57">
+        <v>1.205074629006898</v>
+      </c>
+      <c r="E57">
+        <v>0.06500000000000006</v>
+      </c>
+      <c r="F57">
+        <v>0.539</v>
+      </c>
+      <c r="G57">
+        <v>0.067</v>
+      </c>
+      <c r="H57">
+        <v>0.506</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K57">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L57">
+        <v>0.471</v>
+      </c>
+      <c r="M57">
+        <v>0.0246323</v>
+      </c>
+      <c r="N57">
+        <v>0.4463677</v>
+      </c>
+      <c r="O57">
+        <v>0.107128248</v>
+      </c>
+      <c r="P57">
+        <v>0.339239452</v>
+      </c>
+      <c r="Q57">
+        <v>0.5552394520000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.4689725013895884</v>
+      </c>
+      <c r="T57">
+        <v>1.61560707458389</v>
+      </c>
+      <c r="U57">
+        <v>0.0457</v>
+      </c>
+      <c r="V57">
+        <v>0.24</v>
+      </c>
+      <c r="W57">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>19.12123512623669</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2295643079507747</v>
+      </c>
+      <c r="C58">
+        <v>0.7269127507574508</v>
+      </c>
+      <c r="D58">
+        <v>1.208712750757451</v>
+      </c>
+      <c r="E58">
+        <v>0.07480000000000009</v>
+      </c>
+      <c r="F58">
+        <v>0.5488000000000001</v>
+      </c>
+      <c r="G58">
+        <v>0.067</v>
+      </c>
+      <c r="H58">
+        <v>0.506</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K58">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L58">
+        <v>0.471</v>
+      </c>
+      <c r="M58">
+        <v>0.02508016</v>
+      </c>
+      <c r="N58">
+        <v>0.44591984</v>
+      </c>
+      <c r="O58">
+        <v>0.1070207616</v>
+      </c>
+      <c r="P58">
+        <v>0.3388990784</v>
+      </c>
+      <c r="Q58">
+        <v>0.5548990784000001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.4775326998881244</v>
+      </c>
+      <c r="T58">
+        <v>1.647756775481558</v>
+      </c>
+      <c r="U58">
+        <v>0.0457</v>
+      </c>
+      <c r="V58">
+        <v>0.24</v>
+      </c>
+      <c r="W58">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>18.77978449898246</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2289883902762347</v>
+      </c>
+      <c r="C59">
+        <v>0.7207729060150457</v>
+      </c>
+      <c r="D59">
+        <v>1.212372906015046</v>
+      </c>
+      <c r="E59">
+        <v>0.08460000000000012</v>
+      </c>
+      <c r="F59">
+        <v>0.5586000000000001</v>
+      </c>
+      <c r="G59">
+        <v>0.067</v>
+      </c>
+      <c r="H59">
+        <v>0.506</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K59">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L59">
+        <v>0.471</v>
+      </c>
+      <c r="M59">
+        <v>0.02552802000000001</v>
+      </c>
+      <c r="N59">
+        <v>0.44547198</v>
+      </c>
+      <c r="O59">
+        <v>0.1069132752</v>
+      </c>
+      <c r="P59">
+        <v>0.3385587048</v>
+      </c>
+      <c r="Q59">
+        <v>0.5545587048</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.4864910471540342</v>
+      </c>
+      <c r="T59">
+        <v>1.6814018113047</v>
+      </c>
+      <c r="U59">
+        <v>0.0457</v>
+      </c>
+      <c r="V59">
+        <v>0.24</v>
+      </c>
+      <c r="W59">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>18.45031459549154</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2284124726016947</v>
+      </c>
+      <c r="C60">
+        <v>0.7146552955494844</v>
+      </c>
+      <c r="D60">
+        <v>1.216055295549484</v>
+      </c>
+      <c r="E60">
+        <v>0.09439999999999993</v>
+      </c>
+      <c r="F60">
+        <v>0.5683999999999999</v>
+      </c>
+      <c r="G60">
+        <v>0.067</v>
+      </c>
+      <c r="H60">
+        <v>0.506</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K60">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L60">
+        <v>0.471</v>
+      </c>
+      <c r="M60">
+        <v>0.02597588</v>
+      </c>
+      <c r="N60">
+        <v>0.44502412</v>
+      </c>
+      <c r="O60">
+        <v>0.1068057888</v>
+      </c>
+      <c r="P60">
+        <v>0.3382183312</v>
+      </c>
+      <c r="Q60">
+        <v>0.5542183312000001</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.4958759823849873</v>
+      </c>
+      <c r="T60">
+        <v>1.716648991690848</v>
+      </c>
+      <c r="U60">
+        <v>0.0457</v>
+      </c>
+      <c r="V60">
+        <v>0.24</v>
+      </c>
+      <c r="W60">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>18.13220572315548</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2278365549271546</v>
+      </c>
+      <c r="C61">
+        <v>0.7085601225772246</v>
+      </c>
+      <c r="D61">
+        <v>1.219760122577225</v>
+      </c>
+      <c r="E61">
+        <v>0.1042</v>
+      </c>
+      <c r="F61">
+        <v>0.5781999999999999</v>
+      </c>
+      <c r="G61">
+        <v>0.067</v>
+      </c>
+      <c r="H61">
+        <v>0.506</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K61">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L61">
+        <v>0.471</v>
+      </c>
+      <c r="M61">
+        <v>0.02642374</v>
+      </c>
+      <c r="N61">
+        <v>0.4445762599999999</v>
+      </c>
+      <c r="O61">
+        <v>0.1066983024</v>
+      </c>
+      <c r="P61">
+        <v>0.3378779575999999</v>
+      </c>
+      <c r="Q61">
+        <v>0.5538779576</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.5057187193345234</v>
+      </c>
+      <c r="T61">
+        <v>1.753615546729979</v>
+      </c>
+      <c r="U61">
+        <v>0.0457</v>
+      </c>
+      <c r="V61">
+        <v>0.24</v>
+      </c>
+      <c r="W61">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>17.82488020242403</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2272606372526146</v>
+      </c>
+      <c r="C62">
+        <v>0.7024875927987632</v>
+      </c>
+      <c r="D62">
+        <v>1.223487592798763</v>
+      </c>
+      <c r="E62">
+        <v>0.114</v>
+      </c>
+      <c r="F62">
+        <v>0.588</v>
+      </c>
+      <c r="G62">
+        <v>0.067</v>
+      </c>
+      <c r="H62">
+        <v>0.506</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K62">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L62">
+        <v>0.471</v>
+      </c>
+      <c r="M62">
+        <v>0.0268716</v>
+      </c>
+      <c r="N62">
+        <v>0.4441284</v>
+      </c>
+      <c r="O62">
+        <v>0.106590816</v>
+      </c>
+      <c r="P62">
+        <v>0.337537584</v>
+      </c>
+      <c r="Q62">
+        <v>0.5535375840000001</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.5160535931315364</v>
+      </c>
+      <c r="T62">
+        <v>1.792430429521066</v>
+      </c>
+      <c r="U62">
+        <v>0.0457</v>
+      </c>
+      <c r="V62">
+        <v>0.24</v>
+      </c>
+      <c r="W62">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>17.52779886571696</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2266847195780745</v>
+      </c>
+      <c r="C63">
+        <v>0.6964379144367102</v>
+      </c>
+      <c r="D63">
+        <v>1.22723791443671</v>
+      </c>
+      <c r="E63">
+        <v>0.1238</v>
+      </c>
+      <c r="F63">
+        <v>0.5978</v>
+      </c>
+      <c r="G63">
+        <v>0.067</v>
+      </c>
+      <c r="H63">
+        <v>0.506</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K63">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L63">
+        <v>0.471</v>
+      </c>
+      <c r="M63">
+        <v>0.02731946</v>
+      </c>
+      <c r="N63">
+        <v>0.44368054</v>
+      </c>
+      <c r="O63">
+        <v>0.1064833296</v>
+      </c>
+      <c r="P63">
+        <v>0.3371972103999999</v>
+      </c>
+      <c r="Q63">
+        <v>0.5531972104</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.5269184604566013</v>
+      </c>
+      <c r="T63">
+        <v>1.833235819121953</v>
+      </c>
+      <c r="U63">
+        <v>0.0457</v>
+      </c>
+      <c r="V63">
+        <v>0.24</v>
+      </c>
+      <c r="W63">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>17.24045790070521</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2261088019035345</v>
+      </c>
+      <c r="C64">
+        <v>0.6904112982745597</v>
+      </c>
+      <c r="D64">
+        <v>1.23101129827456</v>
+      </c>
+      <c r="E64">
+        <v>0.1336000000000001</v>
+      </c>
+      <c r="F64">
+        <v>0.6076</v>
+      </c>
+      <c r="G64">
+        <v>0.067</v>
+      </c>
+      <c r="H64">
+        <v>0.506</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K64">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L64">
+        <v>0.471</v>
+      </c>
+      <c r="M64">
+        <v>0.02776732000000001</v>
+      </c>
+      <c r="N64">
+        <v>0.44323268</v>
+      </c>
+      <c r="O64">
+        <v>0.1063758432</v>
+      </c>
+      <c r="P64">
+        <v>0.3368568368</v>
+      </c>
+      <c r="Q64">
+        <v>0.5528568368000001</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.5383551629040382</v>
+      </c>
+      <c r="T64">
+        <v>1.876188860807098</v>
+      </c>
+      <c r="U64">
+        <v>0.0457</v>
+      </c>
+      <c r="V64">
+        <v>0.24</v>
+      </c>
+      <c r="W64">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>16.96238599908093</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2255328842289944</v>
+      </c>
+      <c r="C65">
+        <v>0.6844079576961826</v>
+      </c>
+      <c r="D65">
+        <v>1.234807957696183</v>
+      </c>
+      <c r="E65">
+        <v>0.1434</v>
+      </c>
+      <c r="F65">
+        <v>0.6173999999999999</v>
+      </c>
+      <c r="G65">
+        <v>0.067</v>
+      </c>
+      <c r="H65">
+        <v>0.506</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K65">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L65">
+        <v>0.471</v>
+      </c>
+      <c r="M65">
+        <v>0.02821518</v>
+      </c>
+      <c r="N65">
+        <v>0.44278482</v>
+      </c>
+      <c r="O65">
+        <v>0.1062683568</v>
+      </c>
+      <c r="P65">
+        <v>0.3365164631999999</v>
+      </c>
+      <c r="Q65">
+        <v>0.5525164632</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.5504100654837687</v>
+      </c>
+      <c r="T65">
+        <v>1.921463688529276</v>
+      </c>
+      <c r="U65">
+        <v>0.0457</v>
+      </c>
+      <c r="V65">
+        <v>0.24</v>
+      </c>
+      <c r="W65">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>16.6931417768733</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2249569665544544</v>
+      </c>
+      <c r="C66">
+        <v>0.6784281087260498</v>
+      </c>
+      <c r="D66">
+        <v>1.23862810872605</v>
+      </c>
+      <c r="E66">
+        <v>0.1532</v>
+      </c>
+      <c r="F66">
+        <v>0.6272</v>
+      </c>
+      <c r="G66">
+        <v>0.067</v>
+      </c>
+      <c r="H66">
+        <v>0.506</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K66">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L66">
+        <v>0.471</v>
+      </c>
+      <c r="M66">
+        <v>0.02866304</v>
+      </c>
+      <c r="N66">
+        <v>0.44233696</v>
+      </c>
+      <c r="O66">
+        <v>0.1061608704</v>
+      </c>
+      <c r="P66">
+        <v>0.3361760896</v>
+      </c>
+      <c r="Q66">
+        <v>0.5521760896000001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.5631346848734844</v>
+      </c>
+      <c r="T66">
+        <v>1.969253784458243</v>
+      </c>
+      <c r="U66">
+        <v>0.0457</v>
+      </c>
+      <c r="V66">
+        <v>0.24</v>
+      </c>
+      <c r="W66">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>16.43231143660965</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2243810488799144</v>
+      </c>
+      <c r="C67">
+        <v>0.6724719700702053</v>
+      </c>
+      <c r="D67">
+        <v>1.242471970070205</v>
+      </c>
+      <c r="E67">
+        <v>0.163</v>
+      </c>
+      <c r="F67">
+        <v>0.637</v>
+      </c>
+      <c r="G67">
+        <v>0.067</v>
+      </c>
+      <c r="H67">
+        <v>0.506</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K67">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L67">
+        <v>0.471</v>
+      </c>
+      <c r="M67">
+        <v>0.0291109</v>
+      </c>
+      <c r="N67">
+        <v>0.4418891</v>
+      </c>
+      <c r="O67">
+        <v>0.106053384</v>
+      </c>
+      <c r="P67">
+        <v>0.335835716</v>
+      </c>
+      <c r="Q67">
+        <v>0.551835716</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.5765864253711841</v>
+      </c>
+      <c r="T67">
+        <v>2.019774743011723</v>
+      </c>
+      <c r="U67">
+        <v>0.0457</v>
+      </c>
+      <c r="V67">
+        <v>0.24</v>
+      </c>
+      <c r="W67">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>16.1795066452772</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2238051312053744</v>
+      </c>
+      <c r="C68">
+        <v>0.6665397631580072</v>
+      </c>
+      <c r="D68">
+        <v>1.246339763158007</v>
+      </c>
+      <c r="E68">
+        <v>0.1728000000000001</v>
+      </c>
+      <c r="F68">
+        <v>0.6468</v>
+      </c>
+      <c r="G68">
+        <v>0.067</v>
+      </c>
+      <c r="H68">
+        <v>0.506</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K68">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L68">
+        <v>0.471</v>
+      </c>
+      <c r="M68">
+        <v>0.02955876</v>
+      </c>
+      <c r="N68">
+        <v>0.44144124</v>
+      </c>
+      <c r="O68">
+        <v>0.1059458976</v>
+      </c>
+      <c r="P68">
+        <v>0.3354953424</v>
+      </c>
+      <c r="Q68">
+        <v>0.5514953424</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.5908294447216893</v>
+      </c>
+      <c r="T68">
+        <v>2.073267522656583</v>
+      </c>
+      <c r="U68">
+        <v>0.0457</v>
+      </c>
+      <c r="V68">
+        <v>0.24</v>
+      </c>
+      <c r="W68">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>15.93436260519724</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2232292135308343</v>
+      </c>
+      <c r="C69">
+        <v>0.6606317121846441</v>
+      </c>
+      <c r="D69">
+        <v>1.250231712184644</v>
+      </c>
+      <c r="E69">
+        <v>0.1826000000000001</v>
+      </c>
+      <c r="F69">
+        <v>0.6566000000000001</v>
+      </c>
+      <c r="G69">
+        <v>0.067</v>
+      </c>
+      <c r="H69">
+        <v>0.506</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K69">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L69">
+        <v>0.471</v>
+      </c>
+      <c r="M69">
+        <v>0.03000662</v>
+      </c>
+      <c r="N69">
+        <v>0.44099338</v>
+      </c>
+      <c r="O69">
+        <v>0.1058384112</v>
+      </c>
+      <c r="P69">
+        <v>0.3351549688</v>
+      </c>
+      <c r="Q69">
+        <v>0.5511549688000001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.6059356773661646</v>
+      </c>
+      <c r="T69">
+        <v>2.130002288946586</v>
+      </c>
+      <c r="U69">
+        <v>0.0457</v>
+      </c>
+      <c r="V69">
+        <v>0.24</v>
+      </c>
+      <c r="W69">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>15.69653629765698</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2226532958562942</v>
+      </c>
+      <c r="C70">
+        <v>0.6547480441544581</v>
+      </c>
+      <c r="D70">
+        <v>1.254148044154458</v>
+      </c>
+      <c r="E70">
+        <v>0.1924</v>
+      </c>
+      <c r="F70">
+        <v>0.6664</v>
+      </c>
+      <c r="G70">
+        <v>0.067</v>
+      </c>
+      <c r="H70">
+        <v>0.506</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K70">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L70">
+        <v>0.471</v>
+      </c>
+      <c r="M70">
+        <v>0.03045448</v>
+      </c>
+      <c r="N70">
+        <v>0.44054552</v>
+      </c>
+      <c r="O70">
+        <v>0.1057309248</v>
+      </c>
+      <c r="P70">
+        <v>0.3348145952</v>
+      </c>
+      <c r="Q70">
+        <v>0.5508145952000001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.6219860495509195</v>
+      </c>
+      <c r="T70">
+        <v>2.190282978129714</v>
+      </c>
+      <c r="U70">
+        <v>0.0457</v>
+      </c>
+      <c r="V70">
+        <v>0.24</v>
+      </c>
+      <c r="W70">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>15.46570488151497</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2220773781817542</v>
+      </c>
+      <c r="C71">
+        <v>0.6488889889250781</v>
+      </c>
+      <c r="D71">
+        <v>1.258088988925078</v>
+      </c>
+      <c r="E71">
+        <v>0.2022</v>
+      </c>
+      <c r="F71">
+        <v>0.6762</v>
+      </c>
+      <c r="G71">
+        <v>0.067</v>
+      </c>
+      <c r="H71">
+        <v>0.506</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K71">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L71">
+        <v>0.471</v>
+      </c>
+      <c r="M71">
+        <v>0.03090234</v>
+      </c>
+      <c r="N71">
+        <v>0.4400976599999999</v>
+      </c>
+      <c r="O71">
+        <v>0.1056234384</v>
+      </c>
+      <c r="P71">
+        <v>0.3344742216</v>
+      </c>
+      <c r="Q71">
+        <v>0.5504742216</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.6390719296185621</v>
+      </c>
+      <c r="T71">
+        <v>2.254452744034336</v>
+      </c>
+      <c r="U71">
+        <v>0.0457</v>
+      </c>
+      <c r="V71">
+        <v>0.24</v>
+      </c>
+      <c r="W71">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>15.24156423105823</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2215014605072141</v>
+      </c>
+      <c r="C72">
+        <v>0.643054779252395</v>
+      </c>
+      <c r="D72">
+        <v>1.262054779252395</v>
+      </c>
+      <c r="E72">
+        <v>0.2120000000000001</v>
+      </c>
+      <c r="F72">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="G72">
+        <v>0.067</v>
+      </c>
+      <c r="H72">
+        <v>0.506</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K72">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L72">
+        <v>0.471</v>
+      </c>
+      <c r="M72">
+        <v>0.03135020000000001</v>
+      </c>
+      <c r="N72">
+        <v>0.4396498</v>
+      </c>
+      <c r="O72">
+        <v>0.105515952</v>
+      </c>
+      <c r="P72">
+        <v>0.334133848</v>
+      </c>
+      <c r="Q72">
+        <v>0.5501338480000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.6572968683573805</v>
+      </c>
+      <c r="T72">
+        <v>2.322900494332597</v>
+      </c>
+      <c r="U72">
+        <v>0.0457</v>
+      </c>
+      <c r="V72">
+        <v>0.24</v>
+      </c>
+      <c r="W72">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>15.02382759918597</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2209255428326742</v>
+      </c>
+      <c r="C73">
+        <v>0.637245650836382</v>
+      </c>
+      <c r="D73">
+        <v>1.266045650836382</v>
+      </c>
+      <c r="E73">
+        <v>0.2218</v>
+      </c>
+      <c r="F73">
+        <v>0.6958</v>
+      </c>
+      <c r="G73">
+        <v>0.067</v>
+      </c>
+      <c r="H73">
+        <v>0.506</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K73">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L73">
+        <v>0.471</v>
+      </c>
+      <c r="M73">
+        <v>0.03179806</v>
+      </c>
+      <c r="N73">
+        <v>0.43920194</v>
+      </c>
+      <c r="O73">
+        <v>0.1054084656</v>
+      </c>
+      <c r="P73">
+        <v>0.3337934744</v>
+      </c>
+      <c r="Q73">
+        <v>0.5497934744</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.6767786994230143</v>
+      </c>
+      <c r="T73">
+        <v>2.396068779134187</v>
+      </c>
+      <c r="U73">
+        <v>0.0457</v>
+      </c>
+      <c r="V73">
+        <v>0.24</v>
+      </c>
+      <c r="W73">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>14.81222439356363</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2203496251581341</v>
+      </c>
+      <c r="C74">
+        <v>0.6314618423677949</v>
+      </c>
+      <c r="D74">
+        <v>1.270061842367795</v>
+      </c>
+      <c r="E74">
+        <v>0.2316</v>
+      </c>
+      <c r="F74">
+        <v>0.7056</v>
+      </c>
+      <c r="G74">
+        <v>0.067</v>
+      </c>
+      <c r="H74">
+        <v>0.506</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K74">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L74">
+        <v>0.471</v>
+      </c>
+      <c r="M74">
+        <v>0.03224592</v>
+      </c>
+      <c r="N74">
+        <v>0.43875408</v>
+      </c>
+      <c r="O74">
+        <v>0.1053009792</v>
+      </c>
+      <c r="P74">
+        <v>0.3334531008</v>
+      </c>
+      <c r="Q74">
+        <v>0.5494531008000001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.6976520898504788</v>
+      </c>
+      <c r="T74">
+        <v>2.474463369993034</v>
+      </c>
+      <c r="U74">
+        <v>0.0457</v>
+      </c>
+      <c r="V74">
+        <v>0.24</v>
+      </c>
+      <c r="W74">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>14.60649905476414</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.219773707483594</v>
+      </c>
+      <c r="C75">
+        <v>0.6257035955757565</v>
+      </c>
+      <c r="D75">
+        <v>1.274103595575756</v>
+      </c>
+      <c r="E75">
+        <v>0.2413999999999999</v>
+      </c>
+      <c r="F75">
+        <v>0.7153999999999999</v>
+      </c>
+      <c r="G75">
+        <v>0.067</v>
+      </c>
+      <c r="H75">
+        <v>0.506</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K75">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L75">
+        <v>0.471</v>
+      </c>
+      <c r="M75">
+        <v>0.03269378</v>
+      </c>
+      <c r="N75">
+        <v>0.43830622</v>
+      </c>
+      <c r="O75">
+        <v>0.1051934928</v>
+      </c>
+      <c r="P75">
+        <v>0.3331127272</v>
+      </c>
+      <c r="Q75">
+        <v>0.5491127272</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.7200716573466446</v>
+      </c>
+      <c r="T75">
+        <v>2.558664967582166</v>
+      </c>
+      <c r="U75">
+        <v>0.0457</v>
+      </c>
+      <c r="V75">
+        <v>0.24</v>
+      </c>
+      <c r="W75">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>14.40641002661668</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.219197789809054</v>
+      </c>
+      <c r="C76">
+        <v>0.6199711552762593</v>
+      </c>
+      <c r="D76">
+        <v>1.278171155276259</v>
+      </c>
+      <c r="E76">
+        <v>0.2512</v>
+      </c>
+      <c r="F76">
+        <v>0.7252</v>
+      </c>
+      <c r="G76">
+        <v>0.067</v>
+      </c>
+      <c r="H76">
+        <v>0.506</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K76">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L76">
+        <v>0.471</v>
+      </c>
+      <c r="M76">
+        <v>0.03314164</v>
+      </c>
+      <c r="N76">
+        <v>0.43785836</v>
+      </c>
+      <c r="O76">
+        <v>0.1050860064</v>
+      </c>
+      <c r="P76">
+        <v>0.3327723536</v>
+      </c>
+      <c r="Q76">
+        <v>0.5487723536000001</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.7442158069578999</v>
+      </c>
+      <c r="T76">
+        <v>2.649343611139693</v>
+      </c>
+      <c r="U76">
+        <v>0.0457</v>
+      </c>
+      <c r="V76">
+        <v>0.24</v>
+      </c>
+      <c r="W76">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>14.21172881004078</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.218621872134514</v>
+      </c>
+      <c r="C77">
+        <v>0.6142647694215965</v>
+      </c>
+      <c r="D77">
+        <v>1.282264769421597</v>
+      </c>
+      <c r="E77">
+        <v>0.261</v>
+      </c>
+      <c r="F77">
+        <v>0.735</v>
+      </c>
+      <c r="G77">
+        <v>0.067</v>
+      </c>
+      <c r="H77">
+        <v>0.506</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K77">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L77">
+        <v>0.471</v>
+      </c>
+      <c r="M77">
+        <v>0.0335895</v>
+      </c>
+      <c r="N77">
+        <v>0.4374105</v>
+      </c>
+      <c r="O77">
+        <v>0.10497852</v>
+      </c>
+      <c r="P77">
+        <v>0.33243198</v>
+      </c>
+      <c r="Q77">
+        <v>0.54843198</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.7702914885380558</v>
+      </c>
+      <c r="T77">
+        <v>2.747276546181822</v>
+      </c>
+      <c r="U77">
+        <v>0.0457</v>
+      </c>
+      <c r="V77">
+        <v>0.24</v>
+      </c>
+      <c r="W77">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>14.02223909257357</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2180459544599739</v>
+      </c>
+      <c r="C78">
+        <v>0.6085846891507461</v>
+      </c>
+      <c r="D78">
+        <v>1.286384689150746</v>
+      </c>
+      <c r="E78">
+        <v>0.2708</v>
+      </c>
+      <c r="F78">
+        <v>0.7448</v>
+      </c>
+      <c r="G78">
+        <v>0.067</v>
+      </c>
+      <c r="H78">
+        <v>0.506</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K78">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L78">
+        <v>0.471</v>
+      </c>
+      <c r="M78">
+        <v>0.03403736</v>
+      </c>
+      <c r="N78">
+        <v>0.43696264</v>
+      </c>
+      <c r="O78">
+        <v>0.1048710336</v>
+      </c>
+      <c r="P78">
+        <v>0.3320916064</v>
+      </c>
+      <c r="Q78">
+        <v>0.5480916064000001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.7985401435832247</v>
+      </c>
+      <c r="T78">
+        <v>2.853370559144128</v>
+      </c>
+      <c r="U78">
+        <v>0.0457</v>
+      </c>
+      <c r="V78">
+        <v>0.24</v>
+      </c>
+      <c r="W78">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>13.83773594661865</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2174700367854339</v>
+      </c>
+      <c r="C79">
+        <v>0.6029311688407307</v>
+      </c>
+      <c r="D79">
+        <v>1.290531168840731</v>
+      </c>
+      <c r="E79">
+        <v>0.2806000000000001</v>
+      </c>
+      <c r="F79">
+        <v>0.7546</v>
+      </c>
+      <c r="G79">
+        <v>0.067</v>
+      </c>
+      <c r="H79">
+        <v>0.506</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K79">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L79">
+        <v>0.471</v>
+      </c>
+      <c r="M79">
+        <v>0.03448522</v>
+      </c>
+      <c r="N79">
+        <v>0.43651478</v>
+      </c>
+      <c r="O79">
+        <v>0.1047635472</v>
+      </c>
+      <c r="P79">
+        <v>0.3317512328</v>
+      </c>
+      <c r="Q79">
+        <v>0.5477512328</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.82924520341493</v>
+      </c>
+      <c r="T79">
+        <v>2.968690138450982</v>
+      </c>
+      <c r="U79">
+        <v>0.0457</v>
+      </c>
+      <c r="V79">
+        <v>0.24</v>
+      </c>
+      <c r="W79">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>13.65802509016906</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2168941191108938</v>
+      </c>
+      <c r="C80">
+        <v>0.597304466158973</v>
+      </c>
+      <c r="D80">
+        <v>1.294704466158973</v>
+      </c>
+      <c r="E80">
+        <v>0.2904</v>
+      </c>
+      <c r="F80">
+        <v>0.7644</v>
+      </c>
+      <c r="G80">
+        <v>0.067</v>
+      </c>
+      <c r="H80">
+        <v>0.506</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K80">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L80">
+        <v>0.471</v>
+      </c>
+      <c r="M80">
+        <v>0.03493308000000001</v>
+      </c>
+      <c r="N80">
+        <v>0.43606692</v>
+      </c>
+      <c r="O80">
+        <v>0.1046560608</v>
+      </c>
+      <c r="P80">
+        <v>0.3314108592</v>
+      </c>
+      <c r="Q80">
+        <v>0.5474108592</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.8627416323222448</v>
+      </c>
+      <c r="T80">
+        <v>3.094493315876642</v>
+      </c>
+      <c r="U80">
+        <v>0.0457</v>
+      </c>
+      <c r="V80">
+        <v>0.24</v>
+      </c>
+      <c r="W80">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>13.48292220439766</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2163182014363538</v>
+      </c>
+      <c r="C81">
+        <v>0.5917048421166697</v>
+      </c>
+      <c r="D81">
+        <v>1.29890484211667</v>
+      </c>
+      <c r="E81">
+        <v>0.3002</v>
+      </c>
+      <c r="F81">
+        <v>0.7742</v>
+      </c>
+      <c r="G81">
+        <v>0.067</v>
+      </c>
+      <c r="H81">
+        <v>0.506</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K81">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L81">
+        <v>0.471</v>
+      </c>
+      <c r="M81">
+        <v>0.03538094000000001</v>
+      </c>
+      <c r="N81">
+        <v>0.4356190599999999</v>
+      </c>
+      <c r="O81">
+        <v>0.1045485744</v>
+      </c>
+      <c r="P81">
+        <v>0.3310704856</v>
+      </c>
+      <c r="Q81">
+        <v>0.5470704856</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.8994281973159706</v>
+      </c>
+      <c r="T81">
+        <v>3.232277748295222</v>
+      </c>
+      <c r="U81">
+        <v>0.0457</v>
+      </c>
+      <c r="V81">
+        <v>0.24</v>
+      </c>
+      <c r="W81">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>13.31225230307617</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2157422837618138</v>
+      </c>
+      <c r="C82">
+        <v>0.5861325611232111</v>
+      </c>
+      <c r="D82">
+        <v>1.303132561123211</v>
+      </c>
+      <c r="E82">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="F82">
+        <v>0.784</v>
+      </c>
+      <c r="G82">
+        <v>0.067</v>
+      </c>
+      <c r="H82">
+        <v>0.506</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K82">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L82">
+        <v>0.471</v>
+      </c>
+      <c r="M82">
+        <v>0.03582880000000001</v>
+      </c>
+      <c r="N82">
+        <v>0.4351712</v>
+      </c>
+      <c r="O82">
+        <v>0.104441088</v>
+      </c>
+      <c r="P82">
+        <v>0.330730112</v>
+      </c>
+      <c r="Q82">
+        <v>0.5467301120000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.939783418809069</v>
+      </c>
+      <c r="T82">
+        <v>3.383840623955659</v>
+      </c>
+      <c r="U82">
+        <v>0.0457</v>
+      </c>
+      <c r="V82">
+        <v>0.24</v>
+      </c>
+      <c r="W82">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>13.14584914928772</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2151663660872737</v>
+      </c>
+      <c r="C83">
+        <v>0.5805878910416609</v>
+      </c>
+      <c r="D83">
+        <v>1.307387891041661</v>
+      </c>
+      <c r="E83">
+        <v>0.3198000000000001</v>
+      </c>
+      <c r="F83">
+        <v>0.7938000000000001</v>
+      </c>
+      <c r="G83">
+        <v>0.067</v>
+      </c>
+      <c r="H83">
+        <v>0.506</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K83">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L83">
+        <v>0.471</v>
+      </c>
+      <c r="M83">
+        <v>0.03627666000000001</v>
+      </c>
+      <c r="N83">
+        <v>0.43472334</v>
+      </c>
+      <c r="O83">
+        <v>0.1043336016</v>
+      </c>
+      <c r="P83">
+        <v>0.3303897384</v>
+      </c>
+      <c r="Q83">
+        <v>0.5463897384</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.9843865583540725</v>
+      </c>
+      <c r="T83">
+        <v>3.551357486527722</v>
+      </c>
+      <c r="U83">
+        <v>0.0457</v>
+      </c>
+      <c r="V83">
+        <v>0.24</v>
+      </c>
+      <c r="W83">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>12.9835547153459</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2155875684127336</v>
+      </c>
+      <c r="C84">
+        <v>0.5676729954359969</v>
+      </c>
+      <c r="D84">
+        <v>1.304272995435997</v>
+      </c>
+      <c r="E84">
+        <v>0.3296000000000001</v>
+      </c>
+      <c r="F84">
+        <v>0.8036000000000001</v>
+      </c>
+      <c r="G84">
+        <v>0.067</v>
+      </c>
+      <c r="H84">
+        <v>0.506</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K84">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L84">
+        <v>0.471</v>
+      </c>
+      <c r="M84">
+        <v>0.03801028000000001</v>
+      </c>
+      <c r="N84">
+        <v>0.43298972</v>
+      </c>
+      <c r="O84">
+        <v>0.1039175328</v>
+      </c>
+      <c r="P84">
+        <v>0.3290721872</v>
+      </c>
+      <c r="Q84">
+        <v>0.5450721872000001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>1.033945602292965</v>
+      </c>
+      <c r="T84">
+        <v>3.737487333830013</v>
+      </c>
+      <c r="U84">
+        <v>0.0473</v>
+      </c>
+      <c r="V84">
+        <v>0.24</v>
+      </c>
+      <c r="W84">
+        <v>0.035948</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>12.39138464646932</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2150238107381936</v>
+      </c>
+      <c r="C85">
+        <v>0.562045495779692</v>
+      </c>
+      <c r="D85">
+        <v>1.308445495779692</v>
+      </c>
+      <c r="E85">
+        <v>0.3394</v>
+      </c>
+      <c r="F85">
+        <v>0.8134</v>
+      </c>
+      <c r="G85">
+        <v>0.067</v>
+      </c>
+      <c r="H85">
+        <v>0.506</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K85">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L85">
+        <v>0.471</v>
+      </c>
+      <c r="M85">
+        <v>0.03847382</v>
+      </c>
+      <c r="N85">
+        <v>0.43252618</v>
+      </c>
+      <c r="O85">
+        <v>0.1038062832</v>
+      </c>
+      <c r="P85">
+        <v>0.3287198968</v>
+      </c>
+      <c r="Q85">
+        <v>0.5447198968000001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>1.089335121989375</v>
+      </c>
+      <c r="T85">
+        <v>3.945514810226692</v>
+      </c>
+      <c r="U85">
+        <v>0.0473</v>
+      </c>
+      <c r="V85">
+        <v>0.24</v>
+      </c>
+      <c r="W85">
+        <v>0.035948</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>12.24209085554801</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2144600530636536</v>
+      </c>
+      <c r="C86">
+        <v>0.556444778297817</v>
+      </c>
+      <c r="D86">
+        <v>1.312644778297817</v>
+      </c>
+      <c r="E86">
+        <v>0.3492</v>
+      </c>
+      <c r="F86">
+        <v>0.8231999999999999</v>
+      </c>
+      <c r="G86">
+        <v>0.067</v>
+      </c>
+      <c r="H86">
+        <v>0.506</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K86">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L86">
+        <v>0.471</v>
+      </c>
+      <c r="M86">
+        <v>0.03893736</v>
+      </c>
+      <c r="N86">
+        <v>0.43206264</v>
+      </c>
+      <c r="O86">
+        <v>0.1036950336</v>
+      </c>
+      <c r="P86">
+        <v>0.3283676064</v>
+      </c>
+      <c r="Q86">
+        <v>0.5443676064</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>1.151648331647835</v>
+      </c>
+      <c r="T86">
+        <v>4.179545721172953</v>
+      </c>
+      <c r="U86">
+        <v>0.0473</v>
+      </c>
+      <c r="V86">
+        <v>0.24</v>
+      </c>
+      <c r="W86">
+        <v>0.035948</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>12.09635167869624</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2138962953891135</v>
+      </c>
+      <c r="C87">
+        <v>0.5508711016821342</v>
+      </c>
+      <c r="D87">
+        <v>1.316871101682134</v>
+      </c>
+      <c r="E87">
+        <v>0.359</v>
+      </c>
+      <c r="F87">
+        <v>0.833</v>
+      </c>
+      <c r="G87">
+        <v>0.067</v>
+      </c>
+      <c r="H87">
+        <v>0.506</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K87">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L87">
+        <v>0.471</v>
+      </c>
+      <c r="M87">
+        <v>0.0394009</v>
+      </c>
+      <c r="N87">
+        <v>0.4315991</v>
+      </c>
+      <c r="O87">
+        <v>0.103583784</v>
+      </c>
+      <c r="P87">
+        <v>0.328015316</v>
+      </c>
+      <c r="Q87">
+        <v>0.5440153160000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>1.222269969260757</v>
+      </c>
+      <c r="T87">
+        <v>4.444780753578719</v>
+      </c>
+      <c r="U87">
+        <v>0.0473</v>
+      </c>
+      <c r="V87">
+        <v>0.24</v>
+      </c>
+      <c r="W87">
+        <v>0.035948</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>11.95404165894688</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2133325377145735</v>
+      </c>
+      <c r="C88">
+        <v>0.5453247279668065</v>
+      </c>
+      <c r="D88">
+        <v>1.321124727966807</v>
+      </c>
+      <c r="E88">
+        <v>0.3688</v>
+      </c>
+      <c r="F88">
+        <v>0.8428</v>
+      </c>
+      <c r="G88">
+        <v>0.067</v>
+      </c>
+      <c r="H88">
+        <v>0.506</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K88">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L88">
+        <v>0.471</v>
+      </c>
+      <c r="M88">
+        <v>0.03986444</v>
+      </c>
+      <c r="N88">
+        <v>0.43113556</v>
+      </c>
+      <c r="O88">
+        <v>0.1034725344</v>
+      </c>
+      <c r="P88">
+        <v>0.3276630256</v>
+      </c>
+      <c r="Q88">
+        <v>0.5436630256000001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>1.302980412246953</v>
+      </c>
+      <c r="T88">
+        <v>4.747906504899594</v>
+      </c>
+      <c r="U88">
+        <v>0.0473</v>
+      </c>
+      <c r="V88">
+        <v>0.24</v>
+      </c>
+      <c r="W88">
+        <v>0.035948</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>11.81504117454052</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2127687800400335</v>
+      </c>
+      <c r="C89">
+        <v>0.539805922582556</v>
+      </c>
+      <c r="D89">
+        <v>1.325405922582556</v>
+      </c>
+      <c r="E89">
+        <v>0.3786</v>
+      </c>
+      <c r="F89">
+        <v>0.8526</v>
+      </c>
+      <c r="G89">
+        <v>0.067</v>
+      </c>
+      <c r="H89">
+        <v>0.506</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K89">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L89">
+        <v>0.471</v>
+      </c>
+      <c r="M89">
+        <v>0.04032798</v>
+      </c>
+      <c r="N89">
+        <v>0.43067202</v>
+      </c>
+      <c r="O89">
+        <v>0.1033612848</v>
+      </c>
+      <c r="P89">
+        <v>0.3273107352</v>
+      </c>
+      <c r="Q89">
+        <v>0.5433107352000001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>1.396107846461796</v>
+      </c>
+      <c r="T89">
+        <v>5.097666987192911</v>
+      </c>
+      <c r="U89">
+        <v>0.0473</v>
+      </c>
+      <c r="V89">
+        <v>0.24</v>
+      </c>
+      <c r="W89">
+        <v>0.035948</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>11.67923610356879</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2122050223654934</v>
+      </c>
+      <c r="C90">
+        <v>0.5343149544118754</v>
+      </c>
+      <c r="D90">
+        <v>1.329714954411875</v>
+      </c>
+      <c r="E90">
+        <v>0.3884</v>
+      </c>
+      <c r="F90">
+        <v>0.8623999999999999</v>
+      </c>
+      <c r="G90">
+        <v>0.067</v>
+      </c>
+      <c r="H90">
+        <v>0.506</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K90">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L90">
+        <v>0.471</v>
+      </c>
+      <c r="M90">
+        <v>0.04079152</v>
+      </c>
+      <c r="N90">
+        <v>0.43020848</v>
+      </c>
+      <c r="O90">
+        <v>0.1032500352</v>
+      </c>
+      <c r="P90">
+        <v>0.3269584448</v>
+      </c>
+      <c r="Q90">
+        <v>0.5429584448000001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>1.504756519712445</v>
+      </c>
+      <c r="T90">
+        <v>5.505720883201781</v>
+      </c>
+      <c r="U90">
+        <v>0.0473</v>
+      </c>
+      <c r="V90">
+        <v>0.24</v>
+      </c>
+      <c r="W90">
+        <v>0.035948</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>11.54651751148278</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2116412646909534</v>
+      </c>
+      <c r="C91">
+        <v>0.5288520958453217</v>
+      </c>
+      <c r="D91">
+        <v>1.334052095845322</v>
+      </c>
+      <c r="E91">
+        <v>0.3982</v>
+      </c>
+      <c r="F91">
+        <v>0.8722</v>
+      </c>
+      <c r="G91">
+        <v>0.067</v>
+      </c>
+      <c r="H91">
+        <v>0.506</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K91">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L91">
+        <v>0.471</v>
+      </c>
+      <c r="M91">
+        <v>0.04125506</v>
+      </c>
+      <c r="N91">
+        <v>0.42974494</v>
+      </c>
+      <c r="O91">
+        <v>0.1031387856</v>
+      </c>
+      <c r="P91">
+        <v>0.3266061544</v>
+      </c>
+      <c r="Q91">
+        <v>0.5426061544</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>1.633159497190485</v>
+      </c>
+      <c r="T91">
+        <v>5.987966396666809</v>
+      </c>
+      <c r="U91">
+        <v>0.0473</v>
+      </c>
+      <c r="V91">
+        <v>0.24</v>
+      </c>
+      <c r="W91">
+        <v>0.035948</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>11.41678135966836</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2110775070164133</v>
+      </c>
+      <c r="C92">
+        <v>0.5234176228389144</v>
+      </c>
+      <c r="D92">
+        <v>1.338417622838914</v>
+      </c>
+      <c r="E92">
+        <v>0.408</v>
+      </c>
+      <c r="F92">
+        <v>0.882</v>
+      </c>
+      <c r="G92">
+        <v>0.067</v>
+      </c>
+      <c r="H92">
+        <v>0.506</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K92">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L92">
+        <v>0.471</v>
+      </c>
+      <c r="M92">
+        <v>0.0417186</v>
+      </c>
+      <c r="N92">
+        <v>0.4292814</v>
+      </c>
+      <c r="O92">
+        <v>0.103027536</v>
+      </c>
+      <c r="P92">
+        <v>0.326253864</v>
+      </c>
+      <c r="Q92">
+        <v>0.5422538640000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.787243070164134</v>
+      </c>
+      <c r="T92">
+        <v>6.566661012824843</v>
+      </c>
+      <c r="U92">
+        <v>0.0473</v>
+      </c>
+      <c r="V92">
+        <v>0.24</v>
+      </c>
+      <c r="W92">
+        <v>0.035948</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>11.28992823344983</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2105137493418733</v>
+      </c>
+      <c r="C93">
+        <v>0.5180118149726661</v>
+      </c>
+      <c r="D93">
+        <v>1.342811814972666</v>
+      </c>
+      <c r="E93">
+        <v>0.4178000000000001</v>
+      </c>
+      <c r="F93">
+        <v>0.8918</v>
+      </c>
+      <c r="G93">
+        <v>0.067</v>
+      </c>
+      <c r="H93">
+        <v>0.506</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K93">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L93">
+        <v>0.471</v>
+      </c>
+      <c r="M93">
+        <v>0.04218214</v>
+      </c>
+      <c r="N93">
+        <v>0.42881786</v>
+      </c>
+      <c r="O93">
+        <v>0.1029162864</v>
+      </c>
+      <c r="P93">
+        <v>0.3259015736</v>
+      </c>
+      <c r="Q93">
+        <v>0.5419015736000001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.975567437131926</v>
+      </c>
+      <c r="T93">
+        <v>7.273954432573551</v>
+      </c>
+      <c r="U93">
+        <v>0.0473</v>
+      </c>
+      <c r="V93">
+        <v>0.24</v>
+      </c>
+      <c r="W93">
+        <v>0.035948</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>11.1658630880273</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2099499916673333</v>
+      </c>
+      <c r="C94">
+        <v>0.5126349555102668</v>
+      </c>
+      <c r="D94">
+        <v>1.347234955510267</v>
+      </c>
+      <c r="E94">
+        <v>0.4276000000000001</v>
+      </c>
+      <c r="F94">
+        <v>0.9016000000000001</v>
+      </c>
+      <c r="G94">
+        <v>0.067</v>
+      </c>
+      <c r="H94">
+        <v>0.506</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K94">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L94">
+        <v>0.471</v>
+      </c>
+      <c r="M94">
+        <v>0.04264568000000001</v>
+      </c>
+      <c r="N94">
+        <v>0.42835432</v>
+      </c>
+      <c r="O94">
+        <v>0.1028050368</v>
+      </c>
+      <c r="P94">
+        <v>0.3255492832</v>
+      </c>
+      <c r="Q94">
+        <v>0.5415492832000001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>2.210972895841667</v>
+      </c>
+      <c r="T94">
+        <v>8.158071207259438</v>
+      </c>
+      <c r="U94">
+        <v>0.0473</v>
+      </c>
+      <c r="V94">
+        <v>0.24</v>
+      </c>
+      <c r="W94">
+        <v>0.035948</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>11.04449501098352</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2093862339927932</v>
+      </c>
+      <c r="C95">
+        <v>0.507287331459956</v>
+      </c>
+      <c r="D95">
+        <v>1.351687331459956</v>
+      </c>
+      <c r="E95">
+        <v>0.4374</v>
+      </c>
+      <c r="F95">
+        <v>0.9114</v>
+      </c>
+      <c r="G95">
+        <v>0.067</v>
+      </c>
+      <c r="H95">
+        <v>0.506</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K95">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L95">
+        <v>0.471</v>
+      </c>
+      <c r="M95">
+        <v>0.04310922</v>
+      </c>
+      <c r="N95">
+        <v>0.42789078</v>
+      </c>
+      <c r="O95">
+        <v>0.1026937872</v>
+      </c>
+      <c r="P95">
+        <v>0.3251969928</v>
+      </c>
+      <c r="Q95">
+        <v>0.5411969928</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>2.513637057039905</v>
+      </c>
+      <c r="T95">
+        <v>9.29479277471272</v>
+      </c>
+      <c r="U95">
+        <v>0.0473</v>
+      </c>
+      <c r="V95">
+        <v>0.24</v>
+      </c>
+      <c r="W95">
+        <v>0.035948</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>10.92573700011273</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2088224763182532</v>
+      </c>
+      <c r="C96">
+        <v>0.5019692336365995</v>
+      </c>
+      <c r="D96">
+        <v>1.3561692336366</v>
+      </c>
+      <c r="E96">
+        <v>0.4472</v>
+      </c>
+      <c r="F96">
+        <v>0.9212</v>
+      </c>
+      <c r="G96">
+        <v>0.067</v>
+      </c>
+      <c r="H96">
+        <v>0.506</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K96">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L96">
+        <v>0.471</v>
+      </c>
+      <c r="M96">
+        <v>0.04357276</v>
+      </c>
+      <c r="N96">
+        <v>0.42742724</v>
+      </c>
+      <c r="O96">
+        <v>0.1025825376</v>
+      </c>
+      <c r="P96">
+        <v>0.3248447024</v>
+      </c>
+      <c r="Q96">
+        <v>0.5408447024</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>2.917189271970889</v>
+      </c>
+      <c r="T96">
+        <v>10.8104215313171</v>
+      </c>
+      <c r="U96">
+        <v>0.0473</v>
+      </c>
+      <c r="V96">
+        <v>0.24</v>
+      </c>
+      <c r="W96">
+        <v>0.035948</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>10.80950575543069</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2082587186437132</v>
+      </c>
+      <c r="C97">
+        <v>0.4966809567250123</v>
+      </c>
+      <c r="D97">
+        <v>1.360680956725012</v>
+      </c>
+      <c r="E97">
+        <v>0.4570000000000001</v>
+      </c>
+      <c r="F97">
+        <v>0.931</v>
+      </c>
+      <c r="G97">
+        <v>0.067</v>
+      </c>
+      <c r="H97">
+        <v>0.506</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K97">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L97">
+        <v>0.471</v>
+      </c>
+      <c r="M97">
+        <v>0.04403630000000001</v>
+      </c>
+      <c r="N97">
+        <v>0.4269636999999999</v>
+      </c>
+      <c r="O97">
+        <v>0.102471288</v>
+      </c>
+      <c r="P97">
+        <v>0.324492412</v>
+      </c>
+      <c r="Q97">
+        <v>0.5404924120000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>3.482162372874268</v>
+      </c>
+      <c r="T97">
+        <v>12.93230179056323</v>
+      </c>
+      <c r="U97">
+        <v>0.0473</v>
+      </c>
+      <c r="V97">
+        <v>0.24</v>
+      </c>
+      <c r="W97">
+        <v>0.035948</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>10.69572148432089</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2076949609691731</v>
+      </c>
+      <c r="C98">
+        <v>0.4914227993445458</v>
+      </c>
+      <c r="D98">
+        <v>1.365222799344546</v>
+      </c>
+      <c r="E98">
+        <v>0.4668</v>
+      </c>
+      <c r="F98">
+        <v>0.9408</v>
+      </c>
+      <c r="G98">
+        <v>0.067</v>
+      </c>
+      <c r="H98">
+        <v>0.506</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K98">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L98">
+        <v>0.471</v>
+      </c>
+      <c r="M98">
+        <v>0.04449984</v>
+      </c>
+      <c r="N98">
+        <v>0.42650016</v>
+      </c>
+      <c r="O98">
+        <v>0.1023600384</v>
+      </c>
+      <c r="P98">
+        <v>0.3241401215999999</v>
+      </c>
+      <c r="Q98">
+        <v>0.5401401216</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>4.329622024229324</v>
+      </c>
+      <c r="T98">
+        <v>16.11512217943238</v>
+      </c>
+      <c r="U98">
+        <v>0.0473</v>
+      </c>
+      <c r="V98">
+        <v>0.24</v>
+      </c>
+      <c r="W98">
+        <v>0.035948</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>10.58430771885921</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2071312032946331</v>
+      </c>
+      <c r="C99">
+        <v>0.486195064114972</v>
+      </c>
+      <c r="D99">
+        <v>1.369795064114972</v>
+      </c>
+      <c r="E99">
+        <v>0.4766</v>
+      </c>
+      <c r="F99">
+        <v>0.9506</v>
+      </c>
+      <c r="G99">
+        <v>0.067</v>
+      </c>
+      <c r="H99">
+        <v>0.506</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K99">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L99">
+        <v>0.471</v>
+      </c>
+      <c r="M99">
+        <v>0.04496338</v>
+      </c>
+      <c r="N99">
+        <v>0.42603662</v>
+      </c>
+      <c r="O99">
+        <v>0.1022487888</v>
+      </c>
+      <c r="P99">
+        <v>0.3237878312</v>
+      </c>
+      <c r="Q99">
+        <v>0.5397878312000001</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>5.742054776487764</v>
+      </c>
+      <c r="T99">
+        <v>21.41982282754768</v>
+      </c>
+      <c r="U99">
+        <v>0.0473</v>
+      </c>
+      <c r="V99">
+        <v>0.24</v>
+      </c>
+      <c r="W99">
+        <v>0.035948</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>10.47519114443798</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.206567445620093</v>
+      </c>
+      <c r="C100">
+        <v>0.4809980577237005</v>
+      </c>
+      <c r="D100">
+        <v>1.3743980577237</v>
+      </c>
+      <c r="E100">
+        <v>0.4863999999999999</v>
+      </c>
+      <c r="F100">
+        <v>0.9603999999999999</v>
+      </c>
+      <c r="G100">
+        <v>0.067</v>
+      </c>
+      <c r="H100">
+        <v>0.506</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K100">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L100">
+        <v>0.471</v>
+      </c>
+      <c r="M100">
+        <v>0.04542692</v>
+      </c>
+      <c r="N100">
+        <v>0.42557308</v>
+      </c>
+      <c r="O100">
+        <v>0.1021375392</v>
+      </c>
+      <c r="P100">
+        <v>0.3234355408</v>
+      </c>
+      <c r="Q100">
+        <v>0.5394355408000001</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>8.566920281004643</v>
+      </c>
+      <c r="T100">
+        <v>32.02922412377828</v>
+      </c>
+      <c r="U100">
+        <v>0.0473</v>
+      </c>
+      <c r="V100">
+        <v>0.24</v>
+      </c>
+      <c r="W100">
+        <v>0.035948</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>10.3683014388825</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.206003687945553</v>
+      </c>
+      <c r="C101">
+        <v>0.4758320909943479</v>
+      </c>
+      <c r="D101">
+        <v>1.379032090994348</v>
+      </c>
+      <c r="E101">
+        <v>0.4962</v>
+      </c>
+      <c r="F101">
+        <v>0.9702</v>
+      </c>
+      <c r="G101">
+        <v>0.067</v>
+      </c>
+      <c r="H101">
+        <v>0.506</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K101">
+        <v>0.2160000000000001</v>
+      </c>
+      <c r="L101">
+        <v>0.471</v>
+      </c>
+      <c r="M101">
+        <v>0.04589046</v>
+      </c>
+      <c r="N101">
+        <v>0.42510954</v>
+      </c>
+      <c r="O101">
+        <v>0.1020262896</v>
+      </c>
+      <c r="P101">
+        <v>0.3230832504</v>
+      </c>
+      <c r="Q101">
+        <v>0.5390832504</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>17.04151679455528</v>
+      </c>
+      <c r="T101">
+        <v>63.85742801247009</v>
+      </c>
+      <c r="U101">
+        <v>0.0473</v>
+      </c>
+      <c r="V101">
+        <v>0.24</v>
+      </c>
+      <c r="W101">
+        <v>0.035948</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>10.26357112131802</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_office_equipment_services.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_office_equipment_services.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.2022152804997194</v>
+        <v>0.2017641638265201</v>
       </c>
       <c r="C2">
-        <v>2.334461850450915</v>
+        <v>2.320739020571742</v>
       </c>
       <c r="D2">
-        <v>2.270461850450915</v>
+        <v>2.277029020571742</v>
       </c>
       <c r="E2">
-        <v>-0.969</v>
+        <v>-0.9487099999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.02029</v>
       </c>
       <c r="G2">
         <v>0.064</v>
@@ -1451,28 +1451,28 @@
         <v>0.445</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.001020587</v>
       </c>
       <c r="N2">
-        <v>0.445</v>
+        <v>0.443979413</v>
       </c>
       <c r="O2">
-        <v>0.1068</v>
+        <v>0.10655505912</v>
       </c>
       <c r="P2">
-        <v>0.3382</v>
+        <v>0.33742435388</v>
       </c>
       <c r="Q2">
-        <v>0.6542</v>
+        <v>0.65342435388</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.2022152804997194</v>
+        <v>0.2034160442692122</v>
       </c>
       <c r="T2">
-        <v>0.7685264885431575</v>
+        <v>0.7744262878491455</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>436.0235825069299</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.2017641638265201</v>
+        <v>0.2013130471533207</v>
       </c>
       <c r="C3">
-        <v>2.320739020571742</v>
+        <v>2.307054291160556</v>
       </c>
       <c r="D3">
-        <v>2.277029020571742</v>
+        <v>2.283634291160556</v>
       </c>
       <c r="E3">
-        <v>-0.9487099999999999</v>
+        <v>-0.92842</v>
       </c>
       <c r="F3">
-        <v>0.02029</v>
+        <v>0.04058</v>
       </c>
       <c r="G3">
         <v>0.064</v>
@@ -1533,28 +1533,28 @@
         <v>0.445</v>
       </c>
       <c r="M3">
-        <v>0.001020587</v>
+        <v>0.002041174</v>
       </c>
       <c r="N3">
-        <v>0.443979413</v>
+        <v>0.442958826</v>
       </c>
       <c r="O3">
-        <v>0.10655505912</v>
+        <v>0.10631011824</v>
       </c>
       <c r="P3">
-        <v>0.33742435388</v>
+        <v>0.33664870776</v>
       </c>
       <c r="Q3">
-        <v>0.65342435388</v>
+        <v>0.6526487077600001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.2034160442692122</v>
+        <v>0.2046413134217559</v>
       </c>
       <c r="T3">
-        <v>0.7744262878491455</v>
+        <v>0.7804464912226023</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>436.0235825069299</v>
+        <v>218.011791253465</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.2013130471533207</v>
+        <v>0.2008619304801215</v>
       </c>
       <c r="C4">
-        <v>2.307054291160556</v>
+        <v>2.293407994750744</v>
       </c>
       <c r="D4">
-        <v>2.283634291160556</v>
+        <v>2.290277994750744</v>
       </c>
       <c r="E4">
-        <v>-0.92842</v>
+        <v>-0.90813</v>
       </c>
       <c r="F4">
-        <v>0.04058</v>
+        <v>0.06086999999999999</v>
       </c>
       <c r="G4">
         <v>0.064</v>
@@ -1615,28 +1615,28 @@
         <v>0.445</v>
       </c>
       <c r="M4">
-        <v>0.002041174</v>
+        <v>0.003061761</v>
       </c>
       <c r="N4">
-        <v>0.442958826</v>
+        <v>0.441938239</v>
       </c>
       <c r="O4">
-        <v>0.10631011824</v>
+        <v>0.10606517736</v>
       </c>
       <c r="P4">
-        <v>0.33664870776</v>
+        <v>0.33587306164</v>
       </c>
       <c r="Q4">
-        <v>0.6526487077600001</v>
+        <v>0.65187306164</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.2046413134217559</v>
+        <v>0.2058918458557953</v>
       </c>
       <c r="T4">
-        <v>0.7804464912226023</v>
+        <v>0.7865908225006669</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>218.011791253465</v>
+        <v>145.3411941689766</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.2008619304801215</v>
+        <v>0.2004108138069221</v>
       </c>
       <c r="C5">
-        <v>2.293407994750744</v>
+        <v>2.279800467756699</v>
       </c>
       <c r="D5">
-        <v>2.290277994750744</v>
+        <v>2.296960467756699</v>
       </c>
       <c r="E5">
-        <v>-0.90813</v>
+        <v>-0.88784</v>
       </c>
       <c r="F5">
-        <v>0.06086999999999999</v>
+        <v>0.08116</v>
       </c>
       <c r="G5">
         <v>0.064</v>
@@ -1697,28 +1697,28 @@
         <v>0.445</v>
       </c>
       <c r="M5">
-        <v>0.003061761</v>
+        <v>0.004082348</v>
       </c>
       <c r="N5">
-        <v>0.441938239</v>
+        <v>0.440917652</v>
       </c>
       <c r="O5">
-        <v>0.10606517736</v>
+        <v>0.10582023648</v>
       </c>
       <c r="P5">
-        <v>0.33587306164</v>
+        <v>0.33509741552</v>
       </c>
       <c r="Q5">
-        <v>0.65187306164</v>
+        <v>0.65109741552</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.2058918458557953</v>
+        <v>0.2071684310488772</v>
       </c>
       <c r="T5">
-        <v>0.7865908225006669</v>
+        <v>0.7928631606803576</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>145.3411941689766</v>
+        <v>109.0058956267325</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.2004108138069221</v>
+        <v>0.1999596971337228</v>
       </c>
       <c r="C6">
-        <v>2.279800467756699</v>
+        <v>2.266232050530607</v>
       </c>
       <c r="D6">
-        <v>2.296960467756699</v>
+        <v>2.303682050530607</v>
       </c>
       <c r="E6">
-        <v>-0.88784</v>
+        <v>-0.8675499999999999</v>
       </c>
       <c r="F6">
-        <v>0.08116</v>
+        <v>0.10145</v>
       </c>
       <c r="G6">
         <v>0.064</v>
@@ -1779,28 +1779,28 @@
         <v>0.445</v>
       </c>
       <c r="M6">
-        <v>0.004082348</v>
+        <v>0.005102934999999999</v>
       </c>
       <c r="N6">
-        <v>0.440917652</v>
+        <v>0.439897065</v>
       </c>
       <c r="O6">
-        <v>0.10582023648</v>
+        <v>0.1055752956</v>
       </c>
       <c r="P6">
-        <v>0.33509741552</v>
+        <v>0.3343217694</v>
       </c>
       <c r="Q6">
-        <v>0.65109741552</v>
+        <v>0.6503217694000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.2071684310488772</v>
+        <v>0.2084718917197082</v>
       </c>
       <c r="T6">
-        <v>0.7928631606803576</v>
+        <v>0.7992675480848839</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>109.0058956267325</v>
+        <v>87.20471650138599</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1999596971337228</v>
+        <v>0.1995085804605234</v>
       </c>
       <c r="C7">
-        <v>2.266232050530607</v>
+        <v>2.252703087420225</v>
       </c>
       <c r="D7">
-        <v>2.303682050530607</v>
+        <v>2.310443087420225</v>
       </c>
       <c r="E7">
-        <v>-0.8675499999999999</v>
+        <v>-0.84726</v>
       </c>
       <c r="F7">
-        <v>0.10145</v>
+        <v>0.12174</v>
       </c>
       <c r="G7">
         <v>0.064</v>
@@ -1861,28 +1861,28 @@
         <v>0.445</v>
       </c>
       <c r="M7">
-        <v>0.005102934999999999</v>
+        <v>0.006123522</v>
       </c>
       <c r="N7">
-        <v>0.439897065</v>
+        <v>0.438876478</v>
       </c>
       <c r="O7">
-        <v>0.1055752956</v>
+        <v>0.10533035472</v>
       </c>
       <c r="P7">
-        <v>0.3343217694</v>
+        <v>0.33354612328</v>
       </c>
       <c r="Q7">
-        <v>0.6503217694000001</v>
+        <v>0.6495461232799999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.2084718917197082</v>
+        <v>0.2098030855963016</v>
       </c>
       <c r="T7">
-        <v>0.7992675480848839</v>
+        <v>0.8058081990512086</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>87.20471650138599</v>
+        <v>72.67059708448831</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1995085804605234</v>
+        <v>0.1990574637873241</v>
       </c>
       <c r="C8">
-        <v>2.252703087420225</v>
+        <v>2.239213926827692</v>
       </c>
       <c r="D8">
-        <v>2.310443087420225</v>
+        <v>2.317243926827692</v>
       </c>
       <c r="E8">
-        <v>-0.84726</v>
+        <v>-0.82697</v>
       </c>
       <c r="F8">
-        <v>0.12174</v>
+        <v>0.14203</v>
       </c>
       <c r="G8">
         <v>0.064</v>
@@ -1943,28 +1943,28 @@
         <v>0.445</v>
       </c>
       <c r="M8">
-        <v>0.006123521999999999</v>
+        <v>0.007144108999999999</v>
       </c>
       <c r="N8">
-        <v>0.438876478</v>
+        <v>0.437855891</v>
       </c>
       <c r="O8">
-        <v>0.10533035472</v>
+        <v>0.10508541384</v>
       </c>
       <c r="P8">
-        <v>0.33354612328</v>
+        <v>0.33277047716</v>
       </c>
       <c r="Q8">
-        <v>0.6495461232799999</v>
+        <v>0.64877047716</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2098030855963016</v>
+        <v>0.211162907298198</v>
       </c>
       <c r="T8">
-        <v>0.8058081990512086</v>
+        <v>0.8124895091780994</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>72.67059708448832</v>
+        <v>62.2890832152757</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1990574637873241</v>
+        <v>0.1986063471141248</v>
       </c>
       <c r="C9">
-        <v>2.239213926827693</v>
+        <v>2.225764921269378</v>
       </c>
       <c r="D9">
-        <v>2.317243926827693</v>
+        <v>2.324084921269377</v>
       </c>
       <c r="E9">
-        <v>-0.82697</v>
+        <v>-0.80668</v>
       </c>
       <c r="F9">
-        <v>0.14203</v>
+        <v>0.16232</v>
       </c>
       <c r="G9">
         <v>0.064</v>
@@ -2025,28 +2025,28 @@
         <v>0.445</v>
       </c>
       <c r="M9">
-        <v>0.007144109000000001</v>
+        <v>0.008164695999999999</v>
       </c>
       <c r="N9">
-        <v>0.437855891</v>
+        <v>0.436835304</v>
       </c>
       <c r="O9">
-        <v>0.10508541384</v>
+        <v>0.10484047296</v>
       </c>
       <c r="P9">
-        <v>0.33277047716</v>
+        <v>0.33199483104</v>
       </c>
       <c r="Q9">
-        <v>0.64877047716</v>
+        <v>0.6479948310400001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.211162907298198</v>
+        <v>0.21255229034144</v>
       </c>
       <c r="T9">
-        <v>0.8124895091780994</v>
+        <v>0.8193160651773139</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>62.28908321527568</v>
+        <v>54.50294781336624</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1986063471141248</v>
+        <v>0.1981552304409255</v>
       </c>
       <c r="C10">
-        <v>2.225764921269378</v>
+        <v>2.212356427436783</v>
       </c>
       <c r="D10">
-        <v>2.324084921269377</v>
+        <v>2.330966427436783</v>
       </c>
       <c r="E10">
-        <v>-0.80668</v>
+        <v>-0.7863899999999999</v>
       </c>
       <c r="F10">
-        <v>0.16232</v>
+        <v>0.18261</v>
       </c>
       <c r="G10">
         <v>0.064</v>
@@ -2107,28 +2107,28 @@
         <v>0.445</v>
       </c>
       <c r="M10">
-        <v>0.008164695999999999</v>
+        <v>0.009185282999999999</v>
       </c>
       <c r="N10">
-        <v>0.436835304</v>
+        <v>0.435814717</v>
       </c>
       <c r="O10">
-        <v>0.10484047296</v>
+        <v>0.10459553208</v>
       </c>
       <c r="P10">
-        <v>0.33199483104</v>
+        <v>0.33121918492</v>
       </c>
       <c r="Q10">
-        <v>0.6479948310400001</v>
+        <v>0.64721918492</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.21255229034144</v>
+        <v>0.2139722092757423</v>
       </c>
       <c r="T10">
-        <v>0.8193160651773139</v>
+        <v>0.8262926553743135</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>54.50294781336624</v>
+        <v>48.44706472299221</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1981552304409255</v>
+        <v>0.1977041137677262</v>
       </c>
       <c r="C11">
-        <v>2.212356427436783</v>
+        <v>2.198988806258547</v>
       </c>
       <c r="D11">
-        <v>2.330966427436783</v>
+        <v>2.337888806258547</v>
       </c>
       <c r="E11">
-        <v>-0.7863899999999999</v>
+        <v>-0.7661</v>
       </c>
       <c r="F11">
-        <v>0.18261</v>
+        <v>0.2029</v>
       </c>
       <c r="G11">
         <v>0.064</v>
@@ -2189,28 +2189,28 @@
         <v>0.445</v>
       </c>
       <c r="M11">
-        <v>0.009185282999999999</v>
+        <v>0.01020587</v>
       </c>
       <c r="N11">
-        <v>0.435814717</v>
+        <v>0.43479413</v>
       </c>
       <c r="O11">
-        <v>0.10459553208</v>
+        <v>0.1043505912</v>
       </c>
       <c r="P11">
-        <v>0.33121918492</v>
+        <v>0.3304435388</v>
       </c>
       <c r="Q11">
-        <v>0.64721918492</v>
+        <v>0.6464435388000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2139722092757423</v>
+        <v>0.2154236819641402</v>
       </c>
       <c r="T11">
-        <v>0.8262926553743135</v>
+        <v>0.8334242809090242</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>48.44706472299221</v>
+        <v>43.60235825069299</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1977041137677262</v>
+        <v>0.1972529970945268</v>
       </c>
       <c r="C12">
-        <v>2.198988806258547</v>
+        <v>2.185662422963544</v>
       </c>
       <c r="D12">
-        <v>2.337888806258547</v>
+        <v>2.344852422963544</v>
       </c>
       <c r="E12">
-        <v>-0.7661</v>
+        <v>-0.74581</v>
       </c>
       <c r="F12">
-        <v>0.2029</v>
+        <v>0.22319</v>
       </c>
       <c r="G12">
         <v>0.064</v>
@@ -2271,28 +2271,28 @@
         <v>0.445</v>
       </c>
       <c r="M12">
-        <v>0.01020587</v>
+        <v>0.011226457</v>
       </c>
       <c r="N12">
-        <v>0.43479413</v>
+        <v>0.433773543</v>
       </c>
       <c r="O12">
-        <v>0.1043505912</v>
+        <v>0.10410565032</v>
       </c>
       <c r="P12">
-        <v>0.3304435388</v>
+        <v>0.32966789268</v>
       </c>
       <c r="Q12">
-        <v>0.6464435388000001</v>
+        <v>0.6456678926799999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2154236819641402</v>
+        <v>0.2169077720163223</v>
       </c>
       <c r="T12">
-        <v>0.8334242809090242</v>
+        <v>0.8407161676917059</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>43.60235825069299</v>
+        <v>39.63850750062999</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1972529970945268</v>
+        <v>0.1968018804213275</v>
       </c>
       <c r="C13">
-        <v>2.185662422963544</v>
+        <v>2.172377647145118</v>
       </c>
       <c r="D13">
-        <v>2.344852422963544</v>
+        <v>2.351857647145118</v>
       </c>
       <c r="E13">
-        <v>-0.74581</v>
+        <v>-0.7255199999999999</v>
       </c>
       <c r="F13">
-        <v>0.22319</v>
+        <v>0.24348</v>
       </c>
       <c r="G13">
         <v>0.064</v>
@@ -2353,28 +2353,28 @@
         <v>0.445</v>
       </c>
       <c r="M13">
-        <v>0.011226457</v>
+        <v>0.012247044</v>
       </c>
       <c r="N13">
-        <v>0.433773543</v>
+        <v>0.432752956</v>
       </c>
       <c r="O13">
-        <v>0.10410565032</v>
+        <v>0.10386070944</v>
       </c>
       <c r="P13">
-        <v>0.32966789268</v>
+        <v>0.32889224656</v>
       </c>
       <c r="Q13">
-        <v>0.6456678926799999</v>
+        <v>0.64489224656</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2169077720163223</v>
+        <v>0.2184255913878722</v>
       </c>
       <c r="T13">
-        <v>0.8407161676917059</v>
+        <v>0.8481737791739937</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>39.63850750062999</v>
+        <v>36.33529854224416</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1968018804213275</v>
+        <v>0.1963507637481282</v>
       </c>
       <c r="C14">
-        <v>2.172377647145118</v>
+        <v>2.159134852826476</v>
       </c>
       <c r="D14">
-        <v>2.351857647145118</v>
+        <v>2.358904852826476</v>
       </c>
       <c r="E14">
-        <v>-0.7255199999999999</v>
+        <v>-0.70523</v>
       </c>
       <c r="F14">
-        <v>0.24348</v>
+        <v>0.26377</v>
       </c>
       <c r="G14">
         <v>0.064</v>
@@ -2435,28 +2435,28 @@
         <v>0.445</v>
       </c>
       <c r="M14">
-        <v>0.012247044</v>
+        <v>0.013267631</v>
       </c>
       <c r="N14">
-        <v>0.432752956</v>
+        <v>0.431732369</v>
       </c>
       <c r="O14">
-        <v>0.10386070944</v>
+        <v>0.10361576856</v>
       </c>
       <c r="P14">
-        <v>0.32889224656</v>
+        <v>0.32811660044</v>
       </c>
       <c r="Q14">
-        <v>0.64489224656</v>
+        <v>0.6441166004400001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2184255913878722</v>
+        <v>0.219978303158768</v>
       </c>
       <c r="T14">
-        <v>0.8481737791739937</v>
+        <v>0.8558028300007023</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>36.33529854224416</v>
+        <v>33.54027557745614</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1963507637481282</v>
+        <v>0.1958996470749289</v>
       </c>
       <c r="C15">
-        <v>2.159134852826476</v>
+        <v>2.14593441852725</v>
       </c>
       <c r="D15">
-        <v>2.358904852826476</v>
+        <v>2.36599441852725</v>
       </c>
       <c r="E15">
-        <v>-0.70523</v>
+        <v>-0.6849399999999999</v>
       </c>
       <c r="F15">
-        <v>0.26377</v>
+        <v>0.28406</v>
       </c>
       <c r="G15">
         <v>0.064</v>
@@ -2517,28 +2517,28 @@
         <v>0.445</v>
       </c>
       <c r="M15">
-        <v>0.013267631</v>
+        <v>0.014288218</v>
       </c>
       <c r="N15">
-        <v>0.431732369</v>
+        <v>0.430711782</v>
       </c>
       <c r="O15">
-        <v>0.10361576856</v>
+        <v>0.10337082768</v>
       </c>
       <c r="P15">
-        <v>0.32811660044</v>
+        <v>0.32734095432</v>
       </c>
       <c r="Q15">
-        <v>0.6441166004400001</v>
+        <v>0.6433409543199999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.219978303158768</v>
+        <v>0.2215671245057312</v>
       </c>
       <c r="T15">
-        <v>0.8558028300007023</v>
+        <v>0.8636093006140784</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>33.54027557745614</v>
+        <v>31.14454160763784</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1958996470749289</v>
+        <v>0.1954485304017295</v>
       </c>
       <c r="C16">
-        <v>2.14593441852725</v>
+        <v>2.132776727331279</v>
       </c>
       <c r="D16">
-        <v>2.36599441852725</v>
+        <v>2.373126727331279</v>
       </c>
       <c r="E16">
-        <v>-0.6849399999999999</v>
+        <v>-0.66465</v>
       </c>
       <c r="F16">
-        <v>0.28406</v>
+        <v>0.30435</v>
       </c>
       <c r="G16">
         <v>0.064</v>
@@ -2599,28 +2599,28 @@
         <v>0.445</v>
       </c>
       <c r="M16">
-        <v>0.014288218</v>
+        <v>0.015308805</v>
       </c>
       <c r="N16">
-        <v>0.430711782</v>
+        <v>0.429691195</v>
       </c>
       <c r="O16">
-        <v>0.10337082768</v>
+        <v>0.1031258868</v>
       </c>
       <c r="P16">
-        <v>0.32734095432</v>
+        <v>0.3265653082</v>
       </c>
       <c r="Q16">
-        <v>0.6433409543199999</v>
+        <v>0.6425653082</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2215671245057312</v>
+        <v>0.2231933298843877</v>
       </c>
       <c r="T16">
-        <v>0.8636093006140784</v>
+        <v>0.8715994528889458</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>31.14454160763784</v>
+        <v>29.06823883379532</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1954485304017295</v>
+        <v>0.1949974137285302</v>
       </c>
       <c r="C17">
-        <v>2.132776727331279</v>
+        <v>2.119662166955601</v>
       </c>
       <c r="D17">
-        <v>2.373126727331279</v>
+        <v>2.380302166955601</v>
       </c>
       <c r="E17">
-        <v>-0.66465</v>
+        <v>-0.64436</v>
       </c>
       <c r="F17">
-        <v>0.30435</v>
+        <v>0.32464</v>
       </c>
       <c r="G17">
         <v>0.064</v>
@@ -2681,28 +2681,28 @@
         <v>0.445</v>
       </c>
       <c r="M17">
-        <v>0.015308805</v>
+        <v>0.016329392</v>
       </c>
       <c r="N17">
-        <v>0.429691195</v>
+        <v>0.428670608</v>
       </c>
       <c r="O17">
-        <v>0.1031258868</v>
+        <v>0.10288094592</v>
       </c>
       <c r="P17">
-        <v>0.3265653082</v>
+        <v>0.32578966208</v>
       </c>
       <c r="Q17">
-        <v>0.6425653082</v>
+        <v>0.6417896620800001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2231933298843877</v>
+        <v>0.2248582544387265</v>
       </c>
       <c r="T17">
-        <v>0.8715994528889457</v>
+        <v>0.8797798468846433</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>29.06823883379533</v>
+        <v>27.25147390668312</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1949974137285302</v>
+        <v>0.1945462970553309</v>
       </c>
       <c r="C18">
-        <v>2.119662166955601</v>
+        <v>2.106591129820719</v>
       </c>
       <c r="D18">
-        <v>2.380302166955601</v>
+        <v>2.387521129820719</v>
       </c>
       <c r="E18">
-        <v>-0.64436</v>
+        <v>-0.6240699999999999</v>
       </c>
       <c r="F18">
-        <v>0.32464</v>
+        <v>0.34493</v>
       </c>
       <c r="G18">
         <v>0.064</v>
@@ -2763,28 +2763,28 @@
         <v>0.445</v>
       </c>
       <c r="M18">
-        <v>0.016329392</v>
+        <v>0.017349979</v>
       </c>
       <c r="N18">
-        <v>0.428670608</v>
+        <v>0.427650021</v>
       </c>
       <c r="O18">
-        <v>0.10288094592</v>
+        <v>0.10263600504</v>
       </c>
       <c r="P18">
-        <v>0.32578966208</v>
+        <v>0.32501401596</v>
       </c>
       <c r="Q18">
-        <v>0.6417896620800001</v>
+        <v>0.64101401596</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2248582544387265</v>
+        <v>0.2265632976570252</v>
       </c>
       <c r="T18">
-        <v>0.8797798468846433</v>
+        <v>0.8881573588079479</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>27.25147390668312</v>
+        <v>25.6484460298194</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1945462970553309</v>
+        <v>0.1940951803821316</v>
       </c>
       <c r="C19">
-        <v>2.106591129820719</v>
+        <v>2.093564013122135</v>
       </c>
       <c r="D19">
-        <v>2.387521129820719</v>
+        <v>2.394784013122135</v>
       </c>
       <c r="E19">
-        <v>-0.6240699999999999</v>
+        <v>-0.60378</v>
       </c>
       <c r="F19">
-        <v>0.34493</v>
+        <v>0.36522</v>
       </c>
       <c r="G19">
         <v>0.064</v>
@@ -2845,28 +2845,28 @@
         <v>0.445</v>
       </c>
       <c r="M19">
-        <v>0.017349979</v>
+        <v>0.018370566</v>
       </c>
       <c r="N19">
-        <v>0.427650021</v>
+        <v>0.426629434</v>
       </c>
       <c r="O19">
-        <v>0.10263600504</v>
+        <v>0.10239106416</v>
       </c>
       <c r="P19">
-        <v>0.32501401596</v>
+        <v>0.32423836984</v>
       </c>
       <c r="Q19">
-        <v>0.64101401596</v>
+        <v>0.64023836984</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2265632976570252</v>
+        <v>0.2283099272952824</v>
       </c>
       <c r="T19">
-        <v>0.8881573588079479</v>
+        <v>0.8967392002903576</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>25.6484460298194</v>
+        <v>24.2235323614961</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1940951803821316</v>
+        <v>0.1936440637089322</v>
       </c>
       <c r="C20">
-        <v>2.093564013122135</v>
+        <v>2.080581218903203</v>
       </c>
       <c r="D20">
-        <v>2.394784013122135</v>
+        <v>2.402091218903203</v>
       </c>
       <c r="E20">
-        <v>-0.60378</v>
+        <v>-0.5834900000000001</v>
       </c>
       <c r="F20">
-        <v>0.36522</v>
+        <v>0.38551</v>
       </c>
       <c r="G20">
         <v>0.064</v>
@@ -2927,28 +2927,28 @@
         <v>0.445</v>
       </c>
       <c r="M20">
-        <v>0.018370566</v>
+        <v>0.019391153</v>
       </c>
       <c r="N20">
-        <v>0.426629434</v>
+        <v>0.425608847</v>
       </c>
       <c r="O20">
-        <v>0.10239106416</v>
+        <v>0.10214612328</v>
       </c>
       <c r="P20">
-        <v>0.32423836984</v>
+        <v>0.32346272372</v>
       </c>
       <c r="Q20">
-        <v>0.64023836984</v>
+        <v>0.63946272372</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2283099272952823</v>
+        <v>0.2300996835912743</v>
       </c>
       <c r="T20">
-        <v>0.8967392002903574</v>
+        <v>0.9055329390933203</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>24.2235323614961</v>
+        <v>22.94860960562789</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1936440637089322</v>
+        <v>0.1931929470357329</v>
       </c>
       <c r="C21">
-        <v>2.080581218903203</v>
+        <v>2.067643154129319</v>
       </c>
       <c r="D21">
-        <v>2.402091218903203</v>
+        <v>2.409443154129319</v>
       </c>
       <c r="E21">
-        <v>-0.5834900000000001</v>
+        <v>-0.5631999999999999</v>
       </c>
       <c r="F21">
-        <v>0.38551</v>
+        <v>0.4058</v>
       </c>
       <c r="G21">
         <v>0.064</v>
@@ -3009,28 +3009,28 @@
         <v>0.445</v>
       </c>
       <c r="M21">
-        <v>0.019391153</v>
+        <v>0.02041174</v>
       </c>
       <c r="N21">
-        <v>0.425608847</v>
+        <v>0.42458826</v>
       </c>
       <c r="O21">
-        <v>0.10214612328</v>
+        <v>0.1019011824</v>
       </c>
       <c r="P21">
-        <v>0.32346272372</v>
+        <v>0.3226870776</v>
       </c>
       <c r="Q21">
-        <v>0.63946272372</v>
+        <v>0.6386870776</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2300996835912743</v>
+        <v>0.2319341837946661</v>
       </c>
       <c r="T21">
-        <v>0.9055329390933203</v>
+        <v>0.9145465213663574</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>22.94860960562789</v>
+        <v>21.80117912534649</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1931929470357329</v>
+        <v>0.1927418303625336</v>
       </c>
       <c r="C22">
-        <v>2.067643154129319</v>
+        <v>2.054750230763467</v>
       </c>
       <c r="D22">
-        <v>2.409443154129319</v>
+        <v>2.416840230763467</v>
       </c>
       <c r="E22">
-        <v>-0.5631999999999999</v>
+        <v>-0.54291</v>
       </c>
       <c r="F22">
-        <v>0.4058</v>
+        <v>0.42609</v>
       </c>
       <c r="G22">
         <v>0.064</v>
@@ -3091,28 +3091,28 @@
         <v>0.445</v>
       </c>
       <c r="M22">
-        <v>0.02041174</v>
+        <v>0.021432327</v>
       </c>
       <c r="N22">
-        <v>0.42458826</v>
+        <v>0.423567673</v>
       </c>
       <c r="O22">
-        <v>0.1019011824</v>
+        <v>0.10165624152</v>
       </c>
       <c r="P22">
-        <v>0.3226870776</v>
+        <v>0.32191143148</v>
       </c>
       <c r="Q22">
-        <v>0.6386870776</v>
+        <v>0.6379114314800001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2319341837946661</v>
+        <v>0.2338151270411817</v>
       </c>
       <c r="T22">
-        <v>0.9145465213663574</v>
+        <v>0.9237882955956739</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>21.80117912534649</v>
+        <v>20.76302773842523</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1927418303625336</v>
+        <v>0.1922907136893343</v>
       </c>
       <c r="C23">
-        <v>2.054750230763467</v>
+        <v>2.041902865843179</v>
       </c>
       <c r="D23">
-        <v>2.416840230763467</v>
+        <v>2.424282865843179</v>
       </c>
       <c r="E23">
-        <v>-0.54291</v>
+        <v>-0.52262</v>
       </c>
       <c r="F23">
-        <v>0.42609</v>
+        <v>0.44638</v>
       </c>
       <c r="G23">
         <v>0.064</v>
@@ -3173,28 +3173,28 @@
         <v>0.445</v>
       </c>
       <c r="M23">
-        <v>0.021432327</v>
+        <v>0.022452914</v>
       </c>
       <c r="N23">
-        <v>0.423567673</v>
+        <v>0.422547086</v>
       </c>
       <c r="O23">
-        <v>0.10165624152</v>
+        <v>0.10141130064</v>
       </c>
       <c r="P23">
-        <v>0.32191143148</v>
+        <v>0.32113578536</v>
       </c>
       <c r="Q23">
-        <v>0.6379114314800001</v>
+        <v>0.63713578536</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2338151270411817</v>
+        <v>0.2357442996017106</v>
       </c>
       <c r="T23">
-        <v>0.9237882955956739</v>
+        <v>0.9332670383949729</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>20.76302773842523</v>
+        <v>19.819253750315</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1922907136893343</v>
+        <v>0.1918395970161349</v>
       </c>
       <c r="C24">
-        <v>2.041902865843179</v>
+        <v>2.029101481558905</v>
       </c>
       <c r="D24">
-        <v>2.424282865843179</v>
+        <v>2.431771481558905</v>
       </c>
       <c r="E24">
-        <v>-0.52262</v>
+        <v>-0.5023299999999999</v>
       </c>
       <c r="F24">
-        <v>0.44638</v>
+        <v>0.46667</v>
       </c>
       <c r="G24">
         <v>0.064</v>
@@ -3255,28 +3255,28 @@
         <v>0.445</v>
       </c>
       <c r="M24">
-        <v>0.022452914</v>
+        <v>0.023473501</v>
       </c>
       <c r="N24">
-        <v>0.422547086</v>
+        <v>0.421526499</v>
       </c>
       <c r="O24">
-        <v>0.10141130064</v>
+        <v>0.10116635976</v>
       </c>
       <c r="P24">
-        <v>0.32113578536</v>
+        <v>0.32036013924</v>
       </c>
       <c r="Q24">
-        <v>0.63713578536</v>
+        <v>0.63636013924</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2357442996017106</v>
+        <v>0.237723580540435</v>
       </c>
       <c r="T24">
-        <v>0.9332670383949729</v>
+        <v>0.9429919823059419</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>19.819253750315</v>
+        <v>18.95754706551869</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1918395970161349</v>
+        <v>0.1913884803429356</v>
       </c>
       <c r="C25">
-        <v>2.029101481558905</v>
+        <v>2.016346505333848</v>
       </c>
       <c r="D25">
-        <v>2.431771481558905</v>
+        <v>2.439306505333848</v>
       </c>
       <c r="E25">
-        <v>-0.5023299999999999</v>
+        <v>-0.48204</v>
       </c>
       <c r="F25">
-        <v>0.46667</v>
+        <v>0.48696</v>
       </c>
       <c r="G25">
         <v>0.064</v>
@@ -3337,28 +3337,28 @@
         <v>0.445</v>
       </c>
       <c r="M25">
-        <v>0.023473501</v>
+        <v>0.024494088</v>
       </c>
       <c r="N25">
-        <v>0.421526499</v>
+        <v>0.420505912</v>
       </c>
       <c r="O25">
-        <v>0.10116635976</v>
+        <v>0.10092141888</v>
       </c>
       <c r="P25">
-        <v>0.32036013924</v>
+        <v>0.31958449312</v>
       </c>
       <c r="Q25">
-        <v>0.63636013924</v>
+        <v>0.63558449312</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.237723580540435</v>
+        <v>0.2397549478196521</v>
       </c>
       <c r="T25">
-        <v>0.9429919823059419</v>
+        <v>0.9529728457935154</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>18.95754706551869</v>
+        <v>18.16764927112208</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1913884803429356</v>
+        <v>0.1909373636697363</v>
       </c>
       <c r="C26">
-        <v>2.016346505333848</v>
+        <v>2.003638369905287</v>
       </c>
       <c r="D26">
-        <v>2.439306505333848</v>
+        <v>2.446888369905287</v>
       </c>
       <c r="E26">
-        <v>-0.48204</v>
+        <v>-0.46175</v>
       </c>
       <c r="F26">
-        <v>0.4869599999999999</v>
+        <v>0.50725</v>
       </c>
       <c r="G26">
         <v>0.064</v>
@@ -3419,28 +3419,28 @@
         <v>0.445</v>
       </c>
       <c r="M26">
-        <v>0.024494088</v>
+        <v>0.025514675</v>
       </c>
       <c r="N26">
-        <v>0.420505912</v>
+        <v>0.419485325</v>
       </c>
       <c r="O26">
-        <v>0.10092141888</v>
+        <v>0.100676478</v>
       </c>
       <c r="P26">
-        <v>0.31958449312</v>
+        <v>0.318808847</v>
       </c>
       <c r="Q26">
-        <v>0.63558449312</v>
+        <v>0.634808847</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2397549478196521</v>
+        <v>0.2418404848929817</v>
       </c>
       <c r="T26">
-        <v>0.9529728457935154</v>
+        <v>0.9632198656407575</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>18.16764927112208</v>
+        <v>17.4409433002772</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1909373636697363</v>
+        <v>0.1904862469965369</v>
       </c>
       <c r="C27">
-        <v>2.003638369905287</v>
+        <v>1.990977513407421</v>
       </c>
       <c r="D27">
-        <v>2.446888369905287</v>
+        <v>2.454517513407422</v>
       </c>
       <c r="E27">
-        <v>-0.46175</v>
+        <v>-0.44146</v>
       </c>
       <c r="F27">
-        <v>0.50725</v>
+        <v>0.52754</v>
       </c>
       <c r="G27">
         <v>0.064</v>
@@ -3501,28 +3501,28 @@
         <v>0.445</v>
       </c>
       <c r="M27">
-        <v>0.025514675</v>
+        <v>0.026535262</v>
       </c>
       <c r="N27">
-        <v>0.419485325</v>
+        <v>0.418464738</v>
       </c>
       <c r="O27">
-        <v>0.100676478</v>
+        <v>0.10043153712</v>
       </c>
       <c r="P27">
-        <v>0.318808847</v>
+        <v>0.31803320088</v>
       </c>
       <c r="Q27">
-        <v>0.634808847</v>
+        <v>0.63403320088</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2418404848929817</v>
+        <v>0.243982387833158</v>
       </c>
       <c r="T27">
-        <v>0.9632198656407575</v>
+        <v>0.9737438319703574</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>17.4409433002772</v>
+        <v>16.77013778872807</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1904862469965369</v>
+        <v>0.1900351303233376</v>
       </c>
       <c r="C28">
-        <v>1.990977513407421</v>
+        <v>1.978364379455767</v>
       </c>
       <c r="D28">
-        <v>2.454517513407422</v>
+        <v>2.462194379455767</v>
       </c>
       <c r="E28">
-        <v>-0.44146</v>
+        <v>-0.4211699999999999</v>
       </c>
       <c r="F28">
-        <v>0.52754</v>
+        <v>0.54783</v>
       </c>
       <c r="G28">
         <v>0.064</v>
@@ -3583,28 +3583,28 @@
         <v>0.445</v>
       </c>
       <c r="M28">
-        <v>0.026535262</v>
+        <v>0.027555849</v>
       </c>
       <c r="N28">
-        <v>0.418464738</v>
+        <v>0.417444151</v>
       </c>
       <c r="O28">
-        <v>0.10043153712</v>
+        <v>0.10018659624</v>
       </c>
       <c r="P28">
-        <v>0.31803320088</v>
+        <v>0.31725755476</v>
       </c>
       <c r="Q28">
-        <v>0.63403320088</v>
+        <v>0.63325755476</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.243982387833158</v>
+        <v>0.2461829730456679</v>
       </c>
       <c r="T28">
-        <v>0.9737438319703574</v>
+        <v>0.984556126144604</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>16.77013778872807</v>
+        <v>16.14902157433073</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1900351303233376</v>
+        <v>0.1895840136501383</v>
       </c>
       <c r="C29">
-        <v>1.978364379455767</v>
+        <v>1.965799417233143</v>
       </c>
       <c r="D29">
-        <v>2.462194379455767</v>
+        <v>2.469919417233143</v>
       </c>
       <c r="E29">
-        <v>-0.4211699999999999</v>
+        <v>-0.4008799999999999</v>
       </c>
       <c r="F29">
-        <v>0.54783</v>
+        <v>0.5681200000000001</v>
       </c>
       <c r="G29">
         <v>0.064</v>
@@ -3665,28 +3665,28 @@
         <v>0.445</v>
       </c>
       <c r="M29">
-        <v>0.027555849</v>
+        <v>0.028576436</v>
       </c>
       <c r="N29">
-        <v>0.417444151</v>
+        <v>0.416423564</v>
       </c>
       <c r="O29">
-        <v>0.10018659624</v>
+        <v>0.09994165536000001</v>
       </c>
       <c r="P29">
-        <v>0.31725755476</v>
+        <v>0.31648190864</v>
       </c>
       <c r="Q29">
-        <v>0.63325755476</v>
+        <v>0.63248190864</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2461829730456679</v>
+        <v>0.2484446856251921</v>
       </c>
       <c r="T29">
-        <v>0.984556126144604</v>
+        <v>0.9956687618236908</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>16.14902157433073</v>
+        <v>15.57227080381892</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1895840136501383</v>
+        <v>0.189132896976939</v>
       </c>
       <c r="C30">
-        <v>1.965799417233143</v>
+        <v>1.953283081577287</v>
       </c>
       <c r="D30">
-        <v>2.469919417233143</v>
+        <v>2.477693081577288</v>
       </c>
       <c r="E30">
-        <v>-0.4008799999999999</v>
+        <v>-0.3805899999999999</v>
       </c>
       <c r="F30">
-        <v>0.5681200000000001</v>
+        <v>0.5884100000000001</v>
       </c>
       <c r="G30">
         <v>0.064</v>
@@ -3747,28 +3747,28 @@
         <v>0.445</v>
       </c>
       <c r="M30">
-        <v>0.028576436</v>
+        <v>0.029597023</v>
       </c>
       <c r="N30">
-        <v>0.416423564</v>
+        <v>0.415402977</v>
       </c>
       <c r="O30">
-        <v>0.09994165536000001</v>
+        <v>0.09969671448</v>
       </c>
       <c r="P30">
-        <v>0.31648190864</v>
+        <v>0.31570626252</v>
       </c>
       <c r="Q30">
-        <v>0.63248190864</v>
+        <v>0.6317062625200001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2484446856251921</v>
+        <v>0.2507701084182239</v>
       </c>
       <c r="T30">
-        <v>0.9956687618236908</v>
+        <v>1.007094429493738</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>15.57227080381892</v>
+        <v>15.03529594851482</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.189132896976939</v>
+        <v>0.1886817803037396</v>
       </c>
       <c r="C31">
-        <v>1.953283081577287</v>
+        <v>1.940815833070125</v>
       </c>
       <c r="D31">
-        <v>2.477693081577288</v>
+        <v>2.485515833070124</v>
       </c>
       <c r="E31">
-        <v>-0.38059</v>
+        <v>-0.3603000000000001</v>
       </c>
       <c r="F31">
-        <v>0.58841</v>
+        <v>0.6086999999999999</v>
       </c>
       <c r="G31">
         <v>0.064</v>
@@ -3829,28 +3829,28 @@
         <v>0.445</v>
       </c>
       <c r="M31">
-        <v>0.029597023</v>
+        <v>0.03061760999999999</v>
       </c>
       <c r="N31">
-        <v>0.415402977</v>
+        <v>0.41438239</v>
       </c>
       <c r="O31">
-        <v>0.09969671448</v>
+        <v>0.09945177359999999</v>
       </c>
       <c r="P31">
-        <v>0.31570626252</v>
+        <v>0.3149306164</v>
       </c>
       <c r="Q31">
-        <v>0.6317062625200001</v>
+        <v>0.6309306163999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2507701084182239</v>
+        <v>0.2531619718624852</v>
       </c>
       <c r="T31">
-        <v>1.007094429493738</v>
+        <v>1.0188465448115</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>15.03529594851482</v>
+        <v>14.53411941689766</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1886817803037396</v>
+        <v>0.1882306636305403</v>
       </c>
       <c r="C32">
-        <v>1.940815833070125</v>
+        <v>1.928398138128727</v>
       </c>
       <c r="D32">
-        <v>2.485515833070124</v>
+        <v>2.493388138128727</v>
       </c>
       <c r="E32">
-        <v>-0.3603000000000001</v>
+        <v>-0.34001</v>
       </c>
       <c r="F32">
-        <v>0.6086999999999999</v>
+        <v>0.6289899999999999</v>
       </c>
       <c r="G32">
         <v>0.064</v>
@@ -3911,28 +3911,28 @@
         <v>0.445</v>
       </c>
       <c r="M32">
-        <v>0.03061760999999999</v>
+        <v>0.03163819699999999</v>
       </c>
       <c r="N32">
-        <v>0.41438239</v>
+        <v>0.413361803</v>
       </c>
       <c r="O32">
-        <v>0.09945177359999999</v>
+        <v>0.09920683272</v>
       </c>
       <c r="P32">
-        <v>0.3149306164</v>
+        <v>0.3141549702800001</v>
       </c>
       <c r="Q32">
-        <v>0.6309306163999999</v>
+        <v>0.63015497028</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2531619718624852</v>
+        <v>0.2556231646819425</v>
       </c>
       <c r="T32">
-        <v>1.0188465448115</v>
+        <v>1.030939301152966</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>14.53411941689766</v>
+        <v>14.06527685506226</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1882306636305403</v>
+        <v>0.1877795469573409</v>
       </c>
       <c r="C33">
-        <v>1.928398138128727</v>
+        <v>1.916030469098027</v>
       </c>
       <c r="D33">
-        <v>2.493388138128727</v>
+        <v>2.501310469098027</v>
       </c>
       <c r="E33">
-        <v>-0.34001</v>
+        <v>-0.31972</v>
       </c>
       <c r="F33">
-        <v>0.6289899999999999</v>
+        <v>0.64928</v>
       </c>
       <c r="G33">
         <v>0.064</v>
@@ -3993,28 +3993,28 @@
         <v>0.445</v>
       </c>
       <c r="M33">
-        <v>0.03163819699999999</v>
+        <v>0.032658784</v>
       </c>
       <c r="N33">
-        <v>0.413361803</v>
+        <v>0.412341216</v>
       </c>
       <c r="O33">
-        <v>0.09920683272</v>
+        <v>0.09896189184</v>
       </c>
       <c r="P33">
-        <v>0.3141549702800001</v>
+        <v>0.31337932416</v>
       </c>
       <c r="Q33">
-        <v>0.63015497028</v>
+        <v>0.6293793241600001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2556231646819425</v>
+        <v>0.2581567455255014</v>
       </c>
       <c r="T33">
-        <v>1.030939301152966</v>
+        <v>1.043387726798593</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>14.06527685506226</v>
+        <v>13.62573695334156</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1877795469573409</v>
+        <v>0.1873284302841416</v>
       </c>
       <c r="C34">
-        <v>1.916030469098027</v>
+        <v>1.903713304345283</v>
       </c>
       <c r="D34">
-        <v>2.501310469098027</v>
+        <v>2.509283304345283</v>
       </c>
       <c r="E34">
-        <v>-0.31972</v>
+        <v>-0.29943</v>
       </c>
       <c r="F34">
-        <v>0.64928</v>
+        <v>0.66957</v>
       </c>
       <c r="G34">
         <v>0.064</v>
@@ -4075,28 +4075,28 @@
         <v>0.445</v>
       </c>
       <c r="M34">
-        <v>0.032658784</v>
+        <v>0.033679371</v>
       </c>
       <c r="N34">
-        <v>0.412341216</v>
+        <v>0.411320629</v>
       </c>
       <c r="O34">
-        <v>0.09896189184</v>
+        <v>0.09871695095999999</v>
       </c>
       <c r="P34">
-        <v>0.31337932416</v>
+        <v>0.31260367804</v>
       </c>
       <c r="Q34">
-        <v>0.6293793241600001</v>
+        <v>0.6286036780399999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2581567455255014</v>
+        <v>0.2607659556479726</v>
       </c>
       <c r="T34">
-        <v>1.043387726798593</v>
+        <v>1.056207747239611</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>13.62573695334156</v>
+        <v>13.21283583354333</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1873284302841416</v>
+        <v>0.1872649136109423</v>
       </c>
       <c r="C35">
-        <v>1.903713304345283</v>
+        <v>1.884549953516009</v>
       </c>
       <c r="D35">
-        <v>2.509283304345283</v>
+        <v>2.510409953516008</v>
       </c>
       <c r="E35">
-        <v>-0.29943</v>
+        <v>-0.2791399999999999</v>
       </c>
       <c r="F35">
-        <v>0.66957</v>
+        <v>0.68986</v>
       </c>
       <c r="G35">
         <v>0.064</v>
@@ -4157,45 +4157,45 @@
         <v>0.445</v>
       </c>
       <c r="M35">
-        <v>0.033679371</v>
+        <v>0.035734748</v>
       </c>
       <c r="N35">
-        <v>0.411320629</v>
+        <v>0.409265252</v>
       </c>
       <c r="O35">
-        <v>0.09871695095999999</v>
+        <v>0.09822366048</v>
       </c>
       <c r="P35">
-        <v>0.31260367804</v>
+        <v>0.31104159152</v>
       </c>
       <c r="Q35">
-        <v>0.6286036780399999</v>
+        <v>0.6270415915200001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2607659556479726</v>
+        <v>0.263454232743852</v>
       </c>
       <c r="T35">
-        <v>1.056207747239611</v>
+        <v>1.069416253148539</v>
       </c>
       <c r="U35">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V35">
         <v>0.24</v>
       </c>
       <c r="W35">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y35">
-        <v>13.21283583354333</v>
+        <v>12.45286520559764</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1872649136109423</v>
+        <v>0.186825196937743</v>
       </c>
       <c r="C36">
-        <v>1.884549953516009</v>
+        <v>1.872087413694021</v>
       </c>
       <c r="D36">
-        <v>2.510409953516008</v>
+        <v>2.518237413694021</v>
       </c>
       <c r="E36">
-        <v>-0.2791399999999999</v>
+        <v>-0.2588499999999999</v>
       </c>
       <c r="F36">
-        <v>0.68986</v>
+        <v>0.7101500000000001</v>
       </c>
       <c r="G36">
         <v>0.064</v>
@@ -4239,28 +4239,28 @@
         <v>0.445</v>
       </c>
       <c r="M36">
-        <v>0.035734748</v>
+        <v>0.03678577</v>
       </c>
       <c r="N36">
-        <v>0.409265252</v>
+        <v>0.40821423</v>
       </c>
       <c r="O36">
-        <v>0.09822366048</v>
+        <v>0.09797141519999999</v>
       </c>
       <c r="P36">
-        <v>0.31104159152</v>
+        <v>0.3102428148</v>
       </c>
       <c r="Q36">
-        <v>0.6270415915200001</v>
+        <v>0.6262428148000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.263454232743852</v>
+        <v>0.2662252260580661</v>
       </c>
       <c r="T36">
-        <v>1.069416253148539</v>
+        <v>1.083031174623896</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>12.45286520559764</v>
+        <v>12.09706905686628</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.186825196937743</v>
+        <v>0.1863854802645437</v>
       </c>
       <c r="C37">
-        <v>1.872087413694021</v>
+        <v>1.859673838597872</v>
       </c>
       <c r="D37">
-        <v>2.518237413694021</v>
+        <v>2.526113838597873</v>
       </c>
       <c r="E37">
-        <v>-0.2588499999999999</v>
+        <v>-0.2385599999999999</v>
       </c>
       <c r="F37">
-        <v>0.7101500000000001</v>
+        <v>0.7304400000000001</v>
       </c>
       <c r="G37">
         <v>0.064</v>
@@ -4321,28 +4321,28 @@
         <v>0.445</v>
       </c>
       <c r="M37">
-        <v>0.03678577</v>
+        <v>0.037836792</v>
       </c>
       <c r="N37">
-        <v>0.40821423</v>
+        <v>0.407163208</v>
       </c>
       <c r="O37">
-        <v>0.09797141519999999</v>
+        <v>0.09771916992</v>
       </c>
       <c r="P37">
-        <v>0.3102428148</v>
+        <v>0.30944403808</v>
       </c>
       <c r="Q37">
-        <v>0.6262428148000001</v>
+        <v>0.6254440380799999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2662252260580661</v>
+        <v>0.2690828129133495</v>
       </c>
       <c r="T37">
-        <v>1.083031174623896</v>
+        <v>1.097071562395358</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>12.09706905686628</v>
+        <v>11.76103936084222</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1863854802645436</v>
+        <v>0.1859457635913443</v>
       </c>
       <c r="C38">
-        <v>1.859673838597873</v>
+        <v>1.847309689117836</v>
       </c>
       <c r="D38">
-        <v>2.526113838597873</v>
+        <v>2.534039689117836</v>
       </c>
       <c r="E38">
-        <v>-0.23856</v>
+        <v>-0.21827</v>
       </c>
       <c r="F38">
-        <v>0.73044</v>
+        <v>0.75073</v>
       </c>
       <c r="G38">
         <v>0.064</v>
@@ -4403,28 +4403,28 @@
         <v>0.445</v>
       </c>
       <c r="M38">
-        <v>0.037836792</v>
+        <v>0.038887814</v>
       </c>
       <c r="N38">
-        <v>0.407163208</v>
+        <v>0.406112186</v>
       </c>
       <c r="O38">
-        <v>0.09771916992</v>
+        <v>0.09746692463999999</v>
       </c>
       <c r="P38">
-        <v>0.30944403808</v>
+        <v>0.30864526136</v>
       </c>
       <c r="Q38">
-        <v>0.6254440380799999</v>
+        <v>0.62464526136</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2690828129133495</v>
+        <v>0.2720311168116576</v>
       </c>
       <c r="T38">
-        <v>1.097071562395357</v>
+        <v>1.111557676762738</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>11.76103936084222</v>
+        <v>11.44317343217081</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1859457635913443</v>
+        <v>0.185506046918145</v>
       </c>
       <c r="C39">
-        <v>1.847309689117836</v>
+        <v>1.834995431946683</v>
       </c>
       <c r="D39">
-        <v>2.534039689117836</v>
+        <v>2.542015431946683</v>
       </c>
       <c r="E39">
-        <v>-0.21827</v>
+        <v>-0.19798</v>
       </c>
       <c r="F39">
-        <v>0.75073</v>
+        <v>0.7710199999999999</v>
       </c>
       <c r="G39">
         <v>0.064</v>
@@ -4485,28 +4485,28 @@
         <v>0.445</v>
       </c>
       <c r="M39">
-        <v>0.038887814</v>
+        <v>0.039938836</v>
       </c>
       <c r="N39">
-        <v>0.406112186</v>
+        <v>0.405061164</v>
       </c>
       <c r="O39">
-        <v>0.09746692463999999</v>
+        <v>0.09721467936</v>
       </c>
       <c r="P39">
-        <v>0.30864526136</v>
+        <v>0.30784648464</v>
       </c>
       <c r="Q39">
-        <v>0.62464526136</v>
+        <v>0.62384648464</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2720311168116576</v>
+        <v>0.2750745272873306</v>
       </c>
       <c r="T39">
-        <v>1.111557676762738</v>
+        <v>1.12651108514197</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>11.44317343217081</v>
+        <v>11.14203728921895</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.185506046918145</v>
+        <v>0.1850663302449457</v>
       </c>
       <c r="C40">
-        <v>1.834995431946683</v>
+        <v>1.822731539671291</v>
       </c>
       <c r="D40">
-        <v>2.542015431946683</v>
+        <v>2.550041539671291</v>
       </c>
       <c r="E40">
-        <v>-0.19798</v>
+        <v>-0.17769</v>
       </c>
       <c r="F40">
-        <v>0.7710199999999999</v>
+        <v>0.79131</v>
       </c>
       <c r="G40">
         <v>0.064</v>
@@ -4567,28 +4567,28 @@
         <v>0.445</v>
       </c>
       <c r="M40">
-        <v>0.039938836</v>
+        <v>0.040989858</v>
       </c>
       <c r="N40">
-        <v>0.405061164</v>
+        <v>0.404010142</v>
       </c>
       <c r="O40">
-        <v>0.09721467936</v>
+        <v>0.09696243408000001</v>
       </c>
       <c r="P40">
-        <v>0.30784648464</v>
+        <v>0.30704770792</v>
       </c>
       <c r="Q40">
-        <v>0.62384648464</v>
+        <v>0.6230477079200001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2750745272873306</v>
+        <v>0.2782177217130257</v>
       </c>
       <c r="T40">
-        <v>1.12651108514197</v>
+        <v>1.141954769205767</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>11.14203728921895</v>
+        <v>10.85634402539282</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1850663302449457</v>
+        <v>0.1846266135717463</v>
       </c>
       <c r="C41">
-        <v>1.822731539671291</v>
+        <v>1.810518490865991</v>
       </c>
       <c r="D41">
-        <v>2.550041539671291</v>
+        <v>2.558118490865991</v>
       </c>
       <c r="E41">
-        <v>-0.17769</v>
+        <v>-0.1574</v>
       </c>
       <c r="F41">
-        <v>0.79131</v>
+        <v>0.8116</v>
       </c>
       <c r="G41">
         <v>0.064</v>
@@ -4649,28 +4649,28 @@
         <v>0.445</v>
       </c>
       <c r="M41">
-        <v>0.040989858</v>
+        <v>0.04204088</v>
       </c>
       <c r="N41">
-        <v>0.404010142</v>
+        <v>0.40295912</v>
       </c>
       <c r="O41">
-        <v>0.09696243408000001</v>
+        <v>0.0967101888</v>
       </c>
       <c r="P41">
-        <v>0.30704770792</v>
+        <v>0.3062489312</v>
       </c>
       <c r="Q41">
-        <v>0.6230477079200001</v>
+        <v>0.6222489312</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2782177217130257</v>
+        <v>0.2814656892862439</v>
       </c>
       <c r="T41">
-        <v>1.141954769205767</v>
+        <v>1.157913242738357</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>10.85634402539282</v>
+        <v>10.584935424758</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1846266135717463</v>
+        <v>0.184186896898547</v>
       </c>
       <c r="C42">
-        <v>1.810518490865991</v>
+        <v>1.79835677018768</v>
       </c>
       <c r="D42">
-        <v>2.558118490865991</v>
+        <v>2.56624677018768</v>
       </c>
       <c r="E42">
-        <v>-0.1574</v>
+        <v>-0.13711</v>
       </c>
       <c r="F42">
-        <v>0.8116</v>
+        <v>0.83189</v>
       </c>
       <c r="G42">
         <v>0.064</v>
@@ -4731,28 +4731,28 @@
         <v>0.445</v>
       </c>
       <c r="M42">
-        <v>0.04204088</v>
+        <v>0.043091902</v>
       </c>
       <c r="N42">
-        <v>0.40295912</v>
+        <v>0.401908098</v>
       </c>
       <c r="O42">
-        <v>0.0967101888</v>
+        <v>0.09645794351999999</v>
       </c>
       <c r="P42">
-        <v>0.3062489312</v>
+        <v>0.30545015448</v>
       </c>
       <c r="Q42">
-        <v>0.6222489312</v>
+        <v>0.62145015448</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2814656892862439</v>
+        <v>0.2848237574551645</v>
       </c>
       <c r="T42">
-        <v>1.157913242738357</v>
+        <v>1.174412681475442</v>
       </c>
       <c r="U42">
         <v>0.0518</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>10.584935424758</v>
+        <v>10.32676626805658</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.184186896898547</v>
+        <v>0.1837471802253477</v>
       </c>
       <c r="C43">
-        <v>1.79835677018768</v>
+        <v>1.786246868472778</v>
       </c>
       <c r="D43">
-        <v>2.56624677018768</v>
+        <v>2.574426868472778</v>
       </c>
       <c r="E43">
-        <v>-0.13711</v>
+        <v>-0.1168199999999999</v>
       </c>
       <c r="F43">
-        <v>0.83189</v>
+        <v>0.85218</v>
       </c>
       <c r="G43">
         <v>0.064</v>
@@ -4813,28 +4813,28 @@
         <v>0.445</v>
       </c>
       <c r="M43">
-        <v>0.043091902</v>
+        <v>0.044142924</v>
       </c>
       <c r="N43">
-        <v>0.401908098</v>
+        <v>0.400857076</v>
       </c>
       <c r="O43">
-        <v>0.09645794351999999</v>
+        <v>0.09620569824</v>
       </c>
       <c r="P43">
-        <v>0.30545015448</v>
+        <v>0.30465137776</v>
       </c>
       <c r="Q43">
-        <v>0.62145015448</v>
+        <v>0.62065137776</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2848237574551645</v>
+        <v>0.2882976210781857</v>
       </c>
       <c r="T43">
-        <v>1.174412681475442</v>
+        <v>1.191481066375875</v>
       </c>
       <c r="U43">
         <v>0.0518</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>10.32676626805658</v>
+        <v>10.0808908807219</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1837471802253477</v>
+        <v>0.1833074635521484</v>
       </c>
       <c r="C44">
-        <v>1.786246868472778</v>
+        <v>1.774189282836021</v>
       </c>
       <c r="D44">
-        <v>2.574426868472778</v>
+        <v>2.58265928283602</v>
       </c>
       <c r="E44">
-        <v>-0.11682</v>
+        <v>-0.09653</v>
       </c>
       <c r="F44">
-        <v>0.8521799999999999</v>
+        <v>0.87247</v>
       </c>
       <c r="G44">
         <v>0.064</v>
@@ -4895,28 +4895,28 @@
         <v>0.445</v>
       </c>
       <c r="M44">
-        <v>0.04414292399999999</v>
+        <v>0.045193946</v>
       </c>
       <c r="N44">
-        <v>0.400857076</v>
+        <v>0.399806054</v>
       </c>
       <c r="O44">
-        <v>0.09620569824</v>
+        <v>0.09595345296</v>
       </c>
       <c r="P44">
-        <v>0.3046513777600001</v>
+        <v>0.30385260104</v>
       </c>
       <c r="Q44">
-        <v>0.62065137776</v>
+        <v>0.6198526010400001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2882976210781857</v>
+        <v>0.2918933746528919</v>
       </c>
       <c r="T44">
-        <v>1.191481066375875</v>
+        <v>1.209148341974568</v>
       </c>
       <c r="U44">
         <v>0.0518</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>10.0808908807219</v>
+        <v>9.846451557914417</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1833074635521484</v>
+        <v>0.1834362268789491</v>
       </c>
       <c r="C45">
-        <v>1.774189282836021</v>
+        <v>1.751483118074812</v>
       </c>
       <c r="D45">
-        <v>2.58265928283602</v>
+        <v>2.580243118074812</v>
       </c>
       <c r="E45">
-        <v>-0.09653</v>
+        <v>-0.07623999999999997</v>
       </c>
       <c r="F45">
-        <v>0.87247</v>
+        <v>0.89276</v>
       </c>
       <c r="G45">
         <v>0.064</v>
@@ -4977,45 +4977,45 @@
         <v>0.445</v>
       </c>
       <c r="M45">
-        <v>0.045193946</v>
+        <v>0.04776266</v>
       </c>
       <c r="N45">
-        <v>0.399806054</v>
+        <v>0.39723734</v>
       </c>
       <c r="O45">
-        <v>0.09595345296</v>
+        <v>0.09533696159999999</v>
       </c>
       <c r="P45">
-        <v>0.30385260104</v>
+        <v>0.3019003784</v>
       </c>
       <c r="Q45">
-        <v>0.6198526010400001</v>
+        <v>0.6179003784</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2918933746528919</v>
+        <v>0.2956175479981233</v>
       </c>
       <c r="T45">
-        <v>1.209148341974568</v>
+        <v>1.227446591701786</v>
       </c>
       <c r="U45">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V45">
         <v>0.24</v>
       </c>
       <c r="W45">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>9.846451557914417</v>
+        <v>9.316901529353684</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1834362268789491</v>
+        <v>0.1830094302057497</v>
       </c>
       <c r="C46">
-        <v>1.751483118074812</v>
+        <v>1.739219091050492</v>
       </c>
       <c r="D46">
-        <v>2.580243118074812</v>
+        <v>2.588269091050492</v>
       </c>
       <c r="E46">
-        <v>-0.07623999999999997</v>
+        <v>-0.05594999999999994</v>
       </c>
       <c r="F46">
-        <v>0.89276</v>
+        <v>0.91305</v>
       </c>
       <c r="G46">
         <v>0.064</v>
@@ -5059,28 +5059,28 @@
         <v>0.445</v>
       </c>
       <c r="M46">
-        <v>0.04776266</v>
+        <v>0.048848175</v>
       </c>
       <c r="N46">
-        <v>0.39723734</v>
+        <v>0.396151825</v>
       </c>
       <c r="O46">
-        <v>0.09533696159999999</v>
+        <v>0.095076438</v>
       </c>
       <c r="P46">
-        <v>0.3019003784</v>
+        <v>0.301075387</v>
       </c>
       <c r="Q46">
-        <v>0.6179003784</v>
+        <v>0.6170753870000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2956175479981233</v>
+        <v>0.2994771458286358</v>
       </c>
       <c r="T46">
-        <v>1.227446591701786</v>
+        <v>1.246410232328175</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>9.316901529353684</v>
+        <v>9.109859273145824</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1830094302057497</v>
+        <v>0.1825826335325504</v>
       </c>
       <c r="C47">
-        <v>1.739219091050492</v>
+        <v>1.727005150188088</v>
       </c>
       <c r="D47">
-        <v>2.588269091050492</v>
+        <v>2.596345150188088</v>
       </c>
       <c r="E47">
-        <v>-0.05594999999999994</v>
+        <v>-0.03566000000000003</v>
       </c>
       <c r="F47">
-        <v>0.91305</v>
+        <v>0.9333399999999999</v>
       </c>
       <c r="G47">
         <v>0.064</v>
@@ -5141,28 +5141,28 @@
         <v>0.445</v>
       </c>
       <c r="M47">
-        <v>0.048848175</v>
+        <v>0.04993369</v>
       </c>
       <c r="N47">
-        <v>0.396151825</v>
+        <v>0.39506631</v>
       </c>
       <c r="O47">
-        <v>0.095076438</v>
+        <v>0.09481591440000001</v>
       </c>
       <c r="P47">
-        <v>0.301075387</v>
+        <v>0.3002503956</v>
       </c>
       <c r="Q47">
-        <v>0.6170753870000001</v>
+        <v>0.6162503956000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2994771458286358</v>
+        <v>0.3034796917269452</v>
       </c>
       <c r="T47">
-        <v>1.246410232328175</v>
+        <v>1.266076230014802</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>9.109859273145824</v>
+        <v>8.911818854164395</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1825826335325504</v>
+        <v>0.1821558368593511</v>
       </c>
       <c r="C48">
-        <v>1.727005150188088</v>
+        <v>1.714841765799861</v>
       </c>
       <c r="D48">
-        <v>2.596345150188088</v>
+        <v>2.604471765799861</v>
       </c>
       <c r="E48">
-        <v>-0.03566000000000003</v>
+        <v>-0.01536999999999999</v>
       </c>
       <c r="F48">
-        <v>0.9333399999999999</v>
+        <v>0.95363</v>
       </c>
       <c r="G48">
         <v>0.064</v>
@@ -5223,28 +5223,28 @@
         <v>0.445</v>
       </c>
       <c r="M48">
-        <v>0.04993369</v>
+        <v>0.051019205</v>
       </c>
       <c r="N48">
-        <v>0.39506631</v>
+        <v>0.393980795</v>
       </c>
       <c r="O48">
-        <v>0.09481591440000001</v>
+        <v>0.0945553908</v>
       </c>
       <c r="P48">
-        <v>0.3002503956</v>
+        <v>0.2994254042</v>
       </c>
       <c r="Q48">
-        <v>0.6162503956000001</v>
+        <v>0.6154254042</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.3034796917269452</v>
+        <v>0.3076332770931152</v>
       </c>
       <c r="T48">
-        <v>1.266076230014802</v>
+        <v>1.286484340821678</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>8.911818854164395</v>
+        <v>8.722205687054512</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1821558368593511</v>
+        <v>0.1817290401861517</v>
       </c>
       <c r="C49">
-        <v>1.714841765799861</v>
+        <v>1.702729414104908</v>
       </c>
       <c r="D49">
-        <v>2.604471765799861</v>
+        <v>2.612649414104908</v>
       </c>
       <c r="E49">
-        <v>-0.01536999999999999</v>
+        <v>0.004920000000000035</v>
       </c>
       <c r="F49">
-        <v>0.95363</v>
+        <v>0.97392</v>
       </c>
       <c r="G49">
         <v>0.064</v>
@@ -5305,28 +5305,28 @@
         <v>0.445</v>
       </c>
       <c r="M49">
-        <v>0.051019205</v>
+        <v>0.05210472</v>
       </c>
       <c r="N49">
-        <v>0.393980795</v>
+        <v>0.39289528</v>
       </c>
       <c r="O49">
-        <v>0.0945553908</v>
+        <v>0.09429486719999999</v>
       </c>
       <c r="P49">
-        <v>0.2994254042</v>
+        <v>0.2986004128</v>
       </c>
       <c r="Q49">
-        <v>0.6154254042</v>
+        <v>0.6146004128</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.3076332770931152</v>
+        <v>0.3119466157425995</v>
       </c>
       <c r="T49">
-        <v>1.286484340821678</v>
+        <v>1.30767737896728</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>8.722205687054512</v>
+        <v>8.540493068574211</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1817290401861517</v>
+        <v>0.1813022435129524</v>
       </c>
       <c r="C50">
-        <v>1.702729414104908</v>
+        <v>1.690668577322191</v>
       </c>
       <c r="D50">
-        <v>2.612649414104908</v>
+        <v>2.620878577322191</v>
       </c>
       <c r="E50">
-        <v>0.004919999999999924</v>
+        <v>0.02520999999999995</v>
       </c>
       <c r="F50">
-        <v>0.9739199999999999</v>
+        <v>0.9942099999999999</v>
       </c>
       <c r="G50">
         <v>0.064</v>
@@ -5387,28 +5387,28 @@
         <v>0.445</v>
       </c>
       <c r="M50">
-        <v>0.05210471999999999</v>
+        <v>0.053190235</v>
       </c>
       <c r="N50">
-        <v>0.39289528</v>
+        <v>0.391809765</v>
       </c>
       <c r="O50">
-        <v>0.09429486719999999</v>
+        <v>0.0940343436</v>
       </c>
       <c r="P50">
-        <v>0.2986004128</v>
+        <v>0.2977754214</v>
       </c>
       <c r="Q50">
-        <v>0.6146004128</v>
+        <v>0.6137754214</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.3119466157425995</v>
+        <v>0.3164291049273577</v>
       </c>
       <c r="T50">
-        <v>1.30767737896728</v>
+        <v>1.329701516648004</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>8.540493068574211</v>
+        <v>8.366197291664534</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1813022435129524</v>
+        <v>0.1808754468397531</v>
       </c>
       <c r="C51">
-        <v>1.690668577322191</v>
+        <v>1.678659743765324</v>
       </c>
       <c r="D51">
-        <v>2.620878577322191</v>
+        <v>2.629159743765324</v>
       </c>
       <c r="E51">
-        <v>0.02520999999999995</v>
+        <v>0.04549999999999998</v>
       </c>
       <c r="F51">
-        <v>0.9942099999999999</v>
+        <v>1.0145</v>
       </c>
       <c r="G51">
         <v>0.064</v>
@@ -5469,28 +5469,28 @@
         <v>0.445</v>
       </c>
       <c r="M51">
-        <v>0.053190235</v>
+        <v>0.05427575</v>
       </c>
       <c r="N51">
-        <v>0.391809765</v>
+        <v>0.39072425</v>
       </c>
       <c r="O51">
-        <v>0.0940343436</v>
+        <v>0.09377381999999999</v>
       </c>
       <c r="P51">
-        <v>0.2977754214</v>
+        <v>0.29695043</v>
       </c>
       <c r="Q51">
-        <v>0.6137754214</v>
+        <v>0.6129504299999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.3164291049273577</v>
+        <v>0.3210908936795062</v>
       </c>
       <c r="T51">
-        <v>1.329701516648004</v>
+        <v>1.352606619835957</v>
       </c>
       <c r="U51">
         <v>0.0535</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>8.366197291664534</v>
+        <v>8.198873345831242</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1808754468397531</v>
+        <v>0.1804486501665538</v>
       </c>
       <c r="C52">
-        <v>1.678659743765324</v>
+        <v>1.666703407939161</v>
       </c>
       <c r="D52">
-        <v>2.629159743765324</v>
+        <v>2.637493407939161</v>
       </c>
       <c r="E52">
-        <v>0.04549999999999998</v>
+        <v>0.0657899999999999</v>
       </c>
       <c r="F52">
-        <v>1.0145</v>
+        <v>1.03479</v>
       </c>
       <c r="G52">
         <v>0.064</v>
@@ -5551,28 +5551,28 @@
         <v>0.445</v>
       </c>
       <c r="M52">
-        <v>0.05427575</v>
+        <v>0.05536126499999999</v>
       </c>
       <c r="N52">
-        <v>0.39072425</v>
+        <v>0.389638735</v>
       </c>
       <c r="O52">
-        <v>0.09377381999999999</v>
+        <v>0.0935132964</v>
       </c>
       <c r="P52">
-        <v>0.29695043</v>
+        <v>0.2961254386</v>
       </c>
       <c r="Q52">
-        <v>0.6129504299999999</v>
+        <v>0.6121254386</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.3210908936795062</v>
+        <v>0.3259429595235791</v>
       </c>
       <c r="T52">
-        <v>1.352606619835957</v>
+        <v>1.376446625194847</v>
       </c>
       <c r="U52">
         <v>0.0535</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>8.198873345831242</v>
+        <v>8.038111123363963</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1804486501665538</v>
+        <v>0.1800218534933544</v>
       </c>
       <c r="C53">
-        <v>1.666703407939161</v>
+        <v>1.654800070638238</v>
       </c>
       <c r="D53">
-        <v>2.637493407939161</v>
+        <v>2.645880070638238</v>
       </c>
       <c r="E53">
-        <v>0.0657899999999999</v>
+        <v>0.08608000000000005</v>
       </c>
       <c r="F53">
-        <v>1.03479</v>
+        <v>1.05508</v>
       </c>
       <c r="G53">
         <v>0.064</v>
@@ -5633,28 +5633,28 @@
         <v>0.445</v>
       </c>
       <c r="M53">
-        <v>0.05536126499999999</v>
+        <v>0.05644678</v>
       </c>
       <c r="N53">
-        <v>0.389638735</v>
+        <v>0.38855322</v>
       </c>
       <c r="O53">
-        <v>0.0935132964</v>
+        <v>0.09325277280000001</v>
       </c>
       <c r="P53">
-        <v>0.2961254386</v>
+        <v>0.2953004472</v>
       </c>
       <c r="Q53">
-        <v>0.6121254386</v>
+        <v>0.6113004472000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.3259429595235791</v>
+        <v>0.3309971947778217</v>
       </c>
       <c r="T53">
-        <v>1.376446625194847</v>
+        <v>1.401279964110357</v>
       </c>
       <c r="U53">
         <v>0.0535</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>8.038111123363963</v>
+        <v>7.88353206329927</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1800218534933544</v>
+        <v>0.1795950568201551</v>
       </c>
       <c r="C54">
-        <v>1.654800070638238</v>
+        <v>1.64295023904708</v>
       </c>
       <c r="D54">
-        <v>2.645880070638238</v>
+        <v>2.65432023904708</v>
       </c>
       <c r="E54">
-        <v>0.08608000000000005</v>
+        <v>0.10637</v>
       </c>
       <c r="F54">
-        <v>1.05508</v>
+        <v>1.07537</v>
       </c>
       <c r="G54">
         <v>0.064</v>
@@ -5715,28 +5715,28 @@
         <v>0.445</v>
       </c>
       <c r="M54">
-        <v>0.05644678</v>
+        <v>0.057532295</v>
       </c>
       <c r="N54">
-        <v>0.38855322</v>
+        <v>0.387467705</v>
       </c>
       <c r="O54">
-        <v>0.09325277280000001</v>
+        <v>0.0929922492</v>
       </c>
       <c r="P54">
-        <v>0.2953004472</v>
+        <v>0.2944754558</v>
       </c>
       <c r="Q54">
-        <v>0.6113004472000001</v>
+        <v>0.6104754558000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.3309971947778217</v>
+        <v>0.3362665038726704</v>
       </c>
       <c r="T54">
-        <v>1.401279964110357</v>
+        <v>1.427170040852059</v>
       </c>
       <c r="U54">
         <v>0.0535</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>7.88353206329927</v>
+        <v>7.734786175312492</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1795950568201551</v>
+        <v>0.1794965801469558</v>
       </c>
       <c r="C55">
-        <v>1.64295023904708</v>
+        <v>1.624615327400572</v>
       </c>
       <c r="D55">
-        <v>2.65432023904708</v>
+        <v>2.656275327400572</v>
       </c>
       <c r="E55">
-        <v>0.10637</v>
+        <v>0.1266600000000001</v>
       </c>
       <c r="F55">
-        <v>1.07537</v>
+        <v>1.09566</v>
       </c>
       <c r="G55">
         <v>0.064</v>
@@ -5797,45 +5797,45 @@
         <v>0.445</v>
       </c>
       <c r="M55">
-        <v>0.057532295</v>
+        <v>0.05949433800000001</v>
       </c>
       <c r="N55">
-        <v>0.387467705</v>
+        <v>0.385505662</v>
       </c>
       <c r="O55">
-        <v>0.0929922492</v>
+        <v>0.09252135888</v>
       </c>
       <c r="P55">
-        <v>0.2944754558</v>
+        <v>0.29298430312</v>
       </c>
       <c r="Q55">
-        <v>0.6104754558000001</v>
+        <v>0.60898430312</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3362665038726704</v>
+        <v>0.3417649133629473</v>
       </c>
       <c r="T55">
-        <v>1.427170040852059</v>
+        <v>1.45418577310427</v>
       </c>
       <c r="U55">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V55">
         <v>0.24</v>
       </c>
       <c r="W55">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y55">
-        <v>7.734786175312492</v>
+        <v>7.479703362696463</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1794965801469558</v>
+        <v>0.1790758634737565</v>
       </c>
       <c r="C56">
-        <v>1.624615327400572</v>
+        <v>1.612710486496281</v>
       </c>
       <c r="D56">
-        <v>2.656275327400572</v>
+        <v>2.664660486496281</v>
       </c>
       <c r="E56">
-        <v>0.1266600000000001</v>
+        <v>0.14695</v>
       </c>
       <c r="F56">
-        <v>1.09566</v>
+        <v>1.11595</v>
       </c>
       <c r="G56">
         <v>0.064</v>
@@ -5879,28 +5879,28 @@
         <v>0.445</v>
       </c>
       <c r="M56">
-        <v>0.05949433800000001</v>
+        <v>0.060596085</v>
       </c>
       <c r="N56">
-        <v>0.385505662</v>
+        <v>0.384403915</v>
       </c>
       <c r="O56">
-        <v>0.09252135888</v>
+        <v>0.09225693959999999</v>
       </c>
       <c r="P56">
-        <v>0.29298430312</v>
+        <v>0.2921469754</v>
       </c>
       <c r="Q56">
-        <v>0.60898430312</v>
+        <v>0.6081469754</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3417649133629473</v>
+        <v>0.3475076966083477</v>
       </c>
       <c r="T56">
-        <v>1.45418577310427</v>
+        <v>1.482402204567691</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>7.479703362696463</v>
+        <v>7.343708756101982</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1790758634737565</v>
+        <v>0.1786551468005571</v>
       </c>
       <c r="C57">
-        <v>1.612710486496281</v>
+        <v>1.60085875269885</v>
       </c>
       <c r="D57">
-        <v>2.664660486496281</v>
+        <v>2.67309875269885</v>
       </c>
       <c r="E57">
-        <v>0.14695</v>
+        <v>0.1672400000000002</v>
       </c>
       <c r="F57">
-        <v>1.11595</v>
+        <v>1.13624</v>
       </c>
       <c r="G57">
         <v>0.064</v>
@@ -5961,28 +5961,28 @@
         <v>0.445</v>
       </c>
       <c r="M57">
-        <v>0.060596085</v>
+        <v>0.06169783200000001</v>
       </c>
       <c r="N57">
-        <v>0.384403915</v>
+        <v>0.383302168</v>
       </c>
       <c r="O57">
-        <v>0.09225693959999999</v>
+        <v>0.09199252031999999</v>
       </c>
       <c r="P57">
-        <v>0.2921469754</v>
+        <v>0.29130964768</v>
       </c>
       <c r="Q57">
-        <v>0.6081469754</v>
+        <v>0.60730964768</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3475076966083477</v>
+        <v>0.3535115154558117</v>
       </c>
       <c r="T57">
-        <v>1.482402204567691</v>
+        <v>1.51190120109763</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>7.343708756101982</v>
+        <v>7.212571099743018</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1786551468005571</v>
+        <v>0.1782344301273578</v>
       </c>
       <c r="C58">
-        <v>1.60085875269885</v>
+        <v>1.589060632139017</v>
       </c>
       <c r="D58">
-        <v>2.67309875269885</v>
+        <v>2.681590632139017</v>
       </c>
       <c r="E58">
-        <v>0.1672400000000002</v>
+        <v>0.1875300000000001</v>
       </c>
       <c r="F58">
-        <v>1.13624</v>
+        <v>1.15653</v>
       </c>
       <c r="G58">
         <v>0.064</v>
@@ -6043,28 +6043,28 @@
         <v>0.445</v>
       </c>
       <c r="M58">
-        <v>0.06169783200000001</v>
+        <v>0.06279957900000001</v>
       </c>
       <c r="N58">
-        <v>0.383302168</v>
+        <v>0.382200421</v>
       </c>
       <c r="O58">
-        <v>0.09199252031999999</v>
+        <v>0.09172810104</v>
       </c>
       <c r="P58">
-        <v>0.29130964768</v>
+        <v>0.29047231996</v>
       </c>
       <c r="Q58">
-        <v>0.60730964768</v>
+        <v>0.60647231996</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3535115154558117</v>
+        <v>0.3597945816915298</v>
       </c>
       <c r="T58">
-        <v>1.51190120109763</v>
+        <v>1.542772243977799</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>7.212571099743018</v>
+        <v>7.086034764659807</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1782344301273578</v>
+        <v>0.1778137134541584</v>
       </c>
       <c r="C59">
-        <v>1.589060632139017</v>
+        <v>1.577316637399507</v>
       </c>
       <c r="D59">
-        <v>2.681590632139017</v>
+        <v>2.690136637399507</v>
       </c>
       <c r="E59">
-        <v>0.1875300000000001</v>
+        <v>0.2078200000000002</v>
       </c>
       <c r="F59">
-        <v>1.15653</v>
+        <v>1.17682</v>
       </c>
       <c r="G59">
         <v>0.064</v>
@@ -6125,28 +6125,28 @@
         <v>0.445</v>
       </c>
       <c r="M59">
-        <v>0.06279957900000001</v>
+        <v>0.06390132600000001</v>
       </c>
       <c r="N59">
-        <v>0.382200421</v>
+        <v>0.381098674</v>
       </c>
       <c r="O59">
-        <v>0.09172810104</v>
+        <v>0.09146368175999998</v>
       </c>
       <c r="P59">
-        <v>0.29047231996</v>
+        <v>0.28963499224</v>
       </c>
       <c r="Q59">
-        <v>0.60647231996</v>
+        <v>0.6056349922399999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3597945816915298</v>
+        <v>0.3663768415575201</v>
       </c>
       <c r="T59">
-        <v>1.542772243977799</v>
+        <v>1.575113336518928</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>7.086034764659807</v>
+        <v>6.963861751476017</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1778137134541585</v>
+        <v>0.1773929967809592</v>
       </c>
       <c r="C60">
-        <v>1.577316637399506</v>
+        <v>1.565627287618167</v>
       </c>
       <c r="D60">
-        <v>2.690136637399506</v>
+        <v>2.698737287618167</v>
       </c>
       <c r="E60">
-        <v>0.20782</v>
+        <v>0.2281099999999999</v>
       </c>
       <c r="F60">
-        <v>1.17682</v>
+        <v>1.19711</v>
       </c>
       <c r="G60">
         <v>0.064</v>
@@ -6207,28 +6207,28 @@
         <v>0.445</v>
       </c>
       <c r="M60">
-        <v>0.06390132599999999</v>
+        <v>0.06500307299999999</v>
       </c>
       <c r="N60">
-        <v>0.381098674</v>
+        <v>0.379996927</v>
       </c>
       <c r="O60">
-        <v>0.09146368176</v>
+        <v>0.09119926247999999</v>
       </c>
       <c r="P60">
-        <v>0.28963499224</v>
+        <v>0.28879766452</v>
       </c>
       <c r="Q60">
-        <v>0.6056349922399999</v>
+        <v>0.6047976645199999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3663768415575201</v>
+        <v>0.3732801872706321</v>
       </c>
       <c r="T60">
-        <v>1.575113336518928</v>
+        <v>1.609032043330357</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>6.963861751476019</v>
+        <v>6.845830196366255</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1773929967809592</v>
+        <v>0.1769722801077598</v>
       </c>
       <c r="C61">
-        <v>1.565627287618167</v>
+        <v>1.553993108593094</v>
       </c>
       <c r="D61">
-        <v>2.698737287618167</v>
+        <v>2.707393108593093</v>
       </c>
       <c r="E61">
-        <v>0.2281099999999999</v>
+        <v>0.2483999999999998</v>
       </c>
       <c r="F61">
-        <v>1.19711</v>
+        <v>1.2174</v>
       </c>
       <c r="G61">
         <v>0.064</v>
@@ -6289,28 +6289,28 @@
         <v>0.445</v>
       </c>
       <c r="M61">
-        <v>0.06500307299999999</v>
+        <v>0.06610481999999999</v>
       </c>
       <c r="N61">
-        <v>0.379996927</v>
+        <v>0.37889518</v>
       </c>
       <c r="O61">
-        <v>0.09119926247999999</v>
+        <v>0.09093484319999999</v>
       </c>
       <c r="P61">
-        <v>0.28879766452</v>
+        <v>0.2879603368</v>
       </c>
       <c r="Q61">
-        <v>0.6047976645199999</v>
+        <v>0.6039603367999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3732801872706321</v>
+        <v>0.3805287002693995</v>
       </c>
       <c r="T61">
-        <v>1.609032043330357</v>
+        <v>1.644646685482357</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>6.845830196366255</v>
+        <v>6.731733026426817</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1769722801077598</v>
+        <v>0.1765515634345605</v>
       </c>
       <c r="C62">
-        <v>1.553993108593094</v>
+        <v>1.542414632889781</v>
       </c>
       <c r="D62">
-        <v>2.707393108593093</v>
+        <v>2.716104632889781</v>
       </c>
       <c r="E62">
-        <v>0.2483999999999998</v>
+        <v>0.26869</v>
       </c>
       <c r="F62">
-        <v>1.2174</v>
+        <v>1.23769</v>
       </c>
       <c r="G62">
         <v>0.064</v>
@@ -6371,28 +6371,28 @@
         <v>0.445</v>
       </c>
       <c r="M62">
-        <v>0.06610481999999999</v>
+        <v>0.06720656699999999</v>
       </c>
       <c r="N62">
-        <v>0.37889518</v>
+        <v>0.377793433</v>
       </c>
       <c r="O62">
-        <v>0.09093484319999999</v>
+        <v>0.09067042391999999</v>
       </c>
       <c r="P62">
-        <v>0.2879603368</v>
+        <v>0.28712300908</v>
       </c>
       <c r="Q62">
-        <v>0.6039603367999999</v>
+        <v>0.6031230090799999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3805287002693995</v>
+        <v>0.3881489318834884</v>
       </c>
       <c r="T62">
-        <v>1.644646685482357</v>
+        <v>1.682087719539588</v>
       </c>
       <c r="U62">
         <v>0.0543</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>6.731733026426817</v>
+        <v>6.621376747305066</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1765515634345605</v>
+        <v>0.1761308467613612</v>
       </c>
       <c r="C63">
-        <v>1.542414632889781</v>
+        <v>1.530892399950353</v>
       </c>
       <c r="D63">
-        <v>2.716104632889781</v>
+        <v>2.724872399950352</v>
       </c>
       <c r="E63">
-        <v>0.26869</v>
+        <v>0.2889799999999999</v>
       </c>
       <c r="F63">
-        <v>1.23769</v>
+        <v>1.25798</v>
       </c>
       <c r="G63">
         <v>0.064</v>
@@ -6453,28 +6453,28 @@
         <v>0.445</v>
       </c>
       <c r="M63">
-        <v>0.06720656699999999</v>
+        <v>0.06830831399999999</v>
       </c>
       <c r="N63">
-        <v>0.377793433</v>
+        <v>0.376691686</v>
       </c>
       <c r="O63">
-        <v>0.09067042391999999</v>
+        <v>0.09040600464000001</v>
       </c>
       <c r="P63">
-        <v>0.28712300908</v>
+        <v>0.28628568136</v>
       </c>
       <c r="Q63">
-        <v>0.6031230090799999</v>
+        <v>0.6022856813599999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3881489318834884</v>
+        <v>0.3961702283193715</v>
       </c>
       <c r="T63">
-        <v>1.682087719539588</v>
+        <v>1.721499334336673</v>
       </c>
       <c r="U63">
         <v>0.0543</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>6.621376747305066</v>
+        <v>6.514580348154985</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1761308467613612</v>
+        <v>0.1757101300881618</v>
       </c>
       <c r="C64">
-        <v>1.530892399950353</v>
+        <v>1.51942695620491</v>
       </c>
       <c r="D64">
-        <v>2.724872399950352</v>
+        <v>2.73369695620491</v>
       </c>
       <c r="E64">
-        <v>0.2889799999999999</v>
+        <v>0.30927</v>
       </c>
       <c r="F64">
-        <v>1.25798</v>
+        <v>1.27827</v>
       </c>
       <c r="G64">
         <v>0.064</v>
@@ -6535,28 +6535,28 @@
         <v>0.445</v>
       </c>
       <c r="M64">
-        <v>0.06830831399999999</v>
+        <v>0.06941006100000001</v>
       </c>
       <c r="N64">
-        <v>0.376691686</v>
+        <v>0.375589939</v>
       </c>
       <c r="O64">
-        <v>0.09040600464000001</v>
+        <v>0.09014158536</v>
       </c>
       <c r="P64">
-        <v>0.28628568136</v>
+        <v>0.28544835364</v>
       </c>
       <c r="Q64">
-        <v>0.6022856813599999</v>
+        <v>0.6014483536399999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3961702283193715</v>
+        <v>0.4046251083463833</v>
       </c>
       <c r="T64">
-        <v>1.721499334336673</v>
+        <v>1.763041306690357</v>
       </c>
       <c r="U64">
         <v>0.0543</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>6.514580348154985</v>
+        <v>6.411174310882682</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1757101300881618</v>
+        <v>0.1752894134149625</v>
       </c>
       <c r="C65">
-        <v>1.51942695620491</v>
+        <v>1.508018855185053</v>
       </c>
       <c r="D65">
-        <v>2.73369695620491</v>
+        <v>2.742578855185053</v>
       </c>
       <c r="E65">
-        <v>0.30927</v>
+        <v>0.32956</v>
       </c>
       <c r="F65">
-        <v>1.27827</v>
+        <v>1.29856</v>
       </c>
       <c r="G65">
         <v>0.064</v>
@@ -6617,28 +6617,28 @@
         <v>0.445</v>
       </c>
       <c r="M65">
-        <v>0.06941006100000001</v>
+        <v>0.070511808</v>
       </c>
       <c r="N65">
-        <v>0.375589939</v>
+        <v>0.374488192</v>
       </c>
       <c r="O65">
-        <v>0.09014158536</v>
+        <v>0.08987716608</v>
       </c>
       <c r="P65">
-        <v>0.28544835364</v>
+        <v>0.28461102592</v>
       </c>
       <c r="Q65">
-        <v>0.6014483536399999</v>
+        <v>0.6006110259199999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.4046251083463833</v>
+        <v>0.4135497039304514</v>
       </c>
       <c r="T65">
-        <v>1.763041306690357</v>
+        <v>1.806891166397024</v>
       </c>
       <c r="U65">
         <v>0.0543</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>6.411174310882682</v>
+        <v>6.310999712275142</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1752894134149625</v>
+        <v>0.1748686967417632</v>
       </c>
       <c r="C66">
-        <v>1.508018855185053</v>
+        <v>1.496668657639623</v>
       </c>
       <c r="D66">
-        <v>2.742578855185053</v>
+        <v>2.751518657639623</v>
       </c>
       <c r="E66">
-        <v>0.32956</v>
+        <v>0.3498500000000001</v>
       </c>
       <c r="F66">
-        <v>1.29856</v>
+        <v>1.31885</v>
       </c>
       <c r="G66">
         <v>0.064</v>
@@ -6699,28 +6699,28 @@
         <v>0.445</v>
       </c>
       <c r="M66">
-        <v>0.070511808</v>
+        <v>0.07161355500000001</v>
       </c>
       <c r="N66">
-        <v>0.374488192</v>
+        <v>0.373386445</v>
       </c>
       <c r="O66">
-        <v>0.08987716608</v>
+        <v>0.0896127468</v>
       </c>
       <c r="P66">
-        <v>0.28461102592</v>
+        <v>0.2837736982</v>
       </c>
       <c r="Q66">
-        <v>0.6006110259199999</v>
+        <v>0.5997736981999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.4135497039304514</v>
+        <v>0.4229842764050378</v>
       </c>
       <c r="T66">
-        <v>1.806891166397024</v>
+        <v>1.853246732372643</v>
       </c>
       <c r="U66">
         <v>0.0543</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>6.310999712275142</v>
+        <v>6.213907409009369</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1748686967417632</v>
+        <v>0.1744479800685639</v>
       </c>
       <c r="C67">
-        <v>1.496668657639623</v>
+        <v>1.485376931652718</v>
       </c>
       <c r="D67">
-        <v>2.751518657639623</v>
+        <v>2.760516931652718</v>
       </c>
       <c r="E67">
-        <v>0.3498500000000001</v>
+        <v>0.37014</v>
       </c>
       <c r="F67">
-        <v>1.31885</v>
+        <v>1.33914</v>
       </c>
       <c r="G67">
         <v>0.064</v>
@@ -6781,28 +6781,28 @@
         <v>0.445</v>
       </c>
       <c r="M67">
-        <v>0.07161355500000001</v>
+        <v>0.072715302</v>
       </c>
       <c r="N67">
-        <v>0.373386445</v>
+        <v>0.372284698</v>
       </c>
       <c r="O67">
-        <v>0.0896127468</v>
+        <v>0.08934832752000001</v>
       </c>
       <c r="P67">
-        <v>0.2837736982</v>
+        <v>0.28293637048</v>
       </c>
       <c r="Q67">
-        <v>0.5997736981999999</v>
+        <v>0.59893637048</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.4229842764050378</v>
+        <v>0.4329738237310702</v>
       </c>
       <c r="T67">
-        <v>1.853246732372643</v>
+        <v>1.902329096346828</v>
       </c>
       <c r="U67">
         <v>0.0543</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>6.213907409009369</v>
+        <v>6.119757296751652</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1744479800685639</v>
+        <v>0.1745364633953645</v>
       </c>
       <c r="C68">
-        <v>1.485376931652718</v>
+        <v>1.463189569278763</v>
       </c>
       <c r="D68">
-        <v>2.760516931652718</v>
+        <v>2.758619569278763</v>
       </c>
       <c r="E68">
-        <v>0.37014</v>
+        <v>0.3904299999999999</v>
       </c>
       <c r="F68">
-        <v>1.33914</v>
+        <v>1.35943</v>
       </c>
       <c r="G68">
         <v>0.064</v>
@@ -6863,45 +6863,45 @@
         <v>0.445</v>
       </c>
       <c r="M68">
-        <v>0.072715302</v>
+        <v>0.075176479</v>
       </c>
       <c r="N68">
-        <v>0.372284698</v>
+        <v>0.369823521</v>
       </c>
       <c r="O68">
-        <v>0.08934832752000001</v>
+        <v>0.08875764504</v>
       </c>
       <c r="P68">
-        <v>0.28293637048</v>
+        <v>0.28106587596</v>
       </c>
       <c r="Q68">
-        <v>0.59893637048</v>
+        <v>0.59706587596</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.4329738237310702</v>
+        <v>0.4435687981677714</v>
       </c>
       <c r="T68">
-        <v>1.902329096346828</v>
+        <v>1.954386149046721</v>
       </c>
       <c r="U68">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V68">
         <v>0.24</v>
       </c>
       <c r="W68">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y68">
-        <v>6.119757296751652</v>
+        <v>5.91940465847037</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1745364633953645</v>
+        <v>0.1741233467221652</v>
       </c>
       <c r="C69">
-        <v>1.463189569278763</v>
+        <v>1.451780507690934</v>
       </c>
       <c r="D69">
-        <v>2.758619569278763</v>
+        <v>2.767500507690934</v>
       </c>
       <c r="E69">
-        <v>0.3904299999999999</v>
+        <v>0.4107200000000001</v>
       </c>
       <c r="F69">
-        <v>1.35943</v>
+        <v>1.37972</v>
       </c>
       <c r="G69">
         <v>0.064</v>
@@ -6945,28 +6945,28 @@
         <v>0.445</v>
       </c>
       <c r="M69">
-        <v>0.075176479</v>
+        <v>0.07629851600000001</v>
       </c>
       <c r="N69">
-        <v>0.369823521</v>
+        <v>0.368701484</v>
       </c>
       <c r="O69">
-        <v>0.08875764504</v>
+        <v>0.08848835616</v>
       </c>
       <c r="P69">
-        <v>0.28106587596</v>
+        <v>0.28021312784</v>
       </c>
       <c r="Q69">
-        <v>0.59706587596</v>
+        <v>0.59621312784</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.4435687981677714</v>
+        <v>0.4548259585067663</v>
       </c>
       <c r="T69">
-        <v>1.954386149046721</v>
+        <v>2.009696767540357</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.91940465847037</v>
+        <v>5.832354589963453</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1741233467221652</v>
+        <v>0.1737102300489659</v>
       </c>
       <c r="C70">
-        <v>1.451780507690934</v>
+        <v>1.440428812331438</v>
       </c>
       <c r="D70">
-        <v>2.767500507690934</v>
+        <v>2.776438812331438</v>
       </c>
       <c r="E70">
-        <v>0.4107200000000001</v>
+        <v>0.43101</v>
       </c>
       <c r="F70">
-        <v>1.37972</v>
+        <v>1.40001</v>
       </c>
       <c r="G70">
         <v>0.064</v>
@@ -7027,28 +7027,28 @@
         <v>0.445</v>
       </c>
       <c r="M70">
-        <v>0.07629851600000001</v>
+        <v>0.077420553</v>
       </c>
       <c r="N70">
-        <v>0.368701484</v>
+        <v>0.367579447</v>
       </c>
       <c r="O70">
-        <v>0.08848835616</v>
+        <v>0.08821906727999999</v>
       </c>
       <c r="P70">
-        <v>0.28021312784</v>
+        <v>0.27936037972</v>
       </c>
       <c r="Q70">
-        <v>0.59621312784</v>
+        <v>0.59536037972</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.4548259585067663</v>
+        <v>0.4668093872547288</v>
       </c>
       <c r="T70">
-        <v>2.009696767540357</v>
+        <v>2.068575813033583</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.832354589963453</v>
+        <v>5.747827711848041</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1737102300489659</v>
+        <v>0.1732971133757665</v>
       </c>
       <c r="C71">
-        <v>1.440428812331438</v>
+        <v>1.429135040835149</v>
       </c>
       <c r="D71">
-        <v>2.776438812331438</v>
+        <v>2.785435040835149</v>
       </c>
       <c r="E71">
-        <v>0.43101</v>
+        <v>0.4513000000000001</v>
       </c>
       <c r="F71">
-        <v>1.40001</v>
+        <v>1.4203</v>
       </c>
       <c r="G71">
         <v>0.064</v>
@@ -7109,28 +7109,28 @@
         <v>0.445</v>
       </c>
       <c r="M71">
-        <v>0.077420553</v>
+        <v>0.07854259000000001</v>
       </c>
       <c r="N71">
-        <v>0.367579447</v>
+        <v>0.36645741</v>
       </c>
       <c r="O71">
-        <v>0.08821906727999999</v>
+        <v>0.0879497784</v>
       </c>
       <c r="P71">
-        <v>0.27936037972</v>
+        <v>0.2785076316</v>
       </c>
       <c r="Q71">
-        <v>0.59536037972</v>
+        <v>0.5945076316</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.4668093872547288</v>
+        <v>0.4795917112525552</v>
       </c>
       <c r="T71">
-        <v>2.068575813033583</v>
+        <v>2.131380128226357</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.747827711848041</v>
+        <v>5.665715887393068</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1732971133757665</v>
+        <v>0.1728839967025673</v>
       </c>
       <c r="C72">
-        <v>1.429135040835149</v>
+        <v>1.41789975808783</v>
       </c>
       <c r="D72">
-        <v>2.785435040835149</v>
+        <v>2.79448975808783</v>
       </c>
       <c r="E72">
-        <v>0.4513000000000001</v>
+        <v>0.4715900000000001</v>
       </c>
       <c r="F72">
-        <v>1.4203</v>
+        <v>1.44059</v>
       </c>
       <c r="G72">
         <v>0.064</v>
@@ -7191,28 +7191,28 @@
         <v>0.445</v>
       </c>
       <c r="M72">
-        <v>0.07854259000000001</v>
+        <v>0.079664627</v>
       </c>
       <c r="N72">
-        <v>0.36645741</v>
+        <v>0.365335373</v>
       </c>
       <c r="O72">
-        <v>0.0879497784</v>
+        <v>0.08768048952</v>
       </c>
       <c r="P72">
-        <v>0.2785076316</v>
+        <v>0.27765488348</v>
       </c>
       <c r="Q72">
-        <v>0.5945076316</v>
+        <v>0.59365488348</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4795917112525552</v>
+        <v>0.4932555748364389</v>
       </c>
       <c r="T72">
-        <v>2.131380128226357</v>
+        <v>2.198515775501392</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.665715887393068</v>
+        <v>5.585917072077674</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1728839967025673</v>
+        <v>0.1724708800293679</v>
       </c>
       <c r="C73">
-        <v>1.417899758087831</v>
+        <v>1.406723536344389</v>
       </c>
       <c r="D73">
-        <v>2.79448975808783</v>
+        <v>2.803603536344389</v>
       </c>
       <c r="E73">
-        <v>0.4715899999999998</v>
+        <v>0.49188</v>
       </c>
       <c r="F73">
-        <v>1.44059</v>
+        <v>1.46088</v>
       </c>
       <c r="G73">
         <v>0.064</v>
@@ -7273,28 +7273,28 @@
         <v>0.445</v>
       </c>
       <c r="M73">
-        <v>0.07966462699999999</v>
+        <v>0.08078666399999999</v>
       </c>
       <c r="N73">
-        <v>0.365335373</v>
+        <v>0.364213336</v>
       </c>
       <c r="O73">
-        <v>0.08768048952</v>
+        <v>0.08741120063999999</v>
       </c>
       <c r="P73">
-        <v>0.27765488348</v>
+        <v>0.27680213536</v>
       </c>
       <c r="Q73">
-        <v>0.59365488348</v>
+        <v>0.5928021353599999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4932555748364388</v>
+        <v>0.507895428676314</v>
       </c>
       <c r="T73">
-        <v>2.198515775501392</v>
+        <v>2.270446826153214</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.585917072077675</v>
+        <v>5.50833489052104</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1724708800293679</v>
+        <v>0.1720577633561686</v>
       </c>
       <c r="C74">
-        <v>1.406723536344389</v>
+        <v>1.395606955349423</v>
       </c>
       <c r="D74">
-        <v>2.803603536344389</v>
+        <v>2.812776955349423</v>
       </c>
       <c r="E74">
-        <v>0.49188</v>
+        <v>0.5121699999999999</v>
       </c>
       <c r="F74">
-        <v>1.46088</v>
+        <v>1.48117</v>
       </c>
       <c r="G74">
         <v>0.064</v>
@@ -7355,28 +7355,28 @@
         <v>0.445</v>
       </c>
       <c r="M74">
-        <v>0.08078666399999999</v>
+        <v>0.081908701</v>
       </c>
       <c r="N74">
-        <v>0.364213336</v>
+        <v>0.363091299</v>
       </c>
       <c r="O74">
-        <v>0.08741120063999999</v>
+        <v>0.08714191176000001</v>
       </c>
       <c r="P74">
-        <v>0.27680213536</v>
+        <v>0.27594938724</v>
       </c>
       <c r="Q74">
-        <v>0.5928021353599999</v>
+        <v>0.59194938724</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.507895428676314</v>
+        <v>0.5236197161339576</v>
       </c>
       <c r="T74">
-        <v>2.270446826153214</v>
+        <v>2.347706102779246</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.50833489052104</v>
+        <v>5.432878248185135</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1720577633561686</v>
+        <v>0.1716446466829692</v>
       </c>
       <c r="C75">
-        <v>1.395606955349423</v>
+        <v>1.384550602460158</v>
       </c>
       <c r="D75">
-        <v>2.812776955349423</v>
+        <v>2.822010602460158</v>
       </c>
       <c r="E75">
-        <v>0.5121699999999999</v>
+        <v>0.53246</v>
       </c>
       <c r="F75">
-        <v>1.48117</v>
+        <v>1.50146</v>
       </c>
       <c r="G75">
         <v>0.064</v>
@@ -7437,28 +7437,28 @@
         <v>0.445</v>
       </c>
       <c r="M75">
-        <v>0.081908701</v>
+        <v>0.08303073800000001</v>
       </c>
       <c r="N75">
-        <v>0.363091299</v>
+        <v>0.361969262</v>
       </c>
       <c r="O75">
-        <v>0.08714191176000001</v>
+        <v>0.08687262288</v>
       </c>
       <c r="P75">
-        <v>0.27594938724</v>
+        <v>0.27509663912</v>
       </c>
       <c r="Q75">
-        <v>0.59194938724</v>
+        <v>0.5910966391200001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.5236197161339576</v>
+        <v>0.5405535641652663</v>
       </c>
       <c r="T75">
-        <v>2.347706102779246</v>
+        <v>2.430908400684203</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.432878248185135</v>
+        <v>5.359460974561011</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1716446466829692</v>
+        <v>0.1712315300097699</v>
       </c>
       <c r="C76">
-        <v>1.384550602460158</v>
+        <v>1.373555072771817</v>
       </c>
       <c r="D76">
-        <v>2.822010602460158</v>
+        <v>2.831305072771817</v>
       </c>
       <c r="E76">
-        <v>0.53246</v>
+        <v>0.55275</v>
       </c>
       <c r="F76">
-        <v>1.50146</v>
+        <v>1.52175</v>
       </c>
       <c r="G76">
         <v>0.064</v>
@@ -7519,28 +7519,28 @@
         <v>0.445</v>
       </c>
       <c r="M76">
-        <v>0.08303073800000001</v>
+        <v>0.084152775</v>
       </c>
       <c r="N76">
-        <v>0.361969262</v>
+        <v>0.360847225</v>
       </c>
       <c r="O76">
-        <v>0.08687262288</v>
+        <v>0.08660333399999999</v>
       </c>
       <c r="P76">
-        <v>0.27509663912</v>
+        <v>0.274243891</v>
       </c>
       <c r="Q76">
-        <v>0.5910966391200001</v>
+        <v>0.5902438910000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.5405535641652663</v>
+        <v>0.5588421200390796</v>
       </c>
       <c r="T76">
-        <v>2.430908400684203</v>
+        <v>2.520766882421557</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>5.359460974561011</v>
+        <v>5.288001494900198</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1712315300097699</v>
+        <v>0.1708184133365706</v>
       </c>
       <c r="C77">
-        <v>1.373555072771817</v>
+        <v>1.362620969245457</v>
       </c>
       <c r="D77">
-        <v>2.831305072771817</v>
+        <v>2.840660969245457</v>
       </c>
       <c r="E77">
-        <v>0.55275</v>
+        <v>0.5730399999999999</v>
       </c>
       <c r="F77">
-        <v>1.52175</v>
+        <v>1.54204</v>
       </c>
       <c r="G77">
         <v>0.064</v>
@@ -7601,28 +7601,28 @@
         <v>0.445</v>
       </c>
       <c r="M77">
-        <v>0.084152775</v>
+        <v>0.08527481199999999</v>
       </c>
       <c r="N77">
-        <v>0.360847225</v>
+        <v>0.359725188</v>
       </c>
       <c r="O77">
-        <v>0.08660333399999999</v>
+        <v>0.08633404512000001</v>
       </c>
       <c r="P77">
-        <v>0.274243891</v>
+        <v>0.27339114288</v>
       </c>
       <c r="Q77">
-        <v>0.5902438910000001</v>
+        <v>0.5893911428800001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.5588421200390796</v>
+        <v>0.5786547222357108</v>
       </c>
       <c r="T77">
-        <v>2.520766882421557</v>
+        <v>2.618113570970357</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>5.288001494900198</v>
+        <v>5.218422527862038</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1708184133365706</v>
+        <v>0.1704052966633713</v>
       </c>
       <c r="C78">
-        <v>1.362620969245457</v>
+        <v>1.351748902838379</v>
       </c>
       <c r="D78">
-        <v>2.840660969245457</v>
+        <v>2.850078902838379</v>
       </c>
       <c r="E78">
-        <v>0.5730399999999999</v>
+        <v>0.59333</v>
       </c>
       <c r="F78">
-        <v>1.54204</v>
+        <v>1.56233</v>
       </c>
       <c r="G78">
         <v>0.064</v>
@@ -7683,28 +7683,28 @@
         <v>0.445</v>
       </c>
       <c r="M78">
-        <v>0.08527481199999999</v>
+        <v>0.086396849</v>
       </c>
       <c r="N78">
-        <v>0.359725188</v>
+        <v>0.358603151</v>
       </c>
       <c r="O78">
-        <v>0.08633404512000001</v>
+        <v>0.08606475624</v>
       </c>
       <c r="P78">
-        <v>0.27339114288</v>
+        <v>0.27253839476</v>
       </c>
       <c r="Q78">
-        <v>0.5893911428800001</v>
+        <v>0.58853839476</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.5786547222357108</v>
+        <v>0.600190159405962</v>
       </c>
       <c r="T78">
-        <v>2.618113570970357</v>
+        <v>2.723925188958183</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>5.218422527862038</v>
+        <v>5.150650806720972</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1704052966633713</v>
+        <v>0.1699921799901719</v>
       </c>
       <c r="C79">
-        <v>1.351748902838379</v>
+        <v>1.340939492637103</v>
       </c>
       <c r="D79">
-        <v>2.850078902838379</v>
+        <v>2.859559492637103</v>
       </c>
       <c r="E79">
-        <v>0.59333</v>
+        <v>0.6136199999999999</v>
       </c>
       <c r="F79">
-        <v>1.56233</v>
+        <v>1.58262</v>
       </c>
       <c r="G79">
         <v>0.064</v>
@@ -7765,28 +7765,28 @@
         <v>0.445</v>
       </c>
       <c r="M79">
-        <v>0.086396849</v>
+        <v>0.087518886</v>
       </c>
       <c r="N79">
-        <v>0.358603151</v>
+        <v>0.357481114</v>
       </c>
       <c r="O79">
-        <v>0.08606475624</v>
+        <v>0.08579546735999999</v>
       </c>
       <c r="P79">
-        <v>0.27253839476</v>
+        <v>0.27168564664</v>
       </c>
       <c r="Q79">
-        <v>0.58853839476</v>
+        <v>0.58768564664</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.600190159405962</v>
+        <v>0.6236833635916906</v>
       </c>
       <c r="T79">
-        <v>2.723925188958183</v>
+        <v>2.839356044944902</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.150650806720972</v>
+        <v>5.084616822019421</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1699921799901719</v>
+        <v>0.1695790633169726</v>
       </c>
       <c r="C80">
-        <v>1.340939492637103</v>
+        <v>1.330193365993041</v>
       </c>
       <c r="D80">
-        <v>2.859559492637103</v>
+        <v>2.869103365993041</v>
       </c>
       <c r="E80">
-        <v>0.6136199999999999</v>
+        <v>0.6339100000000001</v>
       </c>
       <c r="F80">
-        <v>1.58262</v>
+        <v>1.60291</v>
       </c>
       <c r="G80">
         <v>0.064</v>
@@ -7847,28 +7847,28 @@
         <v>0.445</v>
       </c>
       <c r="M80">
-        <v>0.087518886</v>
+        <v>0.08864092300000001</v>
       </c>
       <c r="N80">
-        <v>0.357481114</v>
+        <v>0.356359077</v>
       </c>
       <c r="O80">
-        <v>0.08579546735999999</v>
+        <v>0.08552617848000001</v>
       </c>
       <c r="P80">
-        <v>0.27168564664</v>
+        <v>0.27083289852</v>
       </c>
       <c r="Q80">
-        <v>0.58768564664</v>
+        <v>0.58683289852</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.6236833635916906</v>
+        <v>0.6494140157951077</v>
       </c>
       <c r="T80">
-        <v>2.839356044944902</v>
+        <v>2.9657803157875</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>5.084616822019421</v>
+        <v>5.02025458376601</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1695790633169726</v>
+        <v>0.1691659466437733</v>
       </c>
       <c r="C81">
-        <v>1.330193365993041</v>
+        <v>1.319511158660872</v>
       </c>
       <c r="D81">
-        <v>2.869103365993041</v>
+        <v>2.878711158660872</v>
       </c>
       <c r="E81">
-        <v>0.6339100000000001</v>
+        <v>0.6542</v>
       </c>
       <c r="F81">
-        <v>1.60291</v>
+        <v>1.6232</v>
       </c>
       <c r="G81">
         <v>0.064</v>
@@ -7929,28 +7929,28 @@
         <v>0.445</v>
       </c>
       <c r="M81">
-        <v>0.08864092300000001</v>
+        <v>0.08976296</v>
       </c>
       <c r="N81">
-        <v>0.356359077</v>
+        <v>0.35523704</v>
       </c>
       <c r="O81">
-        <v>0.08552617848000001</v>
+        <v>0.0852568896</v>
       </c>
       <c r="P81">
-        <v>0.27083289852</v>
+        <v>0.2699801504</v>
       </c>
       <c r="Q81">
-        <v>0.58683289852</v>
+        <v>0.5859801504</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.6494140157951077</v>
+        <v>0.6777177332188665</v>
       </c>
       <c r="T81">
-        <v>2.9657803157875</v>
+        <v>3.104847013714357</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>5.02025458376601</v>
+        <v>4.957501401468935</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1691659466437733</v>
+        <v>0.1687528299705739</v>
       </c>
       <c r="C82">
-        <v>1.319511158660872</v>
+        <v>1.308893514939718</v>
       </c>
       <c r="D82">
-        <v>2.878711158660872</v>
+        <v>2.888383514939718</v>
       </c>
       <c r="E82">
-        <v>0.6542</v>
+        <v>0.6744900000000001</v>
       </c>
       <c r="F82">
-        <v>1.6232</v>
+        <v>1.64349</v>
       </c>
       <c r="G82">
         <v>0.064</v>
@@ -8011,28 +8011,28 @@
         <v>0.445</v>
       </c>
       <c r="M82">
-        <v>0.08976296</v>
+        <v>0.09088499700000001</v>
       </c>
       <c r="N82">
-        <v>0.35523704</v>
+        <v>0.354115003</v>
       </c>
       <c r="O82">
-        <v>0.0852568896</v>
+        <v>0.08498760071999999</v>
       </c>
       <c r="P82">
-        <v>0.2699801504</v>
+        <v>0.26912740228</v>
       </c>
       <c r="Q82">
-        <v>0.5859801504</v>
+        <v>0.5851274022799999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.6777177332188665</v>
+        <v>0.7090007893188104</v>
       </c>
       <c r="T82">
-        <v>3.104847013714357</v>
+        <v>3.258552311422989</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.957501401468935</v>
+        <v>4.896297680463146</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1687528299705739</v>
+        <v>0.1683397132973746</v>
       </c>
       <c r="C83">
-        <v>1.308893514939718</v>
+        <v>1.298341087817173</v>
       </c>
       <c r="D83">
-        <v>2.888383514939718</v>
+        <v>2.898121087817173</v>
       </c>
       <c r="E83">
-        <v>0.6744900000000001</v>
+        <v>0.6947800000000001</v>
       </c>
       <c r="F83">
-        <v>1.64349</v>
+        <v>1.66378</v>
       </c>
       <c r="G83">
         <v>0.064</v>
@@ -8093,28 +8093,28 @@
         <v>0.445</v>
       </c>
       <c r="M83">
-        <v>0.09088499700000001</v>
+        <v>0.092007034</v>
       </c>
       <c r="N83">
-        <v>0.354115003</v>
+        <v>0.352992966</v>
       </c>
       <c r="O83">
-        <v>0.08498760071999999</v>
+        <v>0.08471831184</v>
       </c>
       <c r="P83">
-        <v>0.26912740228</v>
+        <v>0.26827465416</v>
       </c>
       <c r="Q83">
-        <v>0.5851274022799999</v>
+        <v>0.58427465416</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.7090007893188104</v>
+        <v>0.7437597405409703</v>
       </c>
       <c r="T83">
-        <v>3.258552311422989</v>
+        <v>3.42933597554369</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.896297680463146</v>
+        <v>4.836586733140425</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1683397132973746</v>
+        <v>0.1679265966241753</v>
       </c>
       <c r="C84">
-        <v>1.298341087817173</v>
+        <v>1.287854539116255</v>
       </c>
       <c r="D84">
-        <v>2.898121087817173</v>
+        <v>2.907924539116256</v>
       </c>
       <c r="E84">
-        <v>0.6947800000000001</v>
+        <v>0.7150700000000002</v>
       </c>
       <c r="F84">
-        <v>1.66378</v>
+        <v>1.68407</v>
       </c>
       <c r="G84">
         <v>0.064</v>
@@ -8175,28 +8175,28 @@
         <v>0.445</v>
       </c>
       <c r="M84">
-        <v>0.092007034</v>
+        <v>0.09312907100000001</v>
       </c>
       <c r="N84">
-        <v>0.352992966</v>
+        <v>0.351870929</v>
       </c>
       <c r="O84">
-        <v>0.08471831184</v>
+        <v>0.08444902295999999</v>
       </c>
       <c r="P84">
-        <v>0.26827465416</v>
+        <v>0.26742190604</v>
       </c>
       <c r="Q84">
-        <v>0.58427465416</v>
+        <v>0.58342190604</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.7437597405409703</v>
+        <v>0.782607980142208</v>
       </c>
       <c r="T84">
-        <v>3.42933597554369</v>
+        <v>3.620211835443299</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.836586733140425</v>
+        <v>4.77831460382548</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1679265966241753</v>
+        <v>0.167513479950976</v>
       </c>
       <c r="C85">
-        <v>1.287854539116255</v>
+        <v>1.277434539645353</v>
       </c>
       <c r="D85">
-        <v>2.907924539116256</v>
+        <v>2.917794539645353</v>
       </c>
       <c r="E85">
-        <v>0.7150700000000002</v>
+        <v>0.7353600000000001</v>
       </c>
       <c r="F85">
-        <v>1.68407</v>
+        <v>1.70436</v>
       </c>
       <c r="G85">
         <v>0.064</v>
@@ -8257,28 +8257,28 @@
         <v>0.445</v>
       </c>
       <c r="M85">
-        <v>0.09312907100000001</v>
+        <v>0.09425110800000001</v>
       </c>
       <c r="N85">
-        <v>0.351870929</v>
+        <v>0.350748892</v>
       </c>
       <c r="O85">
-        <v>0.08444902295999999</v>
+        <v>0.08417973407999998</v>
       </c>
       <c r="P85">
-        <v>0.26742190604</v>
+        <v>0.26656915792</v>
       </c>
       <c r="Q85">
-        <v>0.58342190604</v>
+        <v>0.5825691579200001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.782607980142208</v>
+        <v>0.8263122496936003</v>
       </c>
       <c r="T85">
-        <v>3.620211835443299</v>
+        <v>3.834947177830358</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.77831460382548</v>
+        <v>4.72142990616089</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.167513479950976</v>
+        <v>0.1671003632777767</v>
       </c>
       <c r="C86">
-        <v>1.277434539645353</v>
+        <v>1.267081769351229</v>
       </c>
       <c r="D86">
-        <v>2.917794539645353</v>
+        <v>2.927731769351229</v>
       </c>
       <c r="E86">
-        <v>0.7353599999999999</v>
+        <v>0.7556499999999998</v>
       </c>
       <c r="F86">
-        <v>1.70436</v>
+        <v>1.72465</v>
       </c>
       <c r="G86">
         <v>0.064</v>
@@ -8339,28 +8339,28 @@
         <v>0.445</v>
       </c>
       <c r="M86">
-        <v>0.094251108</v>
+        <v>0.09537314499999999</v>
       </c>
       <c r="N86">
-        <v>0.350748892</v>
+        <v>0.349626855</v>
       </c>
       <c r="O86">
-        <v>0.08417973408</v>
+        <v>0.0839104452</v>
       </c>
       <c r="P86">
-        <v>0.26656915792</v>
+        <v>0.2657164098</v>
       </c>
       <c r="Q86">
-        <v>0.5825691579200001</v>
+        <v>0.5817164098000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.8263122496935997</v>
+        <v>0.8758437551851777</v>
       </c>
       <c r="T86">
-        <v>3.834947177830355</v>
+        <v>4.078313899202356</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.721429906160891</v>
+        <v>4.665883671970763</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1671003632777767</v>
+        <v>0.1666872466045773</v>
       </c>
       <c r="C87">
-        <v>1.267081769351229</v>
+        <v>1.256796917475171</v>
       </c>
       <c r="D87">
-        <v>2.927731769351229</v>
+        <v>2.937736917475171</v>
       </c>
       <c r="E87">
-        <v>0.7556499999999998</v>
+        <v>0.77594</v>
       </c>
       <c r="F87">
-        <v>1.72465</v>
+        <v>1.74494</v>
       </c>
       <c r="G87">
         <v>0.064</v>
@@ -8421,28 +8421,28 @@
         <v>0.445</v>
       </c>
       <c r="M87">
-        <v>0.09537314499999999</v>
+        <v>0.096495182</v>
       </c>
       <c r="N87">
-        <v>0.349626855</v>
+        <v>0.348504818</v>
       </c>
       <c r="O87">
-        <v>0.0839104452</v>
+        <v>0.08364115631999999</v>
       </c>
       <c r="P87">
-        <v>0.2657164098</v>
+        <v>0.26486366168</v>
       </c>
       <c r="Q87">
-        <v>0.5817164098000001</v>
+        <v>0.58086366168</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.8758437551851777</v>
+        <v>0.9324511900326951</v>
       </c>
       <c r="T87">
-        <v>4.078313899202356</v>
+        <v>4.35644729505607</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.665883671970763</v>
+        <v>4.611629210668777</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1666872466045773</v>
+        <v>0.166274129931378</v>
       </c>
       <c r="C88">
-        <v>1.256796917475171</v>
+        <v>1.24658068271235</v>
       </c>
       <c r="D88">
-        <v>2.937736917475171</v>
+        <v>2.94781068271235</v>
       </c>
       <c r="E88">
-        <v>0.77594</v>
+        <v>0.7962299999999999</v>
       </c>
       <c r="F88">
-        <v>1.74494</v>
+        <v>1.76523</v>
       </c>
       <c r="G88">
         <v>0.064</v>
@@ -8503,28 +8503,28 @@
         <v>0.445</v>
       </c>
       <c r="M88">
-        <v>0.096495182</v>
+        <v>0.09761721899999999</v>
       </c>
       <c r="N88">
-        <v>0.348504818</v>
+        <v>0.347382781</v>
       </c>
       <c r="O88">
-        <v>0.08364115631999999</v>
+        <v>0.08337186744</v>
       </c>
       <c r="P88">
-        <v>0.26486366168</v>
+        <v>0.2640109135600001</v>
       </c>
       <c r="Q88">
-        <v>0.58086366168</v>
+        <v>0.58001091356</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.9324511900326951</v>
+        <v>0.9977674610106</v>
       </c>
       <c r="T88">
-        <v>4.35644729505607</v>
+        <v>4.677370444118048</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>4.611629210668777</v>
+        <v>4.55862197836224</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.166274129931378</v>
+        <v>0.1658610132581787</v>
       </c>
       <c r="C89">
-        <v>1.24658068271235</v>
+        <v>1.236433773374469</v>
       </c>
       <c r="D89">
-        <v>2.94781068271235</v>
+        <v>2.957953773374469</v>
       </c>
       <c r="E89">
-        <v>0.7962299999999999</v>
+        <v>0.81652</v>
       </c>
       <c r="F89">
-        <v>1.76523</v>
+        <v>1.78552</v>
       </c>
       <c r="G89">
         <v>0.064</v>
@@ -8585,28 +8585,28 @@
         <v>0.445</v>
       </c>
       <c r="M89">
-        <v>0.09761721899999999</v>
+        <v>0.098739256</v>
       </c>
       <c r="N89">
-        <v>0.347382781</v>
+        <v>0.346260744</v>
       </c>
       <c r="O89">
-        <v>0.08337186744</v>
+        <v>0.08310257856</v>
       </c>
       <c r="P89">
-        <v>0.2640109135600001</v>
+        <v>0.26315816544</v>
       </c>
       <c r="Q89">
-        <v>0.58001091356</v>
+        <v>0.57915816544</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.9977674610106</v>
+        <v>1.073969777151489</v>
       </c>
       <c r="T89">
-        <v>4.677370444118048</v>
+        <v>5.051780784690356</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>4.55862197836224</v>
+        <v>4.506819455880851</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1658610132581787</v>
+        <v>0.1671388965849794</v>
       </c>
       <c r="C90">
-        <v>1.236433773374469</v>
+        <v>1.184992016478484</v>
       </c>
       <c r="D90">
-        <v>2.957953773374469</v>
+        <v>2.926802016478484</v>
       </c>
       <c r="E90">
-        <v>0.81652</v>
+        <v>0.8368099999999999</v>
       </c>
       <c r="F90">
-        <v>1.78552</v>
+        <v>1.80581</v>
       </c>
       <c r="G90">
         <v>0.064</v>
@@ -8667,45 +8667,45 @@
         <v>0.445</v>
       </c>
       <c r="M90">
-        <v>0.098739256</v>
+        <v>0.104375818</v>
       </c>
       <c r="N90">
-        <v>0.346260744</v>
+        <v>0.340624182</v>
       </c>
       <c r="O90">
-        <v>0.08310257856</v>
+        <v>0.08174980368</v>
       </c>
       <c r="P90">
-        <v>0.26315816544</v>
+        <v>0.25887437832</v>
       </c>
       <c r="Q90">
-        <v>0.57915816544</v>
+        <v>0.57487437832</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.073969777151489</v>
+        <v>1.164027059863449</v>
       </c>
       <c r="T90">
-        <v>5.051780784690356</v>
+        <v>5.494265732639446</v>
       </c>
       <c r="U90">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V90">
         <v>0.24</v>
       </c>
       <c r="W90">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y90">
-        <v>4.506819455880851</v>
+        <v>4.263439640779629</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1671388965849794</v>
+        <v>0.16674477991178</v>
       </c>
       <c r="C91">
-        <v>1.184992016478484</v>
+        <v>1.174239439050082</v>
       </c>
       <c r="D91">
-        <v>2.926802016478484</v>
+        <v>2.936339439050082</v>
       </c>
       <c r="E91">
-        <v>0.8368099999999999</v>
+        <v>0.8571000000000001</v>
       </c>
       <c r="F91">
-        <v>1.80581</v>
+        <v>1.8261</v>
       </c>
       <c r="G91">
         <v>0.064</v>
@@ -8749,28 +8749,28 @@
         <v>0.445</v>
       </c>
       <c r="M91">
-        <v>0.104375818</v>
+        <v>0.10554858</v>
       </c>
       <c r="N91">
-        <v>0.340624182</v>
+        <v>0.33945142</v>
       </c>
       <c r="O91">
-        <v>0.08174980368</v>
+        <v>0.0814683408</v>
       </c>
       <c r="P91">
-        <v>0.25887437832</v>
+        <v>0.2579830792</v>
       </c>
       <c r="Q91">
-        <v>0.57487437832</v>
+        <v>0.5739830792</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.164027059863449</v>
+        <v>1.272095799117801</v>
       </c>
       <c r="T91">
-        <v>5.494265732639446</v>
+        <v>6.025247670178357</v>
       </c>
       <c r="U91">
         <v>0.0578</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>4.263439640779629</v>
+        <v>4.216068089215411</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.16674477991178</v>
+        <v>0.1663506632385807</v>
       </c>
       <c r="C92">
-        <v>1.174239439050082</v>
+        <v>1.163549223074598</v>
       </c>
       <c r="D92">
-        <v>2.936339439050082</v>
+        <v>2.945939223074598</v>
       </c>
       <c r="E92">
-        <v>0.8571000000000001</v>
+        <v>0.87739</v>
       </c>
       <c r="F92">
-        <v>1.8261</v>
+        <v>1.84639</v>
       </c>
       <c r="G92">
         <v>0.064</v>
@@ -8831,28 +8831,28 @@
         <v>0.445</v>
       </c>
       <c r="M92">
-        <v>0.10554858</v>
+        <v>0.106721342</v>
       </c>
       <c r="N92">
-        <v>0.33945142</v>
+        <v>0.338278658</v>
       </c>
       <c r="O92">
-        <v>0.0814683408</v>
+        <v>0.08118687792</v>
       </c>
       <c r="P92">
-        <v>0.2579830792</v>
+        <v>0.25709178008</v>
       </c>
       <c r="Q92">
-        <v>0.5739830792</v>
+        <v>0.5730917800799999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.272095799117801</v>
+        <v>1.404179813762008</v>
       </c>
       <c r="T92">
-        <v>6.025247670178357</v>
+        <v>6.674225593837023</v>
       </c>
       <c r="U92">
         <v>0.0578</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>4.216068089215411</v>
+        <v>4.169737670652605</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1663506632385807</v>
+        <v>0.1659565465653814</v>
       </c>
       <c r="C93">
-        <v>1.163549223074598</v>
+        <v>1.152921982193708</v>
       </c>
       <c r="D93">
-        <v>2.945939223074598</v>
+        <v>2.955601982193708</v>
       </c>
       <c r="E93">
-        <v>0.87739</v>
+        <v>0.8976799999999999</v>
       </c>
       <c r="F93">
-        <v>1.84639</v>
+        <v>1.86668</v>
       </c>
       <c r="G93">
         <v>0.064</v>
@@ -8913,28 +8913,28 @@
         <v>0.445</v>
       </c>
       <c r="M93">
-        <v>0.106721342</v>
+        <v>0.107894104</v>
       </c>
       <c r="N93">
-        <v>0.338278658</v>
+        <v>0.337105896</v>
       </c>
       <c r="O93">
-        <v>0.08118687792</v>
+        <v>0.08090541504</v>
       </c>
       <c r="P93">
-        <v>0.25709178008</v>
+        <v>0.25620048096</v>
       </c>
       <c r="Q93">
-        <v>0.5730917800799999</v>
+        <v>0.5722004809600001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.404179813762008</v>
+        <v>1.569284832067268</v>
       </c>
       <c r="T93">
-        <v>6.674225593837023</v>
+        <v>7.485447998410359</v>
       </c>
       <c r="U93">
         <v>0.0578</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>4.169737670652605</v>
+        <v>4.124414435102032</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1659565465653814</v>
+        <v>0.1655624298921821</v>
       </c>
       <c r="C94">
-        <v>1.152921982193708</v>
+        <v>1.142358338126635</v>
       </c>
       <c r="D94">
-        <v>2.955601982193708</v>
+        <v>2.965328338126635</v>
       </c>
       <c r="E94">
-        <v>0.8976799999999999</v>
+        <v>0.9179700000000001</v>
       </c>
       <c r="F94">
-        <v>1.86668</v>
+        <v>1.88697</v>
       </c>
       <c r="G94">
         <v>0.064</v>
@@ -8995,28 +8995,28 @@
         <v>0.445</v>
       </c>
       <c r="M94">
-        <v>0.107894104</v>
+        <v>0.109066866</v>
       </c>
       <c r="N94">
-        <v>0.337105896</v>
+        <v>0.335933134</v>
       </c>
       <c r="O94">
-        <v>0.08090541504</v>
+        <v>0.08062395216</v>
       </c>
       <c r="P94">
-        <v>0.25620048096</v>
+        <v>0.25530918184</v>
       </c>
       <c r="Q94">
-        <v>0.5722004809600001</v>
+        <v>0.57130918184</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.569284832067268</v>
+        <v>1.781562712745459</v>
       </c>
       <c r="T94">
-        <v>7.485447998410359</v>
+        <v>8.528448232861788</v>
       </c>
       <c r="U94">
         <v>0.0578</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>4.124414435102032</v>
+        <v>4.080065892789108</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1655624298921821</v>
+        <v>0.1651683132189827</v>
       </c>
       <c r="C95">
-        <v>1.142358338126635</v>
+        <v>1.131858920803481</v>
       </c>
       <c r="D95">
-        <v>2.965328338126635</v>
+        <v>2.975118920803481</v>
       </c>
       <c r="E95">
-        <v>0.9179700000000001</v>
+        <v>0.93826</v>
       </c>
       <c r="F95">
-        <v>1.88697</v>
+        <v>1.90726</v>
       </c>
       <c r="G95">
         <v>0.064</v>
@@ -9077,28 +9077,28 @@
         <v>0.445</v>
       </c>
       <c r="M95">
-        <v>0.109066866</v>
+        <v>0.110239628</v>
       </c>
       <c r="N95">
-        <v>0.335933134</v>
+        <v>0.334760372</v>
       </c>
       <c r="O95">
-        <v>0.08062395216</v>
+        <v>0.08034248927999998</v>
       </c>
       <c r="P95">
-        <v>0.25530918184</v>
+        <v>0.25441788272</v>
       </c>
       <c r="Q95">
-        <v>0.57130918184</v>
+        <v>0.5704178827199999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.781562712745459</v>
+        <v>2.064599886983047</v>
       </c>
       <c r="T95">
-        <v>8.528448232861788</v>
+        <v>9.919115212130363</v>
       </c>
       <c r="U95">
         <v>0.0578</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>4.080065892789108</v>
+        <v>4.036660936482841</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1651683132189827</v>
+        <v>0.1673011965457834</v>
       </c>
       <c r="C96">
-        <v>1.131858920803481</v>
+        <v>1.059342426564473</v>
       </c>
       <c r="D96">
-        <v>2.975118920803481</v>
+        <v>2.922892426564473</v>
       </c>
       <c r="E96">
-        <v>0.93826</v>
+        <v>0.9585500000000001</v>
       </c>
       <c r="F96">
-        <v>1.90726</v>
+        <v>1.92755</v>
       </c>
       <c r="G96">
         <v>0.064</v>
@@ -9159,45 +9159,45 @@
         <v>0.445</v>
       </c>
       <c r="M96">
-        <v>0.110239628</v>
+        <v>0.118158815</v>
       </c>
       <c r="N96">
-        <v>0.334760372</v>
+        <v>0.326841185</v>
       </c>
       <c r="O96">
-        <v>0.08034248927999998</v>
+        <v>0.07844188440000001</v>
       </c>
       <c r="P96">
-        <v>0.25441788272</v>
+        <v>0.2483993006</v>
       </c>
       <c r="Q96">
-        <v>0.5704178827199999</v>
+        <v>0.5643993006000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.064599886983047</v>
+        <v>2.460851930915671</v>
       </c>
       <c r="T96">
-        <v>9.919115212130363</v>
+        <v>11.86604898310637</v>
       </c>
       <c r="U96">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V96">
         <v>0.24</v>
       </c>
       <c r="W96">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y96">
-        <v>4.036660936482841</v>
+        <v>3.766117661217236</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1673011965457834</v>
+        <v>0.166933679872584</v>
       </c>
       <c r="C97">
-        <v>1.059342426564473</v>
+        <v>1.047920411932874</v>
       </c>
       <c r="D97">
-        <v>2.922892426564473</v>
+        <v>2.931760411932874</v>
       </c>
       <c r="E97">
-        <v>0.9585500000000001</v>
+        <v>0.97884</v>
       </c>
       <c r="F97">
-        <v>1.92755</v>
+        <v>1.94784</v>
       </c>
       <c r="G97">
         <v>0.064</v>
@@ -9241,28 +9241,28 @@
         <v>0.445</v>
       </c>
       <c r="M97">
-        <v>0.118158815</v>
+        <v>0.119402592</v>
       </c>
       <c r="N97">
-        <v>0.326841185</v>
+        <v>0.325597408</v>
       </c>
       <c r="O97">
-        <v>0.07844188440000001</v>
+        <v>0.07814337792000001</v>
       </c>
       <c r="P97">
-        <v>0.2483993006</v>
+        <v>0.24745403008</v>
       </c>
       <c r="Q97">
-        <v>0.5643993006000001</v>
+        <v>0.5634540300800001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.460851930915671</v>
+        <v>3.055229996814607</v>
       </c>
       <c r="T97">
-        <v>11.86604898310637</v>
+        <v>14.78644963957038</v>
       </c>
       <c r="U97">
         <v>0.0613</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.766117661217236</v>
+        <v>3.726887268912889</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1669336798725841</v>
+        <v>0.1665661631993847</v>
       </c>
       <c r="C98">
-        <v>1.047920411932874</v>
+        <v>1.036552371566816</v>
       </c>
       <c r="D98">
-        <v>2.931760411932873</v>
+        <v>2.940682371566816</v>
       </c>
       <c r="E98">
-        <v>0.9788399999999998</v>
+        <v>0.99913</v>
       </c>
       <c r="F98">
-        <v>1.94784</v>
+        <v>1.96813</v>
       </c>
       <c r="G98">
         <v>0.064</v>
@@ -9323,28 +9323,28 @@
         <v>0.445</v>
       </c>
       <c r="M98">
-        <v>0.119402592</v>
+        <v>0.120646369</v>
       </c>
       <c r="N98">
-        <v>0.325597408</v>
+        <v>0.324353631</v>
       </c>
       <c r="O98">
-        <v>0.07814337792000001</v>
+        <v>0.07784487144</v>
       </c>
       <c r="P98">
-        <v>0.24745403008</v>
+        <v>0.24650875956</v>
       </c>
       <c r="Q98">
-        <v>0.5634540300800001</v>
+        <v>0.56250875956</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>3.055229996814599</v>
+        <v>4.045860106646154</v>
       </c>
       <c r="T98">
-        <v>14.78644963957034</v>
+        <v>19.65378406701033</v>
       </c>
       <c r="U98">
         <v>0.0613</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.72688726891289</v>
+        <v>3.688465750676674</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1665661631993847</v>
+        <v>0.1661986465261854</v>
       </c>
       <c r="C99">
-        <v>1.036552371566816</v>
+        <v>1.025238799735376</v>
       </c>
       <c r="D99">
-        <v>2.940682371566816</v>
+        <v>2.949658799735376</v>
       </c>
       <c r="E99">
-        <v>0.99913</v>
+        <v>1.01942</v>
       </c>
       <c r="F99">
-        <v>1.96813</v>
+        <v>1.98842</v>
       </c>
       <c r="G99">
         <v>0.064</v>
@@ -9405,28 +9405,28 @@
         <v>0.445</v>
       </c>
       <c r="M99">
-        <v>0.120646369</v>
+        <v>0.121890146</v>
       </c>
       <c r="N99">
-        <v>0.324353631</v>
+        <v>0.323109854</v>
       </c>
       <c r="O99">
-        <v>0.07784487144</v>
+        <v>0.07754636496</v>
       </c>
       <c r="P99">
-        <v>0.24650875956</v>
+        <v>0.24556348904</v>
       </c>
       <c r="Q99">
-        <v>0.56250875956</v>
+        <v>0.5615634890400001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>4.045860106646154</v>
+        <v>6.027120326309266</v>
       </c>
       <c r="T99">
-        <v>19.65378406701033</v>
+        <v>29.38845292189032</v>
       </c>
       <c r="U99">
         <v>0.0613</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.688465750676674</v>
+        <v>3.650828345057525</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1661986465261854</v>
+        <v>0.1658311298529861</v>
       </c>
       <c r="C100">
-        <v>1.025238799735376</v>
+        <v>1.013980196761127</v>
       </c>
       <c r="D100">
-        <v>2.949658799735376</v>
+        <v>2.958690196761127</v>
       </c>
       <c r="E100">
-        <v>1.01942</v>
+        <v>1.03971</v>
       </c>
       <c r="F100">
-        <v>1.98842</v>
+        <v>2.00871</v>
       </c>
       <c r="G100">
         <v>0.064</v>
@@ -9487,28 +9487,28 @@
         <v>0.445</v>
       </c>
       <c r="M100">
-        <v>0.121890146</v>
+        <v>0.123133923</v>
       </c>
       <c r="N100">
-        <v>0.323109854</v>
+        <v>0.321866077</v>
       </c>
       <c r="O100">
-        <v>0.07754636496</v>
+        <v>0.07724785848</v>
       </c>
       <c r="P100">
-        <v>0.24556348904</v>
+        <v>0.24461821852</v>
       </c>
       <c r="Q100">
-        <v>0.5615634890400001</v>
+        <v>0.56061821852</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>6.027120326309266</v>
+        <v>11.9709009852986</v>
       </c>
       <c r="T100">
-        <v>29.38845292189032</v>
+        <v>58.59245948653028</v>
       </c>
       <c r="U100">
         <v>0.0613</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.650828345057525</v>
+        <v>3.613951291067044</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1658311298529861</v>
-      </c>
-      <c r="C101">
-        <v>1.013980196761127</v>
-      </c>
-      <c r="D101">
-        <v>2.958690196761127</v>
-      </c>
-      <c r="E101">
-        <v>1.03971</v>
-      </c>
-      <c r="F101">
-        <v>2.00871</v>
-      </c>
-      <c r="G101">
-        <v>0.064</v>
-      </c>
-      <c r="H101">
-        <v>1.06</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.761</v>
-      </c>
-      <c r="K101">
-        <v>0.316</v>
-      </c>
-      <c r="L101">
-        <v>0.445</v>
-      </c>
-      <c r="M101">
-        <v>0.123133923</v>
-      </c>
-      <c r="N101">
-        <v>0.321866077</v>
-      </c>
-      <c r="O101">
-        <v>0.07724785848</v>
-      </c>
-      <c r="P101">
-        <v>0.24461821852</v>
-      </c>
-      <c r="Q101">
-        <v>0.56061821852</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>11.9709009852986</v>
-      </c>
-      <c r="T101">
-        <v>58.59245948653028</v>
-      </c>
-      <c r="U101">
-        <v>0.0613</v>
-      </c>
-      <c r="V101">
-        <v>0.24</v>
-      </c>
-      <c r="W101">
-        <v>0.046588</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba1/BB+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.613951291067044</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
